--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56164-2024</t>
+          <t>A 54293-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45624</v>
+        <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -647,49 +647,49 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 54293-2023</t>
+          <t>A 11270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45232</v>
+        <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -740,10 +740,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -755,39 +755,43 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Härfågel</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +815,7 @@
         <v>45870</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +920,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1004,7 +1008,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11270-2025</t>
+          <t>A 33920-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,14 +1018,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45726</v>
+        <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1034,7 +1038,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1043,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1055,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -1074,46 +1078,46 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Härfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 33920-2026</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1123,14 +1127,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46252</v>
+        <v>45624</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1143,7 +1147,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>15.7</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1152,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1167,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1176,46 +1180,42 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34906-2022</t>
+          <t>A 9847-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44796</v>
+        <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9847-2022</t>
+          <t>A 34906-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44620</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44627</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50987-2022</t>
+          <t>A 46713-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44867</v>
+        <v>44851</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46713-2022</t>
+          <t>A 50987-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44851</v>
+        <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.7</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44460</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44460</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44858</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45267</v>
+        <v>45358</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>12.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45338</v>
+        <v>45554</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3850,11 +3850,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44867</v>
+        <v>45435</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45253</v>
+        <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50709-2021</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44460</v>
+        <v>45510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>9.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45359</v>
+        <v>45643</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44858</v>
+        <v>45635</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44895</v>
+        <v>45386</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45327</v>
+        <v>44973</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45397</v>
+        <v>45264</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45116</v>
+        <v>45253</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45359</v>
+        <v>45253</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45279</v>
+        <v>45569</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4656,8 +4656,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4700,7 +4705,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4714,10 +4719,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45279</v>
+        <v>45359</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4730,7 +4735,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4773,7 +4778,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45435</v>
+        <v>45358</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4803,7 +4808,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4846,7 +4851,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4860,10 +4865,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44934</v>
+        <v>45792</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4876,7 +4881,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4919,7 +4924,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4933,10 +4938,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44862</v>
+        <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4949,7 +4954,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4992,7 +4997,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44988</v>
+        <v>45685</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5022,7 +5027,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45260</v>
+        <v>45594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44616</v>
+        <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45055</v>
+        <v>44935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5241,7 +5246,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5284,7 +5289,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5298,10 +5303,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45450</v>
+        <v>45475</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5314,7 +5319,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5357,7 +5362,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45688</v>
+        <v>45604</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5386,13 +5391,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45358</v>
+        <v>45475</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>12.2</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45825</v>
+        <v>45840</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5581,7 +5581,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45728</v>
+        <v>45629</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45595</v>
+        <v>45629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5727,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45832</v>
+        <v>45146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5800,7 +5800,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44539</v>
+        <v>44550</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46069</v>
+        <v>46020</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45834</v>
+        <v>45232</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45713</v>
+        <v>44539</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45146</v>
+        <v>45685</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45685</v>
+        <v>44655</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6248,14 +6248,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45786</v>
+        <v>45638</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45841</v>
+        <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33664-2025</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6394,14 +6394,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45841</v>
+        <v>45728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45217</v>
+        <v>45435</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33910-2025</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45842</v>
+        <v>45899</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45569</v>
+        <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6632,13 +6632,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45898</v>
+        <v>46038</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6711,7 +6706,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45899</v>
+        <v>45825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6779,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45667</v>
+        <v>44895</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6852,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6895,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6909,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45434</v>
+        <v>45908</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6925,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6968,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6982,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45908</v>
+        <v>44771</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +6998,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7041,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7055,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45308</v>
+        <v>45832</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7071,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7114,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45701</v>
+        <v>46048</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7148,8 +7143,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45348</v>
+        <v>45740</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45870</v>
+        <v>45142</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7348,14 +7348,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45870</v>
+        <v>45834</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44700</v>
+        <v>45575</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7440,8 +7440,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7489,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7494,14 +7499,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44893</v>
+        <v>45786</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7514,7 +7519,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7557,7 +7562,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7571,10 +7576,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45622</v>
+        <v>44823</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7587,7 +7592,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7635,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7644,10 +7649,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46073</v>
+        <v>45841</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7660,7 +7665,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7708,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 33664-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7722,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46073</v>
+        <v>45841</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7733,7 +7738,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7776,7 +7781,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 33910-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7790,10 +7795,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46073</v>
+        <v>45842</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7806,7 +7811,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7849,7 +7854,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7863,10 +7868,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46073</v>
+        <v>45176</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7879,7 +7884,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7922,7 +7927,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7936,10 +7941,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46073</v>
+        <v>45327</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7952,7 +7957,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7995,7 +8000,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8009,10 +8014,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44934</v>
+        <v>45230</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8025,7 +8030,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8068,7 +8073,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8082,10 +8087,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45643</v>
+        <v>45667</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8098,7 +8103,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8141,7 +8146,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8155,10 +8160,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45601</v>
+        <v>46069</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8171,7 +8176,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8214,7 +8219,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44973</v>
+        <v>45701</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8244,7 +8249,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8287,7 +8292,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8297,14 +8302,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45271</v>
+        <v>46073</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8317,7 +8322,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8360,7 +8365,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8374,10 +8379,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45142</v>
+        <v>46073</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8390,7 +8395,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8433,7 +8438,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8447,10 +8452,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45116</v>
+        <v>46073</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8463,7 +8468,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8506,7 +8511,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8520,10 +8525,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45116</v>
+        <v>46073</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8536,7 +8541,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8579,7 +8584,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8593,10 +8598,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45645</v>
+        <v>46073</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8609,7 +8614,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8652,7 +8657,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8666,10 +8671,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45569</v>
+        <v>45870</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8681,13 +8686,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8740,14 +8740,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45575</v>
+        <v>45870</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8759,13 +8759,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8808,7 +8803,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8822,10 +8817,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44771</v>
+        <v>44895</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8838,7 +8833,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8881,7 +8876,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8895,10 +8890,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44642</v>
+        <v>45687</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8911,7 +8906,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8971,7 +8966,7 @@
         <v>45943</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9032,7 +9027,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9042,14 +9037,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46091</v>
+        <v>45271</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9062,7 +9057,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>10.9</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9105,7 +9100,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9119,10 +9114,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45947</v>
+        <v>44867</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9135,7 +9130,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9178,7 +9173,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9192,10 +9187,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44601</v>
+        <v>45947</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9208,7 +9203,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9268,7 +9263,7 @@
         <v>45947</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9324,7 +9319,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9338,10 +9333,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46097</v>
+        <v>45947</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9354,7 +9349,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9397,7 +9392,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9411,10 +9406,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45947</v>
+        <v>45757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9427,7 +9422,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9470,7 +9465,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9484,10 +9479,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44816</v>
+        <v>45576</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9500,7 +9495,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9543,7 +9538,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9557,10 +9552,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45715</v>
+        <v>45090</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9572,13 +9567,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9621,7 +9611,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9635,10 +9625,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45960</v>
+        <v>45265</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9651,7 +9641,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>19.8</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9694,7 +9684,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9708,10 +9698,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45960</v>
+        <v>46091</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9724,7 +9714,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>10.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9767,7 +9757,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31967-2024</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9781,10 +9771,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45510</v>
+        <v>45359</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9797,7 +9787,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>9.1</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9840,7 +9830,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9854,10 +9844,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45637</v>
+        <v>46097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9870,7 +9860,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9913,7 +9903,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9930,7 +9920,7 @@
         <v>45960</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9943,7 +9933,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9986,7 +9976,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10000,10 +9990,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45687</v>
+        <v>45960</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10016,7 +10006,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.8</v>
+        <v>19.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10059,7 +10049,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10069,14 +10059,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45202</v>
+        <v>45279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10089,7 +10079,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10132,7 +10122,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10146,10 +10136,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44823</v>
+        <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10162,7 +10152,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10222,7 +10212,7 @@
         <v>46113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10283,7 +10273,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10297,10 +10287,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44579</v>
+        <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10356,7 +10346,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10370,10 +10360,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45971</v>
+        <v>45348</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10386,7 +10376,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10429,7 +10419,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10443,10 +10433,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45176</v>
+        <v>45971</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10459,7 +10449,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10502,7 +10492,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10516,10 +10506,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45979</v>
+        <v>44935</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10532,7 +10522,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10575,7 +10565,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10589,10 +10579,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45253</v>
+        <v>44934</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10605,7 +10595,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10648,7 +10638,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10662,10 +10652,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45994</v>
+        <v>45979</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10678,7 +10668,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10721,7 +10711,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10735,10 +10725,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45993</v>
+        <v>45940</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10751,7 +10741,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>19.6</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10794,7 +10784,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10808,10 +10798,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45098</v>
+        <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10824,7 +10814,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10867,7 +10857,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10881,10 +10871,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44685</v>
+        <v>44461</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10897,7 +10887,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10940,7 +10930,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10954,10 +10944,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44685</v>
+        <v>45677</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10970,7 +10960,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11013,7 +11003,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11023,14 +11013,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44900</v>
+        <v>45299</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11043,7 +11033,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11086,7 +11076,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11100,10 +11090,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45541</v>
+        <v>45777</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11116,7 +11106,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11159,7 +11149,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11169,14 +11159,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45299</v>
+        <v>44616</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11189,7 +11179,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11232,7 +11222,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11242,14 +11232,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45740</v>
+        <v>45637</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11262,7 +11252,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11305,7 +11295,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11319,10 +11309,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46136</v>
+        <v>45993</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11335,7 +11325,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>19.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11378,7 +11368,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11392,10 +11382,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45840</v>
+        <v>45098</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11408,7 +11398,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11451,7 +11441,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11465,10 +11455,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44875</v>
+        <v>44934</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11481,7 +11471,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>8.4</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11524,7 +11514,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11538,10 +11528,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44461</v>
+        <v>45994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11554,7 +11544,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11597,7 +11587,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11611,10 +11601,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44461</v>
+        <v>45196</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11627,7 +11617,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11670,7 +11660,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11684,10 +11674,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46020</v>
+        <v>45595</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11700,7 +11690,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11743,7 +11733,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11753,14 +11743,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45940</v>
+        <v>44631</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11773,7 +11763,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11816,7 +11806,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11833,7 +11823,7 @@
         <v>45142</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11846,7 +11836,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11889,7 +11879,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11903,10 +11893,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44909</v>
+        <v>44461</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11919,7 +11909,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11962,7 +11952,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11976,10 +11966,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44550</v>
+        <v>45243</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11992,7 +11982,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12035,7 +12025,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12049,10 +12039,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46129</v>
+        <v>45478</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12065,7 +12055,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12108,7 +12098,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12122,10 +12112,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45576</v>
+        <v>46129</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12138,7 +12128,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12181,7 +12171,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12198,7 +12188,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12211,7 +12201,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12254,7 +12244,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12268,10 +12258,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46038</v>
+        <v>44979</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12284,7 +12274,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12327,7 +12317,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12341,10 +12331,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46048</v>
+        <v>45359</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12356,13 +12346,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12405,7 +12390,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12419,10 +12404,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45338</v>
+        <v>45358</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12434,13 +12419,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12483,7 +12463,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12497,10 +12477,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45243</v>
+        <v>45561</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12513,7 +12493,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12556,7 +12536,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12570,10 +12550,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45777</v>
+        <v>45246</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12586,7 +12566,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12629,7 +12609,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 50709-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12643,10 +12623,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45344</v>
+        <v>44460</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12659,7 +12639,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12702,7 +12682,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 50712-2021</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12716,10 +12696,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45478</v>
+        <v>44460</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12732,7 +12712,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12775,7 +12755,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12789,10 +12769,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45180</v>
+        <v>45967</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12805,7 +12785,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12848,7 +12828,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12858,14 +12838,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44644</v>
+        <v>46157</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12878,7 +12858,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12921,7 +12901,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12931,14 +12911,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45435</v>
+        <v>45377</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12951,7 +12931,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12994,7 +12974,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13008,10 +12988,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45621</v>
+        <v>45898</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13024,7 +13004,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13067,7 +13047,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13081,10 +13061,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45160</v>
+        <v>45217</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13097,7 +13077,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13140,7 +13120,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13154,10 +13134,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45196</v>
+        <v>44551</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13170,7 +13150,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13213,7 +13193,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13227,10 +13207,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45358</v>
+        <v>44685</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13243,7 +13223,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13286,7 +13266,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13300,10 +13280,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44565</v>
+        <v>44685</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13316,7 +13296,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13359,7 +13339,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13373,10 +13353,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45218</v>
+        <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13389,7 +13369,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13432,7 +13412,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13446,10 +13426,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45967</v>
+        <v>45944</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13462,7 +13442,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13505,7 +13485,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13519,10 +13499,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45898</v>
+        <v>46178</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13535,7 +13515,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13578,7 +13558,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13592,10 +13572,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45377</v>
+        <v>46196</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13608,7 +13588,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13651,7 +13631,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13665,10 +13645,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46157</v>
+        <v>46195</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13724,7 +13704,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13738,10 +13718,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45629</v>
+        <v>46195</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13754,7 +13734,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13797,7 +13777,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13811,10 +13791,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45226</v>
+        <v>46198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13827,7 +13807,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13870,7 +13850,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13884,10 +13864,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45629</v>
+        <v>45221</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13900,7 +13880,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13943,7 +13923,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13957,10 +13937,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44637</v>
+        <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13973,7 +13953,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14016,7 +13996,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14030,10 +14010,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45232</v>
+        <v>45622</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14046,7 +14026,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14089,7 +14069,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14103,10 +14083,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45728</v>
+        <v>45397</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14119,7 +14099,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14162,7 +14142,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14176,10 +14156,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45757</v>
+        <v>45910</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14192,7 +14172,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14235,7 +14215,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14249,10 +14229,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46171</v>
+        <v>46209</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14265,7 +14245,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14308,7 +14288,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14322,10 +14302,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45944</v>
+        <v>44895</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14338,7 +14318,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14381,7 +14361,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14395,10 +14375,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45142</v>
+        <v>44895</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14411,7 +14391,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14454,7 +14434,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14468,10 +14448,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45274</v>
+        <v>46212</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14484,7 +14464,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14527,7 +14507,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14541,10 +14521,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44615</v>
+        <v>44565</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14557,7 +14537,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14600,7 +14580,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14614,10 +14594,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45265</v>
+        <v>46045</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14630,7 +14610,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14673,7 +14653,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14687,10 +14667,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46178</v>
+        <v>46265</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14703,7 +14683,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14746,7 +14726,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14760,10 +14740,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45320</v>
+        <v>46220</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14776,7 +14756,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14819,7 +14799,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14833,10 +14813,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45264</v>
+        <v>46220</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14849,7 +14829,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.2</v>
+        <v>15.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14892,7 +14872,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14906,10 +14886,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44895</v>
+        <v>46220</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14922,7 +14902,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14965,7 +14945,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14979,10 +14959,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44895</v>
+        <v>45629</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14995,7 +14975,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15038,7 +15018,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15052,10 +15032,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45253</v>
+        <v>45338</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15067,8 +15047,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15111,7 +15096,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15125,10 +15110,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45043</v>
+        <v>44862</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15141,7 +15126,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15184,7 +15169,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15198,10 +15183,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45701</v>
+        <v>45116</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15214,7 +15199,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15257,7 +15242,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15271,10 +15256,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44895</v>
+        <v>45116</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15287,7 +15272,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15330,7 +15315,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15344,10 +15329,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46195</v>
+        <v>46227</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15360,7 +15345,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15403,7 +15388,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15417,10 +15402,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46195</v>
+        <v>45142</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15433,7 +15418,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15476,7 +15461,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15490,10 +15475,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45561</v>
+        <v>44988</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15506,7 +15491,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15549,7 +15534,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15563,10 +15548,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46197</v>
+        <v>45274</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15579,7 +15564,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15622,7 +15607,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15636,10 +15621,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45142</v>
+        <v>45629</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15652,7 +15637,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15695,7 +15680,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15709,10 +15694,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46196</v>
+        <v>44837</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15725,7 +15710,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15768,7 +15753,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 50712-2021</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15782,10 +15767,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44460</v>
+        <v>45267</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15798,7 +15783,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15858,7 +15843,7 @@
         <v>44460</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15914,7 +15899,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15928,10 +15913,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44900</v>
+        <v>45677</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15944,7 +15929,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,7 +15972,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16001,10 +15986,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46198</v>
+        <v>45688</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16016,8 +16001,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16060,7 +16050,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16064,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44935</v>
+        <v>45541</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16080,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16133,7 +16123,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16147,10 +16137,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44935</v>
+        <v>44579</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16163,7 +16153,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16206,7 +16196,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16220,10 +16210,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44539</v>
+        <v>45601</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16236,7 +16226,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16279,7 +16269,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16293,10 +16283,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44551</v>
+        <v>45202</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16309,7 +16299,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16352,7 +16342,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16366,10 +16356,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44979</v>
+        <v>45266</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16382,7 +16372,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16425,7 +16415,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16435,14 +16425,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45146</v>
+        <v>45005</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16498,7 +16488,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16512,10 +16502,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45359</v>
+        <v>45338</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16527,8 +16517,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16571,7 +16566,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16585,10 +16580,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45358</v>
+        <v>45434</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16601,7 +16596,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16644,7 +16639,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16658,10 +16653,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45230</v>
+        <v>44900</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16674,7 +16669,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16717,7 +16712,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16731,10 +16726,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45005</v>
+        <v>45142</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16747,7 +16742,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16790,7 +16785,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16804,10 +16799,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45246</v>
+        <v>44858</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16820,7 +16815,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16863,7 +16858,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16877,10 +16872,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45221</v>
+        <v>45160</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16893,7 +16888,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16936,7 +16931,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16950,10 +16945,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45090</v>
+        <v>45435</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16966,7 +16961,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17009,7 +17004,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17019,14 +17014,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
         <v>45435</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17039,7 +17034,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17082,7 +17077,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17096,10 +17091,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46209</v>
+        <v>45320</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17112,7 +17107,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17155,7 +17150,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17169,10 +17164,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45910</v>
+        <v>45218</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17185,7 +17180,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17228,7 +17223,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17242,10 +17237,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45237</v>
+        <v>45344</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17258,7 +17253,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17301,7 +17296,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17315,10 +17310,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46212</v>
+        <v>44601</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17331,7 +17326,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17374,7 +17369,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17388,10 +17383,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45448</v>
+        <v>45253</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17404,7 +17399,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17447,7 +17442,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17461,10 +17456,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46045</v>
+        <v>45569</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17476,8 +17471,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17520,7 +17520,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17530,14 +17530,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45435</v>
+        <v>45146</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17593,7 +17593,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45358</v>
+        <v>45728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17676,14 +17676,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44631</v>
+        <v>44642</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17739,7 +17739,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17753,10 +17753,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45677</v>
+        <v>44615</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17812,7 +17812,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17826,10 +17826,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45628</v>
+        <v>45450</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17899,10 +17899,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45677</v>
+        <v>45253</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17958,7 +17958,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17972,10 +17972,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45266</v>
+        <v>45308</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18031,7 +18031,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18045,10 +18045,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46220</v>
+        <v>44893</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18118,10 +18118,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45635</v>
+        <v>44637</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18177,7 +18177,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18191,10 +18191,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46265</v>
+        <v>44539</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18250,7 +18250,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18264,10 +18264,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46220</v>
+        <v>45116</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18323,7 +18323,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18337,10 +18337,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45387</v>
+        <v>44812</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18396,7 +18396,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18410,10 +18410,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46220</v>
+        <v>44816</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18483,10 +18483,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45554</v>
+        <v>45237</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18498,13 +18498,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18547,7 +18542,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18561,10 +18556,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45569</v>
+        <v>44875</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18576,13 +18571,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18625,7 +18615,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18639,10 +18629,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46227</v>
+        <v>44909</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18655,7 +18645,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -18698,7 +18688,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18712,10 +18702,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45719</v>
+        <v>45701</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18727,13 +18717,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18776,7 +18761,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18790,10 +18775,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44463</v>
+        <v>44900</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18806,7 +18791,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18849,7 +18834,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18863,10 +18848,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44812</v>
+        <v>45226</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18879,7 +18864,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18922,7 +18907,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18932,14 +18917,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44655</v>
+        <v>44644</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18952,7 +18937,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18995,7 +18980,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19009,10 +18994,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44600</v>
+        <v>45265</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19025,7 +19010,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19068,7 +19053,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19082,10 +19067,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44837</v>
+        <v>45180</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19098,7 +19083,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19141,7 +19126,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19155,10 +19140,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45253</v>
+        <v>45645</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19171,7 +19156,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19214,7 +19199,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 52237-2021</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19228,10 +19213,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45630</v>
+        <v>44463</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19244,7 +19229,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19287,7 +19272,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19301,10 +19286,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45265</v>
+        <v>45358</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19317,7 +19302,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19360,7 +19345,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19374,10 +19359,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45386</v>
+        <v>45260</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19390,7 +19375,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19433,7 +19418,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19447,10 +19432,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45665</v>
+        <v>45715</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19462,8 +19447,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19506,7 +19496,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19520,10 +19510,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45387</v>
+        <v>45043</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19536,7 +19526,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19579,7 +19569,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19589,14 +19579,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45365</v>
+        <v>44600</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19599,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19642,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19666,10 +19656,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45713</v>
+        <v>45719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19681,8 +19671,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19720,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19734,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45792</v>
+        <v>45621</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19750,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19793,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19812,10 +19807,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45594</v>
+        <v>45569</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19827,8 +19822,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I261" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45792</v>
+        <v>45387</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45685</v>
+        <v>45055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20017,7 +20017,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20031,10 +20031,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45629</v>
+        <v>45728</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20090,7 +20090,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20104,10 +20104,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45629</v>
+        <v>44700</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20163,7 +20163,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45475</v>
+        <v>45630</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20236,7 +20236,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20250,10 +20250,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45604</v>
+        <v>45665</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20309,7 +20309,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45475</v>
+        <v>45387</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20382,7 +20382,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45638</v>
+        <v>45365</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20455,7 +20455,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45728</v>
+        <v>45713</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20528,7 +20528,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 1352-2022</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20542,10 +20542,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44628</v>
+        <v>45323</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20557,13 +20557,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I271" t="n">
-        <v>47.1</v>
+        <v>3.8</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -20606,7 +20601,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 1352-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20616,14 +20611,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44601</v>
+        <v>44628</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20637,11 +20632,11 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.4</v>
+        <v>47.1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -20684,7 +20679,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20701,7 +20696,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20714,7 +20709,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>3.8</v>
+        <v>38.9</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -20757,7 +20752,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 510-2025</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20767,14 +20762,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45706</v>
+        <v>44601</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -20786,8 +20781,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I274" t="n">
-        <v>32.6</v>
+        <v>1.4</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -20830,7 +20830,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -20840,14 +20840,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45323</v>
+        <v>45368</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>38.9</v>
+        <v>2.9</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -20903,7 +20903,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -20913,14 +20913,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45368</v>
+        <v>45323</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -20976,7 +20976,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -20993,7 +20993,7 @@
         <v>45323</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>7.9</v>
+        <v>16.3</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 280-2024</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21063,10 +21063,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45323</v>
+        <v>45706</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>16.3</v>
+        <v>32.6</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54293-2023</t>
+          <t>A 11270-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45232</v>
+        <v>45726</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -635,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,46 +650,50 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Härfågel</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 11270-2025</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +707,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45726</v>
+        <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +723,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>15.7</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -740,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -752,46 +756,42 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Härfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
@@ -815,7 +815,7 @@
         <v>45870</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 33920-2026</t>
+          <t>A 54293-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1018,14 +1018,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46252</v>
+        <v>45232</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,151 +1074,151 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 33920-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Gulsparv</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56164-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45624</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 9847-2022</t>
+          <t>A 34906-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44620</v>
+        <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34906-2022</t>
+          <t>A 9847-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44627</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44851</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 50699-2021</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44460</v>
+        <v>45142</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 50702-2021</t>
+          <t>A 5174-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44460</v>
+        <v>44594</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49047-2022</t>
+          <t>A 50699-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44858</v>
+        <v>44460</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50985-2022</t>
+          <t>A 50702-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44867</v>
+        <v>44460</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5174-2022</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44594</v>
+        <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50984-2022</t>
+          <t>A 49047-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44867</v>
+        <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33171-2022</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44785</v>
+        <v>45274</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10503-2022</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44623</v>
+        <v>45359</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12173-2022</t>
+          <t>A 50984-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44636</v>
+        <v>44867</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12175-2022</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44636</v>
+        <v>45338</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3556,8 +3556,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3600,7 +3605,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21085-2022</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3614,10 +3619,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44704</v>
+        <v>44867</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3630,7 +3635,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3673,7 +3678,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9212-2022</t>
+          <t>A 33171-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3687,10 +3692,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44616</v>
+        <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3703,7 +3708,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3746,7 +3751,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3760,10 +3765,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45358</v>
+        <v>44615</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3776,7 +3781,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>12.2</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3819,7 +3824,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3833,10 +3838,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45554</v>
+        <v>45265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3848,13 +3853,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45435</v>
+        <v>45253</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 50985-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45628</v>
+        <v>44867</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31967-2024</t>
+          <t>A 10503-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45510</v>
+        <v>44623</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.1</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45643</v>
+        <v>45359</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 50709-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45635</v>
+        <v>44460</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 12173-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45386</v>
+        <v>44636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 12175-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44973</v>
+        <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 21085-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45264</v>
+        <v>44704</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 9212-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45253</v>
+        <v>44616</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45253</v>
+        <v>44858</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45569</v>
+        <v>45271</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4656,13 +4656,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4705,7 +4700,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4719,10 +4714,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45359</v>
+        <v>45320</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4735,7 +4730,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4778,7 +4773,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45358</v>
+        <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4808,7 +4803,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4851,7 +4846,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4865,10 +4860,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45792</v>
+        <v>45327</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4881,7 +4876,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45792</v>
+        <v>45264</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45685</v>
+        <v>45397</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5027,7 +5022,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45594</v>
+        <v>44895</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45713</v>
+        <v>44895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5230,10 +5225,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44935</v>
+        <v>45253</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5246,7 +5241,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5289,7 +5284,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5303,10 +5298,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45475</v>
+        <v>45116</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5319,7 +5314,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5362,7 +5357,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5376,10 +5371,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45604</v>
+        <v>45043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5392,7 +5387,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5430,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5444,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45475</v>
+        <v>45435</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5460,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5503,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5518,14 +5513,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45840</v>
+        <v>45279</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5595,10 +5590,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45629</v>
+        <v>45279</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5611,7 +5606,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5649,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5663,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45629</v>
+        <v>44539</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5684,7 +5679,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5722,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5736,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45146</v>
+        <v>45450</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5757,7 +5752,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5800,7 +5795,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5814,10 +5809,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44550</v>
+        <v>45713</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5830,7 +5825,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5868,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5887,10 +5882,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46020</v>
+        <v>45146</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5903,7 +5898,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5941,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5955,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45232</v>
+        <v>45685</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5971,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6014,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6028,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44539</v>
+        <v>44934</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6044,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6087,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6101,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45685</v>
+        <v>46091</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6117,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6160,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6174,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44655</v>
+        <v>45898</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6190,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6233,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6247,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45638</v>
+        <v>46097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6263,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6306,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6320,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45448</v>
+        <v>45899</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6336,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6379,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6394,14 +6389,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45728</v>
+        <v>44988</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6409,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6452,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6466,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45435</v>
+        <v>44862</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6487,7 +6482,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6525,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6544,10 +6539,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45899</v>
+        <v>45908</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6555,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6598,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6612,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45898</v>
+        <v>44616</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6633,7 +6628,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6671,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6685,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46038</v>
+        <v>45701</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6706,7 +6701,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6744,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6758,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45825</v>
+        <v>45260</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6779,7 +6774,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6817,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6836,10 +6831,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44895</v>
+        <v>46113</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6851,8 +6846,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6895,7 +6895,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45908</v>
+        <v>44895</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44771</v>
+        <v>45055</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45832</v>
+        <v>45688</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7070,8 +7070,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7114,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7128,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46048</v>
+        <v>45358</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7143,13 +7148,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>12.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45740</v>
+        <v>45728</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45142</v>
+        <v>45595</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45834</v>
+        <v>45561</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45575</v>
+        <v>45142</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7440,13 +7440,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7489,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 50712-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7499,14 +7494,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45786</v>
+        <v>44460</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7519,7 +7514,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7562,7 +7557,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 50713-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7576,10 +7571,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44823</v>
+        <v>44460</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7592,7 +7587,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7635,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7645,14 +7640,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45841</v>
+        <v>45299</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7665,7 +7660,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7708,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33664-2025</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7722,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45841</v>
+        <v>45943</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7737,8 +7732,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7781,7 +7781,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33910-2025</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45842</v>
+        <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7854,7 +7854,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7868,10 +7868,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45176</v>
+        <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7927,7 +7927,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45327</v>
+        <v>45947</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8000,7 +8000,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45230</v>
+        <v>45947</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8073,7 +8073,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45667</v>
+        <v>46136</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8146,7 +8146,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46069</v>
+        <v>45217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8219,7 +8219,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8233,10 +8233,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45701</v>
+        <v>45569</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8248,8 +8248,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8292,7 +8297,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8306,10 +8311,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46073</v>
+        <v>44461</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8322,7 +8327,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8365,7 +8370,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8379,10 +8384,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46073</v>
+        <v>44461</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8395,7 +8400,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8438,7 +8443,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8452,10 +8457,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46073</v>
+        <v>45940</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8468,7 +8473,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>9</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8511,7 +8516,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8525,10 +8530,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46073</v>
+        <v>45434</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8541,7 +8546,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8584,7 +8589,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8598,10 +8603,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46073</v>
+        <v>44935</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8614,7 +8619,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8657,7 +8662,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8671,10 +8676,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45870</v>
+        <v>45960</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8687,7 +8692,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>19.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8730,7 +8735,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8740,14 +8745,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45870</v>
+        <v>45960</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8760,7 +8765,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8803,7 +8808,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8817,10 +8822,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44895</v>
+        <v>45308</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8833,7 +8838,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8876,7 +8881,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8890,10 +8895,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45687</v>
+        <v>45348</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8906,7 +8911,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8949,7 +8954,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8963,10 +8968,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45943</v>
+        <v>45960</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8978,13 +8983,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9037,14 +9037,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45271</v>
+        <v>44700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44867</v>
+        <v>44893</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9173,7 +9173,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9187,10 +9187,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45947</v>
+        <v>46129</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45947</v>
+        <v>45622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9319,7 +9319,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9333,10 +9333,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45947</v>
+        <v>44934</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9392,7 +9392,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9406,10 +9406,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45757</v>
+        <v>45643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9465,7 +9465,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45576</v>
+        <v>45601</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9538,7 +9538,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45090</v>
+        <v>45971</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9611,7 +9611,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45265</v>
+        <v>44935</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9684,7 +9684,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9698,10 +9698,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46091</v>
+        <v>44973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>10.9</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9757,7 +9757,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45359</v>
+        <v>45142</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46097</v>
+        <v>45116</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45960</v>
+        <v>45116</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45960</v>
+        <v>45645</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>19.8</v>
+        <v>3.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10049,7 +10049,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10059,14 +10059,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45279</v>
+        <v>44539</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10122,7 +10122,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45279</v>
+        <v>45777</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46113</v>
+        <v>45979</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10224,13 +10224,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10273,7 +10268,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10287,10 +10282,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45960</v>
+        <v>44551</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10303,7 +10298,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10346,7 +10341,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10360,10 +10355,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45348</v>
+        <v>44979</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10376,7 +10371,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10419,7 +10414,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10429,14 +10424,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45971</v>
+        <v>45146</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10449,7 +10444,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10492,7 +10487,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10506,10 +10501,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44935</v>
+        <v>45569</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10521,8 +10516,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10565,7 +10565,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44934</v>
+        <v>45575</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10594,8 +10594,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10638,7 +10643,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10652,10 +10657,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45979</v>
+        <v>44771</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10668,7 +10673,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10711,7 +10716,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10725,10 +10730,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45940</v>
+        <v>44642</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10741,7 +10746,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10784,7 +10789,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10798,10 +10803,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46136</v>
+        <v>45994</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10814,7 +10819,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10857,7 +10862,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10871,10 +10876,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44461</v>
+        <v>45993</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10887,7 +10892,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>19.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10930,7 +10935,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10944,10 +10949,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45677</v>
+        <v>44601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10960,7 +10965,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11003,7 +11008,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11013,14 +11018,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45299</v>
+        <v>44816</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11033,7 +11038,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11076,7 +11081,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11090,10 +11095,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45777</v>
+        <v>45715</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11105,8 +11110,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11149,7 +11159,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11163,10 +11173,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44616</v>
+        <v>45510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11179,7 +11189,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>9.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11239,7 +11249,7 @@
         <v>45637</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11295,7 +11305,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11309,10 +11319,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45993</v>
+        <v>45359</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11325,7 +11335,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>19.6</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11368,7 +11378,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11382,10 +11392,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45098</v>
+        <v>45358</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11398,7 +11408,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11441,7 +11451,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11455,10 +11465,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44934</v>
+        <v>45687</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11471,7 +11481,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11514,7 +11524,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11528,10 +11538,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45994</v>
+        <v>45967</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11544,7 +11554,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11587,7 +11597,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11601,10 +11611,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45196</v>
+        <v>45202</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11617,7 +11627,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11660,7 +11670,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11674,10 +11684,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45595</v>
+        <v>44823</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11690,7 +11700,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11733,7 +11743,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11743,14 +11753,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44631</v>
+        <v>44579</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11763,7 +11773,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11806,7 +11816,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11820,10 +11830,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45142</v>
+        <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11836,7 +11846,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11879,7 +11889,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11893,10 +11903,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44461</v>
+        <v>45377</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11909,7 +11919,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11952,7 +11962,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11966,10 +11976,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45243</v>
+        <v>46157</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11982,7 +11992,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12025,7 +12035,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12039,10 +12049,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45478</v>
+        <v>45840</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12055,7 +12065,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12098,7 +12108,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12112,10 +12122,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46129</v>
+        <v>46020</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12128,7 +12138,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12171,7 +12181,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12185,10 +12195,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45265</v>
+        <v>45230</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12201,7 +12211,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12244,7 +12254,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12258,10 +12268,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44979</v>
+        <v>45176</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12274,7 +12284,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12317,7 +12327,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12331,10 +12341,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45359</v>
+        <v>46038</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12347,7 +12357,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12390,7 +12400,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12404,10 +12414,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45358</v>
+        <v>45005</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12420,7 +12430,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12473,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12487,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45561</v>
+        <v>45253</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12503,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12553,7 +12563,7 @@
         <v>45246</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12609,7 +12619,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 50709-2021</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12623,10 +12633,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44460</v>
+        <v>45221</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12639,7 +12649,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12682,7 +12692,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 50712-2021</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12696,10 +12706,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44460</v>
+        <v>46171</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12712,7 +12722,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12755,7 +12765,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12769,10 +12779,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45967</v>
+        <v>45944</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12785,7 +12795,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12828,7 +12838,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12842,10 +12852,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46157</v>
+        <v>45098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12858,7 +12868,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12901,7 +12911,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12915,10 +12925,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45377</v>
+        <v>44685</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12931,7 +12941,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12974,7 +12984,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12988,10 +12998,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45898</v>
+        <v>44685</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13004,7 +13014,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13047,7 +13057,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13061,10 +13071,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45217</v>
+        <v>44900</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13077,7 +13087,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13120,7 +13130,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13134,10 +13144,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44551</v>
+        <v>45090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13150,7 +13160,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13193,7 +13203,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13207,10 +13217,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44685</v>
+        <v>45541</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13266,7 +13276,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13280,10 +13290,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44685</v>
+        <v>45435</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13296,7 +13306,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13339,7 +13349,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13353,10 +13363,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46171</v>
+        <v>46048</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13368,8 +13378,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13412,7 +13427,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13426,10 +13441,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45944</v>
+        <v>46178</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13442,7 +13457,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13485,7 +13500,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13495,14 +13510,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46178</v>
+        <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13515,7 +13530,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13558,7 +13573,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13572,10 +13587,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46196</v>
+        <v>44875</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13588,7 +13603,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13631,7 +13646,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13645,10 +13660,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46195</v>
+        <v>46069</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13661,7 +13676,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13704,7 +13719,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13718,10 +13733,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46195</v>
+        <v>45142</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13734,7 +13749,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13777,7 +13792,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13791,10 +13806,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46198</v>
+        <v>44909</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13807,7 +13822,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13850,7 +13865,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13864,10 +13879,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45221</v>
+        <v>44550</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13880,7 +13895,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13923,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13937,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46197</v>
+        <v>46073</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13953,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13996,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14010,10 +14025,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45622</v>
+        <v>46073</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14026,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14069,7 +14084,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14083,10 +14098,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45397</v>
+        <v>46073</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14099,7 +14114,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14142,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14156,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45910</v>
+        <v>46073</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14172,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14215,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14229,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46209</v>
+        <v>46073</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14245,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14288,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14302,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44895</v>
+        <v>45576</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14318,7 +14333,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14361,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14375,10 +14390,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44895</v>
+        <v>45265</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14391,7 +14406,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14434,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14448,10 +14463,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46212</v>
+        <v>45237</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14464,7 +14479,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14507,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14521,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44565</v>
+        <v>46195</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14537,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>7.8</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14580,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14594,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46045</v>
+        <v>46195</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14610,7 +14625,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14653,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14667,10 +14682,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46265</v>
+        <v>45448</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14683,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14726,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14740,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46220</v>
+        <v>46197</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14756,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14799,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14813,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46220</v>
+        <v>45338</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14828,8 +14843,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>15.5</v>
+        <v>3.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14872,7 +14892,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14886,10 +14906,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46220</v>
+        <v>46196</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14902,7 +14922,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14945,7 +14965,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14959,10 +14979,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45629</v>
+        <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14975,7 +14995,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15018,7 +15038,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15032,10 +15052,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45338</v>
+        <v>46198</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15047,13 +15067,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15096,7 +15111,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15110,10 +15125,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44862</v>
+        <v>45435</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15126,7 +15141,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15169,7 +15184,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15183,10 +15198,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45116</v>
+        <v>45358</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15199,7 +15214,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15242,7 +15257,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15256,10 +15271,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45116</v>
+        <v>45344</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15272,7 +15287,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15315,7 +15330,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15329,10 +15344,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46227</v>
+        <v>45478</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15345,7 +15360,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15388,7 +15403,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15402,10 +15417,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45142</v>
+        <v>45180</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15418,7 +15433,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15461,7 +15476,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15471,14 +15486,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44988</v>
+        <v>44631</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15491,7 +15506,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15534,7 +15549,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15548,10 +15563,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45274</v>
+        <v>45677</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15564,7 +15579,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15607,7 +15622,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15617,14 +15632,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45629</v>
+        <v>44644</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15637,7 +15652,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15680,7 +15695,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15690,14 +15705,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44837</v>
+        <v>45435</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15710,7 +15725,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15753,7 +15768,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15767,10 +15782,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45267</v>
+        <v>45621</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15826,7 +15841,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 50713-2021</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15840,10 +15855,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44460</v>
+        <v>45160</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15856,7 +15871,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15899,7 +15914,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15913,10 +15928,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45677</v>
+        <v>45196</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15929,7 +15944,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15972,7 +15987,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15986,10 +16001,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45688</v>
+        <v>45628</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16001,13 +16016,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16050,7 +16060,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16064,10 +16074,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45541</v>
+        <v>45358</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16080,7 +16090,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16123,7 +16133,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16137,10 +16147,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44579</v>
+        <v>44565</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16153,7 +16163,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16196,7 +16206,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16210,10 +16220,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45601</v>
+        <v>45218</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16226,7 +16236,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16269,7 +16279,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16283,10 +16293,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45202</v>
+        <v>46209</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16299,7 +16309,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16342,7 +16352,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16356,10 +16366,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45266</v>
+        <v>45677</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16372,7 +16382,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16415,7 +16425,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16429,10 +16439,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45005</v>
+        <v>45910</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16445,7 +16455,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16488,7 +16498,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16502,10 +16512,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45338</v>
+        <v>45266</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16517,13 +16527,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16566,7 +16571,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16580,10 +16585,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45434</v>
+        <v>45635</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16596,7 +16601,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16639,7 +16644,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16653,10 +16658,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44900</v>
+        <v>45629</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16669,7 +16674,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16712,7 +16717,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16726,10 +16731,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45142</v>
+        <v>45226</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16742,7 +16747,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16785,7 +16790,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16799,10 +16804,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44858</v>
+        <v>46212</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16815,7 +16820,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16858,7 +16863,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16872,10 +16877,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45160</v>
+        <v>45387</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16888,7 +16893,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16931,7 +16936,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16945,10 +16950,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45435</v>
+        <v>45629</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16961,7 +16966,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17004,7 +17009,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17014,14 +17019,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45435</v>
+        <v>46045</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17034,7 +17039,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17077,7 +17082,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17091,10 +17096,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45320</v>
+        <v>44637</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17107,7 +17112,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17150,7 +17155,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17164,10 +17169,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45218</v>
+        <v>45232</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17180,7 +17185,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17223,7 +17228,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17237,10 +17242,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45344</v>
+        <v>45728</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17253,7 +17258,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17296,7 +17301,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17310,10 +17315,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44601</v>
+        <v>45757</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17326,7 +17331,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17369,7 +17374,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17383,10 +17388,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45253</v>
+        <v>45554</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17398,8 +17403,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17459,7 +17469,7 @@
         <v>45569</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17520,7 +17530,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17530,14 +17540,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45146</v>
+        <v>46220</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17550,7 +17560,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.7</v>
+        <v>15.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17593,7 +17603,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17607,10 +17617,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45728</v>
+        <v>46265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17623,7 +17633,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17666,7 +17676,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17680,10 +17690,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44642</v>
+        <v>46220</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17696,7 +17706,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17739,7 +17749,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17753,10 +17763,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44615</v>
+        <v>45719</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17768,8 +17778,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17812,7 +17827,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17826,10 +17841,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45450</v>
+        <v>46220</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17842,7 +17857,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17885,7 +17900,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 52237-2021</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17899,10 +17914,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45253</v>
+        <v>44463</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17915,7 +17930,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17958,7 +17973,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17972,10 +17987,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45308</v>
+        <v>44812</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -17988,7 +18003,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18031,7 +18046,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18045,10 +18060,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44893</v>
+        <v>46227</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18061,7 +18076,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18104,7 +18119,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18118,10 +18133,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44637</v>
+        <v>44655</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18134,7 +18149,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18177,7 +18192,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18191,10 +18206,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44539</v>
+        <v>44600</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18207,7 +18222,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18250,7 +18265,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18264,10 +18279,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45116</v>
+        <v>44837</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18280,7 +18295,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18323,7 +18338,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18337,10 +18352,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44812</v>
+        <v>45253</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18353,7 +18368,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18396,7 +18411,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18410,10 +18425,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44816</v>
+        <v>45630</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18426,7 +18441,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18469,7 +18484,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18483,10 +18498,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45237</v>
+        <v>45265</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18499,7 +18514,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18542,7 +18557,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18556,10 +18571,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44875</v>
+        <v>45386</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18572,7 +18587,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18615,7 +18630,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18629,10 +18644,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44909</v>
+        <v>45665</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18688,7 +18703,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18702,10 +18717,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45701</v>
+        <v>45387</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18718,7 +18733,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18761,7 +18776,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18771,14 +18786,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44900</v>
+        <v>45365</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18791,7 +18806,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18834,7 +18849,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18848,10 +18863,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45226</v>
+        <v>45713</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18864,7 +18879,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18907,7 +18922,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18917,14 +18932,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44644</v>
+        <v>45792</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18937,7 +18952,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18980,7 +18995,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18994,10 +19009,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45265</v>
+        <v>45594</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19010,7 +19025,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19053,7 +19068,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19067,10 +19082,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45180</v>
+        <v>45792</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19126,7 +19141,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19140,10 +19155,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45645</v>
+        <v>45685</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19156,7 +19171,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19199,7 +19214,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19213,10 +19228,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44463</v>
+        <v>45629</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19229,7 +19244,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19272,7 +19287,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19286,10 +19301,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45358</v>
+        <v>45629</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19345,7 +19360,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19359,10 +19374,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45260</v>
+        <v>45475</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19375,7 +19390,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19418,7 +19433,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19432,10 +19447,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45715</v>
+        <v>45604</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19447,13 +19462,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I256" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19496,7 +19506,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19510,10 +19520,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45043</v>
+        <v>45475</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19526,7 +19536,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19569,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19583,10 +19593,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44600</v>
+        <v>45638</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19599,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19642,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19652,14 +19662,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45719</v>
+        <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19671,13 +19681,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19720,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19734,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45621</v>
+        <v>45825</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19750,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19793,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19807,10 +19812,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45569</v>
+        <v>45832</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19822,13 +19827,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45387</v>
+        <v>45834</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19954,14 +19954,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45055</v>
+        <v>45786</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20017,7 +20017,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20031,10 +20031,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45728</v>
+        <v>45841</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20090,7 +20090,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 33664-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20104,10 +20104,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44700</v>
+        <v>45841</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20163,7 +20163,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 33910-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45630</v>
+        <v>45842</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20236,7 +20236,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20250,10 +20250,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45665</v>
+        <v>45667</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20309,7 +20309,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45387</v>
+        <v>45701</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20382,7 +20382,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45365</v>
+        <v>45870</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20455,7 +20455,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45713</v>
+        <v>45870</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20528,7 +20528,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>S 1352-2022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20542,10 +20542,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45323</v>
+        <v>44628</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20557,8 +20557,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I271" t="n">
-        <v>3.8</v>
+        <v>47.1</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -20601,7 +20606,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 1352-2022</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20611,14 +20616,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44628</v>
+        <v>44601</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20632,11 +20637,11 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>47.1</v>
+        <v>1.4</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -20679,7 +20684,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20696,7 +20701,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20709,7 +20714,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>38.9</v>
+        <v>3.8</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -20752,7 +20757,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20762,14 +20767,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>44601</v>
+        <v>45706</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -20781,13 +20786,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I274" t="n">
-        <v>1.4</v>
+        <v>32.6</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -20830,7 +20830,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -20840,14 +20840,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45368</v>
+        <v>45323</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>2.9</v>
+        <v>38.9</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -20903,7 +20903,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -20913,14 +20913,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45323</v>
+        <v>45368</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -20976,7 +20976,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 280-2024</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -20993,7 +20993,7 @@
         <v>45323</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>16.3</v>
+        <v>7.9</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 510-2025</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21063,10 +21063,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45706</v>
+        <v>45323</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>32.6</v>
+        <v>16.3</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 11270-2025</t>
+          <t>A 54293-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45726</v>
+        <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -635,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,151 +650,151 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 11270-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45726</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
           <t>Härfågel</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 56164-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45624</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>45870</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54293-2023</t>
+          <t>A 33920-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1018,14 +1018,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45232</v>
+        <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,46 +1074,50 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 33920-2026</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1123,14 +1127,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46252</v>
+        <v>45624</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1143,7 +1147,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>15.7</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1152,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1167,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1176,46 +1180,42 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62540-2021</t>
+          <t>A 10831-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44503</v>
+        <v>44627</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10831-2022</t>
+          <t>A 62540-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44627</v>
+        <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46713-2022</t>
+          <t>A 50987-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44851</v>
+        <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50987-2022</t>
+          <t>A 46713-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44867</v>
+        <v>44851</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54964-2021</t>
+          <t>A 62992-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44474</v>
+        <v>44504</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 62992-2021</t>
+          <t>A 54964-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44504</v>
+        <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 50699-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45142</v>
+        <v>44460</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5174-2022</t>
+          <t>A 50702-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44594</v>
+        <v>44460</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 50699-2021</t>
+          <t>A 49047-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44460</v>
+        <v>44858</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50702-2021</t>
+          <t>A 50985-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44460</v>
+        <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 5174-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45267</v>
+        <v>44594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49047-2022</t>
+          <t>A 50984-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44858</v>
+        <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 33171-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45274</v>
+        <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 10503-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45359</v>
+        <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50984-2022</t>
+          <t>A 12173-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44867</v>
+        <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 12175-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45338</v>
+        <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3556,13 +3556,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3605,7 +3600,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 21085-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3619,10 +3614,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44867</v>
+        <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3635,7 +3630,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3678,7 +3673,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33171-2022</t>
+          <t>A 9212-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3692,10 +3687,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44785</v>
+        <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3708,7 +3703,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3751,7 +3746,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3765,10 +3760,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44615</v>
+        <v>45554</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3780,8 +3775,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45265</v>
+        <v>45358</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>12.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45253</v>
+        <v>45435</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50985-2022</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44867</v>
+        <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10503-2022</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44623</v>
+        <v>45510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>9.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45359</v>
+        <v>45643</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50709-2021</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44460</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12173-2022</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44636</v>
+        <v>45635</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12175-2022</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44636</v>
+        <v>45386</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21085-2022</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44704</v>
+        <v>45264</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9212-2022</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44616</v>
+        <v>45253</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44858</v>
+        <v>45253</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45271</v>
+        <v>45359</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45320</v>
+        <v>45358</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44895</v>
+        <v>45569</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4802,8 +4802,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4846,7 +4851,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4860,10 +4865,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45327</v>
+        <v>45232</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4876,7 +4881,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4919,7 +4924,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4933,10 +4938,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45264</v>
+        <v>44935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4949,7 +4954,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4992,7 +4997,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45397</v>
+        <v>44655</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44895</v>
+        <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44895</v>
+        <v>45448</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45253</v>
+        <v>45435</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5241,7 +5246,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5284,7 +5289,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5298,10 +5303,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45116</v>
+        <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5314,7 +5319,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5357,7 +5362,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45043</v>
+        <v>45475</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5387,7 +5392,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5430,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5444,10 +5449,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45435</v>
+        <v>45604</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5460,7 +5465,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5503,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5513,14 +5518,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45279</v>
+        <v>45475</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5533,7 +5538,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5576,7 +5581,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5590,10 +5595,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45279</v>
+        <v>45629</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5606,7 +5611,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5649,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5663,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44539</v>
+        <v>45629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5679,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5722,7 +5727,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5736,10 +5741,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45450</v>
+        <v>44895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5752,7 +5757,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5795,7 +5800,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5809,10 +5814,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45713</v>
+        <v>45146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5825,7 +5830,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5882,10 +5887,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45146</v>
+        <v>44771</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5898,7 +5903,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45685</v>
+        <v>44539</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5971,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6014,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6028,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44934</v>
+        <v>45685</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6044,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6087,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6097,14 +6102,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46091</v>
+        <v>45740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6117,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.9</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6174,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45898</v>
+        <v>45142</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6190,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6233,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6247,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46097</v>
+        <v>45638</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6263,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6306,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6316,14 +6321,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45899</v>
+        <v>45728</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6336,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6379,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6393,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44988</v>
+        <v>45575</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6408,8 +6413,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6452,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6466,10 +6476,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44862</v>
+        <v>44823</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6482,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6525,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6539,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45908</v>
+        <v>45899</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6555,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6598,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6612,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44616</v>
+        <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6628,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6671,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6685,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45701</v>
+        <v>45825</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6701,7 +6711,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6744,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6758,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45260</v>
+        <v>45176</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6774,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6817,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6831,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46113</v>
+        <v>45327</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6846,13 +6856,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6895,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44895</v>
+        <v>45832</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45055</v>
+        <v>45908</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6998,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7041,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7055,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45688</v>
+        <v>45230</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7070,13 +7075,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45358</v>
+        <v>45834</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>12.2</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45728</v>
+        <v>45786</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45595</v>
+        <v>45841</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 33664-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45561</v>
+        <v>45841</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45142</v>
+        <v>44895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50712-2021</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44460</v>
+        <v>45687</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>7.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50713-2021</t>
+          <t>A 33910-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44460</v>
+        <v>45842</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7640,14 +7640,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45299</v>
+        <v>44867</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45943</v>
+        <v>45757</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7732,13 +7732,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7781,7 +7776,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7795,10 +7790,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44900</v>
+        <v>45667</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7811,7 +7806,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7854,7 +7849,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45947</v>
+        <v>45576</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7884,7 +7879,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7927,7 +7922,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7941,10 +7936,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45947</v>
+        <v>46038</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7957,7 +7952,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8000,7 +7995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8014,10 +8009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45947</v>
+        <v>45701</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8030,7 +8025,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8073,7 +8068,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8087,10 +8082,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46136</v>
+        <v>45090</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8146,7 +8141,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8160,10 +8155,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45217</v>
+        <v>45265</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8176,7 +8171,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8219,7 +8214,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45569</v>
+        <v>45870</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8248,13 +8243,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8297,7 +8287,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8307,14 +8297,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44461</v>
+        <v>45870</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8327,7 +8317,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8370,7 +8360,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8384,10 +8374,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44461</v>
+        <v>45943</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8399,8 +8389,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8443,7 +8438,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8457,10 +8452,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45940</v>
+        <v>46048</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8472,8 +8467,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8516,7 +8516,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45434</v>
+        <v>45947</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44935</v>
+        <v>45947</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8672,14 +8672,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45960</v>
+        <v>45271</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>19.8</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8735,7 +8735,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8749,10 +8749,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45960</v>
+        <v>45947</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45308</v>
+        <v>45359</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8891,14 +8891,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45348</v>
+        <v>45279</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45960</v>
+        <v>45279</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44700</v>
+        <v>45960</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44893</v>
+        <v>45960</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>19.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9173,7 +9173,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9187,10 +9187,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46129</v>
+        <v>45348</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45622</v>
+        <v>45960</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9319,7 +9319,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9333,10 +9333,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44934</v>
+        <v>45971</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9392,7 +9392,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9406,10 +9406,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45643</v>
+        <v>44935</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9465,7 +9465,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45601</v>
+        <v>44934</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9538,7 +9538,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45971</v>
+        <v>46069</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9611,7 +9611,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44935</v>
+        <v>45979</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9684,7 +9684,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9698,10 +9698,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44973</v>
+        <v>45677</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9757,7 +9757,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45142</v>
+        <v>46073</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45116</v>
+        <v>46073</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45116</v>
+        <v>46073</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45645</v>
+        <v>46073</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10049,7 +10049,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44539</v>
+        <v>46073</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10122,7 +10122,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45777</v>
+        <v>44616</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45979</v>
+        <v>45637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44551</v>
+        <v>45098</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10341,7 +10341,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10355,10 +10355,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44979</v>
+        <v>44934</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10414,7 +10414,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10424,14 +10424,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45146</v>
+        <v>45196</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10487,7 +10487,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45569</v>
+        <v>45595</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10516,13 +10516,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10565,7 +10560,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10579,10 +10574,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45575</v>
+        <v>45993</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10594,13 +10589,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>19.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10643,7 +10633,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10653,14 +10643,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44771</v>
+        <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10673,7 +10663,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10716,7 +10706,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10730,10 +10720,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44642</v>
+        <v>45142</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10746,7 +10736,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10806,7 +10796,7 @@
         <v>45994</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10862,7 +10852,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10876,10 +10866,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45993</v>
+        <v>45243</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10892,7 +10882,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>19.6</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10935,7 +10925,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10949,10 +10939,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44601</v>
+        <v>45478</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10965,7 +10955,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11008,7 +10998,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11022,10 +11012,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44816</v>
+        <v>45265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11038,7 +11028,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11081,7 +11071,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11095,10 +11085,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45715</v>
+        <v>46091</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11110,13 +11100,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>10.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11159,7 +11144,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 31967-2024</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11173,10 +11158,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45510</v>
+        <v>44979</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11189,7 +11174,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11232,7 +11217,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11246,10 +11231,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45637</v>
+        <v>45359</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11262,7 +11247,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11305,7 +11290,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11319,10 +11304,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45359</v>
+        <v>45358</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11335,7 +11320,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11378,7 +11363,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11392,10 +11377,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45358</v>
+        <v>45840</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11408,7 +11393,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11451,7 +11436,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11465,10 +11450,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45687</v>
+        <v>46020</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11481,7 +11466,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11524,7 +11509,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11538,10 +11523,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45967</v>
+        <v>46097</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11554,7 +11539,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11597,7 +11582,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11611,10 +11596,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45202</v>
+        <v>45561</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11627,7 +11612,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11670,7 +11655,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11684,10 +11669,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44823</v>
+        <v>45246</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11700,7 +11685,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11743,7 +11728,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 50709-2021</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11757,10 +11742,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44579</v>
+        <v>44460</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11773,7 +11758,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11816,7 +11801,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 50712-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11830,10 +11815,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45898</v>
+        <v>44460</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11846,7 +11831,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11889,7 +11874,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11903,10 +11888,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45377</v>
+        <v>46113</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11918,8 +11903,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11962,7 +11952,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11976,10 +11966,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46157</v>
+        <v>45217</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12035,7 +12025,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12049,10 +12039,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45840</v>
+        <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12065,7 +12055,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12108,7 +12098,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12122,10 +12112,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46020</v>
+        <v>44685</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12138,7 +12128,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12181,7 +12171,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12195,10 +12185,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45230</v>
+        <v>44685</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12211,7 +12201,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12254,7 +12244,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12268,10 +12258,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45176</v>
+        <v>45221</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12284,7 +12274,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12327,7 +12317,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12341,10 +12331,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46038</v>
+        <v>45622</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12357,7 +12347,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12400,7 +12390,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12414,10 +12404,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45005</v>
+        <v>45397</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12430,7 +12420,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12473,7 +12463,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12487,10 +12477,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45253</v>
+        <v>44895</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12503,7 +12493,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12546,7 +12536,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12560,10 +12550,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45246</v>
+        <v>44895</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12576,7 +12566,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12619,7 +12609,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12633,10 +12623,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45221</v>
+        <v>45940</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12649,7 +12639,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12692,7 +12682,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12706,10 +12696,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46171</v>
+        <v>46136</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12765,7 +12755,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12779,10 +12769,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45944</v>
+        <v>44461</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12795,7 +12785,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12838,7 +12828,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12852,10 +12842,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45098</v>
+        <v>44565</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12868,7 +12858,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12911,7 +12901,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12921,14 +12911,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44685</v>
+        <v>45299</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12984,7 +12974,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12998,10 +12988,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44685</v>
+        <v>45777</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13014,7 +13004,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13057,7 +13047,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13071,10 +13061,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44900</v>
+        <v>45629</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13087,7 +13077,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13130,7 +13120,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13144,10 +13134,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45090</v>
+        <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13159,8 +13149,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13203,7 +13198,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13217,10 +13212,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45541</v>
+        <v>44461</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13233,7 +13228,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13276,7 +13271,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13290,10 +13285,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45435</v>
+        <v>44862</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13306,7 +13301,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13349,7 +13344,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13363,10 +13358,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46048</v>
+        <v>45116</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13378,13 +13373,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13427,7 +13417,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13441,10 +13431,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46178</v>
+        <v>45116</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13457,7 +13447,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13500,7 +13490,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13510,14 +13500,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45740</v>
+        <v>46129</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13530,7 +13520,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13573,7 +13563,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13587,10 +13577,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44875</v>
+        <v>45142</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13603,7 +13593,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13646,7 +13636,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13660,10 +13650,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46069</v>
+        <v>44988</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13676,7 +13666,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13719,7 +13709,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13733,10 +13723,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45142</v>
+        <v>45274</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13749,7 +13739,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13792,7 +13782,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13806,10 +13796,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44909</v>
+        <v>45629</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13822,7 +13812,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13865,7 +13855,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13879,10 +13869,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44550</v>
+        <v>44837</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13895,7 +13885,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13938,7 +13928,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13952,10 +13942,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46073</v>
+        <v>45267</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13968,7 +13958,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14011,7 +14001,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 50713-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14025,10 +14015,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46073</v>
+        <v>44460</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14041,7 +14031,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14084,7 +14074,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14098,10 +14088,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46073</v>
+        <v>45967</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14114,7 +14104,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14157,7 +14147,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14171,10 +14161,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46073</v>
+        <v>46157</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14187,7 +14177,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14230,7 +14220,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14244,10 +14234,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46073</v>
+        <v>45377</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14260,7 +14250,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14303,7 +14293,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14317,10 +14307,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45576</v>
+        <v>45898</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14333,7 +14323,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>8.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14376,7 +14366,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14390,10 +14380,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45265</v>
+        <v>45677</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14406,7 +14396,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14449,7 +14439,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14463,10 +14453,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14478,8 +14468,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14522,7 +14517,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14536,10 +14531,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46195</v>
+        <v>45541</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14552,7 +14547,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14595,7 +14590,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14609,10 +14604,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46195</v>
+        <v>44579</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14625,7 +14620,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14663,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14682,10 +14677,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45448</v>
+        <v>45601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14693,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14736,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14750,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46197</v>
+        <v>45202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14766,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14809,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14823,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45338</v>
+        <v>45266</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14843,13 +14838,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14892,7 +14882,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14906,10 +14896,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46196</v>
+        <v>46171</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14922,7 +14912,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14965,7 +14955,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14979,10 +14969,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45243</v>
+        <v>45944</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14995,7 +14985,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15038,7 +15028,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15052,10 +15042,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46198</v>
+        <v>45005</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15068,7 +15058,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15111,7 +15101,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15125,10 +15115,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45435</v>
+        <v>46178</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15184,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15198,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45358</v>
+        <v>45338</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15213,8 +15203,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15257,7 +15252,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15271,10 +15266,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45344</v>
+        <v>45434</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15287,7 +15282,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15330,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15344,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45478</v>
+        <v>44900</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15360,7 +15355,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15403,7 +15398,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15417,10 +15412,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45180</v>
+        <v>45142</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15433,7 +15428,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15476,7 +15471,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15486,14 +15481,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44631</v>
+        <v>44858</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15506,7 +15501,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15549,7 +15544,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15563,10 +15558,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45677</v>
+        <v>45160</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15579,7 +15574,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15622,7 +15617,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15632,14 +15627,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44644</v>
+        <v>45435</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15652,7 +15647,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15712,7 +15707,7 @@
         <v>45435</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15768,7 +15763,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15782,10 +15777,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45621</v>
+        <v>45320</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15798,7 +15793,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15841,7 +15836,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15855,10 +15850,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45160</v>
+        <v>45218</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15871,7 +15866,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15914,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15928,10 +15923,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45196</v>
+        <v>45344</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15944,7 +15939,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,7 +15982,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16001,10 +15996,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45628</v>
+        <v>44601</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16017,7 +16012,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16060,7 +16055,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16069,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45358</v>
+        <v>45253</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16085,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16133,7 +16128,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16147,10 +16142,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44565</v>
+        <v>45569</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16162,8 +16157,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16206,7 +16206,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16216,14 +16216,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45218</v>
+        <v>45146</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16279,7 +16279,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46209</v>
+        <v>46196</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16352,7 +16352,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45677</v>
+        <v>45728</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16425,7 +16425,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45910</v>
+        <v>46195</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16498,7 +16498,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45266</v>
+        <v>46195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16585,10 +16585,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45635</v>
+        <v>46198</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16644,7 +16644,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16658,10 +16658,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45629</v>
+        <v>44642</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16717,7 +16717,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45226</v>
+        <v>44615</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16790,7 +16790,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16804,10 +16804,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46212</v>
+        <v>46197</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45387</v>
+        <v>45450</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16950,10 +16950,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45629</v>
+        <v>45253</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17009,7 +17009,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17023,10 +17023,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46045</v>
+        <v>45308</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17096,10 +17096,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44637</v>
+        <v>44893</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17155,7 +17155,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17169,10 +17169,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45232</v>
+        <v>44637</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17228,7 +17228,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17242,10 +17242,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45728</v>
+        <v>44539</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45757</v>
+        <v>45116</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17374,7 +17374,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17388,10 +17388,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45554</v>
+        <v>45910</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17403,13 +17403,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17452,7 +17447,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17466,10 +17461,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45569</v>
+        <v>46209</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17481,13 +17476,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17530,7 +17520,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17544,10 +17534,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46220</v>
+        <v>44812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17560,7 +17550,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17603,7 +17593,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17617,10 +17607,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46265</v>
+        <v>44816</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17633,7 +17623,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17676,7 +17666,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17690,10 +17680,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46220</v>
+        <v>46212</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17706,7 +17696,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17749,7 +17739,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17763,10 +17753,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45719</v>
+        <v>45237</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17778,13 +17768,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17827,7 +17812,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17841,10 +17826,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46220</v>
+        <v>46045</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17857,7 +17842,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17900,7 +17885,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17914,10 +17899,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44463</v>
+        <v>44875</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17930,7 +17915,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17973,7 +17958,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17987,10 +17972,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44812</v>
+        <v>44909</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18003,7 +17988,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18046,7 +18031,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18060,10 +18045,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46227</v>
+        <v>45701</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18076,7 +18061,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18119,7 +18104,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18133,10 +18118,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44655</v>
+        <v>44900</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18149,7 +18134,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18192,7 +18177,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18206,10 +18191,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44600</v>
+        <v>45226</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18222,7 +18207,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18265,7 +18250,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18275,14 +18260,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44837</v>
+        <v>44644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18295,7 +18280,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18338,7 +18323,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18352,10 +18337,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45253</v>
+        <v>45265</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18368,7 +18353,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18411,7 +18396,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18425,10 +18410,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45630</v>
+        <v>46265</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18484,7 +18469,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18498,10 +18483,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45265</v>
+        <v>45180</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18557,7 +18542,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18571,10 +18556,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45386</v>
+        <v>46220</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18587,7 +18572,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18630,7 +18615,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18644,10 +18629,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45665</v>
+        <v>46220</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18660,7 +18645,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.2</v>
+        <v>15.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -18703,7 +18688,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18717,10 +18702,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45387</v>
+        <v>46220</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18733,7 +18718,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18776,7 +18761,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18786,14 +18771,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45365</v>
+        <v>45645</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18806,7 +18791,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18849,7 +18834,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 52237-2021</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18863,10 +18848,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45713</v>
+        <v>44463</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18879,7 +18864,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18922,7 +18907,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18936,10 +18921,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45792</v>
+        <v>45358</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18952,7 +18937,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18995,7 +18980,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19009,10 +18994,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45594</v>
+        <v>45260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19025,7 +19010,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19068,7 +19053,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19082,10 +19067,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45792</v>
+        <v>45715</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19097,8 +19082,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19141,7 +19131,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19155,10 +19145,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45685</v>
+        <v>45043</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19171,7 +19161,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19214,7 +19204,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19228,10 +19218,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45629</v>
+        <v>44600</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19244,7 +19234,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19287,7 +19277,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19301,10 +19291,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45629</v>
+        <v>45719</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19316,8 +19306,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19360,7 +19355,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19374,10 +19369,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45475</v>
+        <v>45621</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19390,7 +19385,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19433,7 +19428,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19447,10 +19442,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45604</v>
+        <v>46227</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19463,7 +19458,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19506,7 +19501,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19520,10 +19515,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45475</v>
+        <v>45569</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19535,8 +19530,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19579,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19593,10 +19593,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45638</v>
+        <v>45387</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19662,14 +19662,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45728</v>
+        <v>45055</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45825</v>
+        <v>45728</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19812,10 +19812,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45832</v>
+        <v>44700</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45834</v>
+        <v>45630</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19954,14 +19954,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45786</v>
+        <v>45665</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20017,7 +20017,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20031,10 +20031,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45841</v>
+        <v>45387</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20090,7 +20090,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 33664-2025</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20100,14 +20100,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45841</v>
+        <v>45365</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20163,7 +20163,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 33910-2025</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45842</v>
+        <v>45713</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20236,7 +20236,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20250,10 +20250,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45667</v>
+        <v>45792</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20309,7 +20309,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45701</v>
+        <v>45792</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20396,10 +20396,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45870</v>
+        <v>45685</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20455,7 +20455,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45870</v>
+        <v>45594</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20528,7 +20528,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 1352-2022</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20542,10 +20542,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44628</v>
+        <v>45323</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20557,13 +20557,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I271" t="n">
-        <v>47.1</v>
+        <v>3.8</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -20606,7 +20601,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 1352-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20616,14 +20611,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44601</v>
+        <v>44628</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20637,11 +20632,11 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.4</v>
+        <v>47.1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -20684,7 +20679,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20701,7 +20696,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20714,7 +20709,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>3.8</v>
+        <v>38.9</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -20757,7 +20752,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 510-2025</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20767,14 +20762,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45706</v>
+        <v>44601</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -20786,8 +20781,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I274" t="n">
-        <v>32.6</v>
+        <v>1.4</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -20830,7 +20830,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -20840,14 +20840,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45323</v>
+        <v>45368</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>38.9</v>
+        <v>2.9</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -20903,7 +20903,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -20913,14 +20913,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45368</v>
+        <v>45323</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -20976,7 +20976,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -20993,7 +20993,7 @@
         <v>45323</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>7.9</v>
+        <v>16.3</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 280-2024</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21063,10 +21063,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45323</v>
+        <v>45706</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>16.3</v>
+        <v>32.6</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54293-2023</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45232</v>
+        <v>45624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -647,578 +647,578 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 54293-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45232</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 33920-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A 11270-2025</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>45726</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Härfågel</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 36627-2025</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45870</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.6</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 36627-2025 artfynd.xlsx", "A 36627-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 36627-2025 karta.png", "A 36627-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 36627-2025 georefererad karta.tif", "A 36627-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 36627-2025 FSC-klagomål.docx", "A 36627-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 36627-2025 FSC-klagomål mail.docx", "A 36627-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 36627-2025 tillsynsbegäran.docx", "A 36627-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 36627-2025 tillsynsbegäran mail.docx", "A 36627-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 60881-2025</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>6.6</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rostfläck</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 60881-2025 artfynd.xlsx", "A 60881-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 60881-2025 karta.png", "A 60881-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 60881-2025 georefererad karta.tif", "A 60881-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 60881-2025 FSC-klagomål.docx", "A 60881-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 60881-2025 FSC-klagomål mail.docx", "A 60881-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 60881-2025 tillsynsbegäran.docx", "A 60881-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 60881-2025 tillsynsbegäran mail.docx", "A 60881-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 33920-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56164-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45624</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44627</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44851</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 62992-2021</t>
+          <t>A 54964-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44504</v>
+        <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 54964-2021</t>
+          <t>A 62992-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44474</v>
+        <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44460</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44460</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44858</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45554</v>
+        <v>45267</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3775,13 +3775,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3824,7 +3819,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,10 +3833,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45358</v>
+        <v>45338</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3853,8 +3848,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>12.2</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45435</v>
+        <v>44867</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45628</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31967-2024</t>
+          <t>A 50709-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45510</v>
+        <v>44460</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.1</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45643</v>
+        <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44973</v>
+        <v>45359</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45635</v>
+        <v>44858</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45386</v>
+        <v>44895</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45264</v>
+        <v>45327</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45253</v>
+        <v>45397</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45253</v>
+        <v>45116</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45359</v>
+        <v>45435</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45358</v>
+        <v>45279</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45569</v>
+        <v>45279</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4802,13 +4802,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4851,7 +4846,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4865,10 +4860,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45232</v>
+        <v>44934</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4881,7 +4876,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44935</v>
+        <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44655</v>
+        <v>45450</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5027,7 +5022,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44550</v>
+        <v>44988</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45448</v>
+        <v>45260</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5230,10 +5225,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45435</v>
+        <v>44616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5246,7 +5241,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5289,7 +5284,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5303,10 +5298,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45713</v>
+        <v>45055</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5319,7 +5314,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5362,7 +5357,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5376,10 +5371,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45475</v>
+        <v>45688</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5391,8 +5386,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45604</v>
+        <v>45358</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>12.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45475</v>
+        <v>44539</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5581,7 +5581,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45629</v>
+        <v>46069</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45629</v>
+        <v>45825</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5727,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44895</v>
+        <v>45728</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5800,7 +5800,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45146</v>
+        <v>45595</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44771</v>
+        <v>45832</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44539</v>
+        <v>46073</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45685</v>
+        <v>46073</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45740</v>
+        <v>46073</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45142</v>
+        <v>46073</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45638</v>
+        <v>46073</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45728</v>
+        <v>45834</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45575</v>
+        <v>45217</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6413,13 +6413,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6472,14 +6467,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44823</v>
+        <v>45786</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6492,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6549,10 +6544,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45899</v>
+        <v>45841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 33664-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45898</v>
+        <v>45841</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6633,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45825</v>
+        <v>45569</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6710,8 +6705,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45176</v>
+        <v>45713</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45327</v>
+        <v>46091</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.6</v>
+        <v>10.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45832</v>
+        <v>45146</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45908</v>
+        <v>45685</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 33910-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45230</v>
+        <v>45842</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45834</v>
+        <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45786</v>
+        <v>46097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45841</v>
+        <v>45308</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33664-2025</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45841</v>
+        <v>45348</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.7</v>
+        <v>8.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44895</v>
+        <v>44700</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45687</v>
+        <v>44893</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33910-2025</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45842</v>
+        <v>45667</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44867</v>
+        <v>45622</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45757</v>
+        <v>44934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45667</v>
+        <v>45643</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45576</v>
+        <v>45601</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46038</v>
+        <v>45701</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45701</v>
+        <v>45870</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8068,7 +8068,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8078,14 +8078,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45090</v>
+        <v>45870</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45265</v>
+        <v>46113</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8170,8 +8170,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8214,7 +8219,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45870</v>
+        <v>44973</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8244,7 +8249,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8287,7 +8292,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8297,14 +8302,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45870</v>
+        <v>45142</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8317,7 +8322,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8360,7 +8365,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8374,10 +8379,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45943</v>
+        <v>45116</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8389,13 +8394,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8438,7 +8438,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46048</v>
+        <v>45116</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8467,13 +8467,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8516,7 +8511,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45947</v>
+        <v>45645</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8546,7 +8541,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8589,7 +8584,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8603,10 +8598,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45947</v>
+        <v>45569</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8618,8 +8613,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8672,14 +8672,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45271</v>
+        <v>45575</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8691,8 +8691,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8735,7 +8740,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8749,10 +8754,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45947</v>
+        <v>44771</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8765,7 +8770,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8808,7 +8813,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8822,10 +8827,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45359</v>
+        <v>44642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8838,7 +8843,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8881,7 +8886,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8895,10 +8900,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45279</v>
+        <v>45271</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8911,7 +8916,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8954,7 +8959,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8968,10 +8973,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45279</v>
+        <v>45898</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8984,7 +8989,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9027,7 +9032,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9041,10 +9046,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45960</v>
+        <v>45899</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9057,7 +9062,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9100,7 +9105,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9110,14 +9115,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45960</v>
+        <v>45299</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9130,7 +9135,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>19.8</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9173,7 +9178,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9187,10 +9192,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45348</v>
+        <v>44601</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9203,7 +9208,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9246,7 +9251,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9260,10 +9265,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45960</v>
+        <v>45908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9276,7 +9281,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9319,7 +9324,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9333,10 +9338,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45971</v>
+        <v>46136</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9349,7 +9354,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9392,7 +9397,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9406,10 +9411,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44935</v>
+        <v>44816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9422,7 +9427,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9465,7 +9470,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9479,10 +9484,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44934</v>
+        <v>44461</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9495,7 +9500,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9538,7 +9543,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9552,10 +9557,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46069</v>
+        <v>44461</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9568,7 +9573,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9611,7 +9616,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9625,10 +9630,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45979</v>
+        <v>45715</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9640,8 +9645,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9684,7 +9694,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9698,10 +9708,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45677</v>
+        <v>45510</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9714,7 +9724,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.2</v>
+        <v>9.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9757,7 +9767,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9771,10 +9781,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46073</v>
+        <v>45637</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9787,7 +9797,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9830,7 +9840,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9844,10 +9854,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46073</v>
+        <v>45940</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9860,7 +9870,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9903,7 +9913,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9917,10 +9927,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46073</v>
+        <v>45687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9933,7 +9943,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9976,7 +9986,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9990,10 +10000,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46073</v>
+        <v>45202</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10006,7 +10016,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10049,7 +10059,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10063,10 +10073,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46073</v>
+        <v>44823</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10079,7 +10089,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10122,7 +10132,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10136,10 +10146,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44616</v>
+        <v>44579</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10152,7 +10162,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10195,7 +10205,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10209,10 +10219,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45637</v>
+        <v>46129</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10225,7 +10235,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10268,7 +10278,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10282,10 +10292,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45098</v>
+        <v>45176</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10298,7 +10308,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10341,7 +10351,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10355,10 +10365,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44934</v>
+        <v>45777</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10371,7 +10381,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10414,7 +10424,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10428,10 +10438,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45196</v>
+        <v>45253</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10444,7 +10454,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10487,7 +10497,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10501,10 +10511,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45595</v>
+        <v>45098</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10517,7 +10527,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10560,7 +10570,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10574,10 +10584,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45993</v>
+        <v>44685</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10590,7 +10600,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>19.6</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10633,7 +10643,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10643,14 +10653,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44631</v>
+        <v>44685</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10706,7 +10716,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10720,10 +10730,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45142</v>
+        <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10736,7 +10746,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10779,7 +10789,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10793,10 +10803,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45994</v>
+        <v>45541</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10809,7 +10819,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10852,7 +10862,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10862,14 +10872,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45243</v>
+        <v>45740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10882,7 +10892,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10925,7 +10935,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10939,10 +10949,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45478</v>
+        <v>44875</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10955,7 +10965,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10998,7 +11008,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11012,10 +11022,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45265</v>
+        <v>45967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11028,7 +11038,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11071,7 +11081,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11085,10 +11095,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46091</v>
+        <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11101,7 +11111,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11144,7 +11154,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11158,10 +11168,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44979</v>
+        <v>45377</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11174,7 +11184,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11217,7 +11227,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11231,10 +11241,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45359</v>
+        <v>46157</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11247,7 +11257,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11290,7 +11300,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11304,10 +11314,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45358</v>
+        <v>45142</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11320,7 +11330,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11363,7 +11373,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11377,10 +11387,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45840</v>
+        <v>44909</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11393,7 +11403,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11436,7 +11446,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11450,10 +11460,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46020</v>
+        <v>44550</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11466,7 +11476,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11509,7 +11519,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11523,10 +11533,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46097</v>
+        <v>45576</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11539,7 +11549,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11582,7 +11592,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11596,10 +11606,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45561</v>
+        <v>45265</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11612,7 +11622,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11655,7 +11665,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11669,10 +11679,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45246</v>
+        <v>45943</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11684,8 +11694,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11728,7 +11743,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 50709-2021</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11742,10 +11757,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44460</v>
+        <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11757,8 +11772,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11801,7 +11821,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50712-2021</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11815,10 +11835,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44460</v>
+        <v>46171</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11831,7 +11851,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11874,7 +11894,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11888,10 +11908,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46113</v>
+        <v>45944</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11903,13 +11923,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11952,7 +11967,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11966,10 +11981,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45217</v>
+        <v>45243</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11982,7 +11997,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12025,7 +12040,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12039,10 +12054,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44551</v>
+        <v>45947</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12055,7 +12070,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12098,7 +12113,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12112,10 +12127,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44685</v>
+        <v>45344</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12128,7 +12143,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12171,7 +12186,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12185,10 +12200,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44685</v>
+        <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12201,7 +12216,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12244,7 +12259,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12258,10 +12273,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45221</v>
+        <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12274,7 +12289,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12317,7 +12332,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12331,10 +12346,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45622</v>
+        <v>45478</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12347,7 +12362,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12390,7 +12405,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12404,10 +12419,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45397</v>
+        <v>46178</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12420,7 +12435,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12478,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12492,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44895</v>
+        <v>45180</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12508,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12536,7 +12551,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12546,14 +12561,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44895</v>
+        <v>44644</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12609,7 +12624,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12619,14 +12634,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45940</v>
+        <v>45435</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12639,7 +12654,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12682,7 +12697,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12696,10 +12711,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46136</v>
+        <v>45621</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12712,7 +12727,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12755,7 +12770,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12769,10 +12784,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44461</v>
+        <v>45960</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12785,7 +12800,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.7</v>
+        <v>19.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12828,7 +12843,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12842,10 +12857,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44565</v>
+        <v>45960</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12858,7 +12873,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12901,7 +12916,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12911,14 +12926,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45299</v>
+        <v>45160</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12931,7 +12946,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12974,7 +12989,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12988,10 +13003,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45777</v>
+        <v>45196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13004,7 +13019,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13047,7 +13062,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13061,10 +13076,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45629</v>
+        <v>45358</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13077,7 +13092,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13120,7 +13135,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13134,10 +13149,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45338</v>
+        <v>44565</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13149,13 +13164,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13198,7 +13208,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13212,10 +13222,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44461</v>
+        <v>45218</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13228,7 +13238,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13271,7 +13281,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13285,10 +13295,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44862</v>
+        <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13344,7 +13354,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13358,10 +13368,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45116</v>
+        <v>46195</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13374,7 +13384,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13417,7 +13427,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13431,10 +13441,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45116</v>
+        <v>46195</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13447,7 +13457,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13490,7 +13500,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13504,10 +13514,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46129</v>
+        <v>46197</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13520,7 +13530,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13563,7 +13573,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13577,10 +13587,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45142</v>
+        <v>46196</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13593,7 +13603,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13636,7 +13646,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13650,10 +13660,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44988</v>
+        <v>45971</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13666,7 +13676,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13709,7 +13719,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13723,10 +13733,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45274</v>
+        <v>46198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13739,7 +13749,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13782,7 +13792,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13799,7 +13809,7 @@
         <v>45629</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13812,7 +13822,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13855,7 +13865,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13869,10 +13879,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44837</v>
+        <v>45226</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13885,7 +13895,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13928,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13942,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45267</v>
+        <v>45979</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13958,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14001,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 50713-2021</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14015,10 +14025,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44460</v>
+        <v>45629</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14031,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14074,7 +14084,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14088,10 +14098,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45967</v>
+        <v>44637</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14104,7 +14114,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14147,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14161,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46157</v>
+        <v>45232</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14177,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14220,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14234,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45377</v>
+        <v>45728</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14250,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14293,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14307,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45898</v>
+        <v>45757</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14323,7 +14333,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14366,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14380,10 +14390,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45677</v>
+        <v>45142</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14396,7 +14406,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14439,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14453,10 +14463,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45688</v>
+        <v>45274</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14468,13 +14478,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14517,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14531,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45541</v>
+        <v>46209</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14547,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14590,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14604,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44579</v>
+        <v>44615</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14620,7 +14625,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14663,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14677,10 +14682,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45601</v>
+        <v>45265</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14693,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14736,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14750,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45202</v>
+        <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14766,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14809,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14823,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45266</v>
+        <v>45994</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14839,7 +14844,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14882,7 +14887,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14896,10 +14901,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46171</v>
+        <v>45320</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14912,7 +14917,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14955,7 +14960,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14969,10 +14974,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45944</v>
+        <v>46212</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14985,7 +14990,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15028,7 +15033,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15042,10 +15047,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45005</v>
+        <v>45993</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15058,7 +15063,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>19.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15101,7 +15106,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15115,10 +15120,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46178</v>
+        <v>45264</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15131,7 +15136,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15174,7 +15179,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15193,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45338</v>
+        <v>46045</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15203,13 +15208,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15252,7 +15252,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15266,10 +15266,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45434</v>
+        <v>44895</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15339,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44900</v>
+        <v>44895</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15398,7 +15398,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15412,10 +15412,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45142</v>
+        <v>45253</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15485,10 +15485,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44858</v>
+        <v>46220</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15544,7 +15544,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45160</v>
+        <v>46265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45435</v>
+        <v>46220</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15690,7 +15690,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15700,14 +15700,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45435</v>
+        <v>45043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15763,7 +15763,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45320</v>
+        <v>46220</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15836,7 +15836,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15850,10 +15850,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45218</v>
+        <v>46227</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15923,10 +15923,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45344</v>
+        <v>45701</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15982,7 +15982,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15996,10 +15996,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44601</v>
+        <v>44895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16055,7 +16055,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16069,10 +16069,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45253</v>
+        <v>45561</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16128,7 +16128,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16142,10 +16142,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45569</v>
+        <v>45840</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16157,13 +16157,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16206,7 +16201,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16216,14 +16211,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45146</v>
+        <v>45142</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16236,7 +16231,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16279,7 +16274,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16293,10 +16288,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46196</v>
+        <v>46020</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16309,7 +16304,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16352,7 +16347,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 50712-2021</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16366,10 +16361,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45728</v>
+        <v>44460</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16382,7 +16377,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16425,7 +16420,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 50713-2021</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16439,10 +16434,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46195</v>
+        <v>44460</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16455,7 +16450,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16498,7 +16493,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16512,10 +16507,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46195</v>
+        <v>44900</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16528,7 +16523,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16571,7 +16566,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16585,10 +16580,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46198</v>
+        <v>44935</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16601,7 +16596,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16644,7 +16639,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16658,10 +16653,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44642</v>
+        <v>44935</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16674,7 +16669,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16717,7 +16712,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16731,10 +16726,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44615</v>
+        <v>44539</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16747,7 +16742,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16790,7 +16785,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16804,10 +16799,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46197</v>
+        <v>44551</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16820,7 +16815,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16863,7 +16858,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16877,10 +16872,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45450</v>
+        <v>44979</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16893,7 +16888,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16936,7 +16931,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16946,14 +16941,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45253</v>
+        <v>45146</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16966,7 +16961,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17009,7 +17004,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17023,10 +17018,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45308</v>
+        <v>45359</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17039,7 +17034,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17082,7 +17077,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17096,10 +17091,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44893</v>
+        <v>45358</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17112,7 +17107,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17155,7 +17150,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17169,10 +17164,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44637</v>
+        <v>45230</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17185,7 +17180,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17228,7 +17223,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17242,10 +17237,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44539</v>
+        <v>46038</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17258,7 +17253,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17301,7 +17296,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17315,10 +17310,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45116</v>
+        <v>45005</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17331,7 +17326,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17374,7 +17369,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17388,10 +17383,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45910</v>
+        <v>45246</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17404,7 +17399,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17447,7 +17442,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17461,10 +17456,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46209</v>
+        <v>45221</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17477,7 +17472,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17520,7 +17515,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17534,10 +17529,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44812</v>
+        <v>45090</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17550,7 +17545,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17593,7 +17588,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17607,10 +17602,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44816</v>
+        <v>45435</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17623,7 +17618,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17666,7 +17661,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17680,10 +17675,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46212</v>
+        <v>45237</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17696,7 +17691,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17739,7 +17734,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17753,10 +17748,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45237</v>
+        <v>46048</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17768,8 +17763,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17812,7 +17812,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17826,10 +17826,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46045</v>
+        <v>45448</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17899,10 +17899,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44875</v>
+        <v>45435</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>8.4</v>
+        <v>0.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17958,7 +17958,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17972,10 +17972,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44909</v>
+        <v>45358</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18031,7 +18031,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18041,14 +18041,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45701</v>
+        <v>44631</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18118,10 +18118,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44900</v>
+        <v>45677</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18177,7 +18177,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18191,10 +18191,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45226</v>
+        <v>45628</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18250,7 +18250,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18260,14 +18260,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44644</v>
+        <v>45677</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18323,7 +18323,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18337,10 +18337,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18396,7 +18396,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18410,10 +18410,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46265</v>
+        <v>45635</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18483,10 +18483,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45180</v>
+        <v>45387</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18542,7 +18542,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18556,10 +18556,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46220</v>
+        <v>45554</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18571,8 +18571,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18615,7 +18620,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18629,10 +18634,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46220</v>
+        <v>45569</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18644,8 +18649,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>15.5</v>
+        <v>1.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -18688,7 +18698,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18702,10 +18712,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46220</v>
+        <v>45719</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18717,8 +18727,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18761,7 +18776,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 52237-2021</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18775,10 +18790,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45645</v>
+        <v>44463</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18791,7 +18806,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18834,7 +18849,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18848,10 +18863,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44463</v>
+        <v>44812</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18864,7 +18879,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18907,7 +18922,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18921,10 +18936,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45358</v>
+        <v>44655</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18937,7 +18952,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18980,7 +18995,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18994,10 +19009,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45260</v>
+        <v>44600</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19010,7 +19025,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19053,7 +19068,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19067,10 +19082,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45715</v>
+        <v>44837</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19082,13 +19097,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19131,7 +19141,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19145,10 +19155,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45043</v>
+        <v>45253</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19161,7 +19171,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19204,7 +19214,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19218,10 +19228,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44600</v>
+        <v>45630</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19234,7 +19244,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19277,7 +19287,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19291,10 +19301,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45719</v>
+        <v>45265</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19306,13 +19316,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I254" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19355,7 +19360,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19369,10 +19374,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45621</v>
+        <v>45386</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19385,7 +19390,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19428,7 +19433,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19442,10 +19447,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46227</v>
+        <v>45665</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19458,7 +19463,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19501,7 +19506,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19515,10 +19520,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45569</v>
+        <v>45387</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19530,13 +19535,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19579,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19589,14 +19589,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45387</v>
+        <v>45365</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19666,10 +19666,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45055</v>
+        <v>45713</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45728</v>
+        <v>45792</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19812,10 +19812,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44700</v>
+        <v>45594</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45630</v>
+        <v>45792</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45665</v>
+        <v>45685</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20017,7 +20017,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20031,10 +20031,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45387</v>
+        <v>45629</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20100,14 +20100,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45365</v>
+        <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20163,7 +20163,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45713</v>
+        <v>45475</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20236,7 +20236,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20250,10 +20250,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45792</v>
+        <v>45604</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20309,7 +20309,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45792</v>
+        <v>45475</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20382,7 +20382,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20396,10 +20396,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45685</v>
+        <v>45638</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20455,7 +20455,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45594</v>
+        <v>45728</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20528,7 +20528,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>S 1352-2022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20542,10 +20542,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45323</v>
+        <v>44628</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20557,8 +20557,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I271" t="n">
-        <v>3.8</v>
+        <v>47.1</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -20601,7 +20606,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 1352-2022</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20611,14 +20616,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44628</v>
+        <v>44601</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20632,11 +20637,11 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>47.1</v>
+        <v>1.4</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -20679,7 +20684,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20696,7 +20701,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20709,7 +20714,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>38.9</v>
+        <v>3.8</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -20752,7 +20757,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20762,14 +20767,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>44601</v>
+        <v>45706</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -20781,13 +20786,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I274" t="n">
-        <v>1.4</v>
+        <v>32.6</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -20830,7 +20830,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -20840,14 +20840,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45368</v>
+        <v>45323</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>2.9</v>
+        <v>38.9</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -20903,7 +20903,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -20913,14 +20913,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45323</v>
+        <v>45368</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -20976,7 +20976,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 280-2024</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -20993,7 +20993,7 @@
         <v>45323</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>16.3</v>
+        <v>7.9</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 510-2025</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21063,10 +21063,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45706</v>
+        <v>45323</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>32.6</v>
+        <v>16.3</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56164-2024</t>
+          <t>A 54293-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45624</v>
+        <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -647,578 +647,578 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 11270-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45726</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Härfågel</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 36627-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 36627-2025 artfynd.xlsx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 36627-2025 karta.png", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 36627-2025 georefererad karta.tif", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 36627-2025 FSC-klagomål.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 36627-2025 FSC-klagomål mail.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 36627-2025 tillsynsbegäran.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 36627-2025 tillsynsbegäran mail.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60881-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 60881-2025 artfynd.xlsx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 60881-2025 karta.png", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 60881-2025 georefererad karta.tif", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 60881-2025 FSC-klagomål.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 60881-2025 FSC-klagomål mail.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 60881-2025 tillsynsbegäran.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 60881-2025 tillsynsbegäran mail.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 56164-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45624</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Mattlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 54293-2023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45232</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 33920-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 33920-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gulsparv</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 11270-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45726</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Härfågel</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 36627-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45870</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 36627-2025 artfynd.xlsx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 36627-2025 karta.png", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 36627-2025 georefererad karta.tif", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 36627-2025 FSC-klagomål.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 36627-2025 FSC-klagomål mail.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 36627-2025 tillsynsbegäran.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 36627-2025 tillsynsbegäran mail.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 60881-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rostfläck</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 60881-2025 artfynd.xlsx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 60881-2025 karta.png", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 60881-2025 georefererad karta.tif", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 60881-2025 FSC-klagomål.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 60881-2025 FSC-klagomål mail.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 60881-2025 tillsynsbegäran.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 60881-2025 tillsynsbegäran mail.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34906-2022</t>
+          <t>A 9847-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44796</v>
+        <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9847-2022</t>
+          <t>A 34906-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44620</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44627</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50987-2022</t>
+          <t>A 46713-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44867</v>
+        <v>44851</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46713-2022</t>
+          <t>A 50987-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44851</v>
+        <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.7</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44460</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44460</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44858</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45267</v>
+        <v>45554</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3775,8 +3775,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3819,7 +3824,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3833,10 +3838,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45338</v>
+        <v>45358</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3848,13 +3853,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44867</v>
+        <v>45510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>9.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50709-2021</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44460</v>
+        <v>45635</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45253</v>
+        <v>45386</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45359</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44858</v>
+        <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44895</v>
+        <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45327</v>
+        <v>45253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45397</v>
+        <v>45435</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45116</v>
+        <v>45628</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45435</v>
+        <v>45569</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4656,8 +4656,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4700,7 +4705,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4710,14 +4715,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45279</v>
+        <v>45359</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4730,7 +4735,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4773,7 +4778,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45279</v>
+        <v>45358</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4803,7 +4808,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4846,7 +4851,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4860,10 +4865,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44934</v>
+        <v>44935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4876,7 +4881,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4919,7 +4924,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4933,10 +4938,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44862</v>
+        <v>45232</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4949,7 +4954,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4992,7 +4997,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45450</v>
+        <v>44550</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5022,7 +5027,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44988</v>
+        <v>45448</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45260</v>
+        <v>44655</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44616</v>
+        <v>45435</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5241,7 +5246,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5284,7 +5289,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5298,10 +5303,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45055</v>
+        <v>44895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5314,7 +5319,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5357,7 +5362,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45688</v>
+        <v>45142</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5386,13 +5391,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45358</v>
+        <v>44771</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>12.2</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44539</v>
+        <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5581,7 +5581,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46069</v>
+        <v>45176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45825</v>
+        <v>45575</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5683,8 +5683,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5732,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45728</v>
+        <v>45327</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5757,7 +5762,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5800,7 +5805,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5814,10 +5819,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45595</v>
+        <v>45230</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5830,7 +5835,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5878,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5883,14 +5888,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45832</v>
+        <v>45740</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5903,7 +5908,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5951,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5965,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46073</v>
+        <v>44895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5981,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6024,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6038,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46073</v>
+        <v>45687</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6054,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6097,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6111,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46073</v>
+        <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6127,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6170,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6184,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46073</v>
+        <v>45576</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6200,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6243,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6257,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46073</v>
+        <v>45757</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6273,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.1</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45834</v>
+        <v>45090</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6346,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45217</v>
+        <v>45265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6419,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6467,14 +6472,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45786</v>
+        <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6487,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6544,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45841</v>
+        <v>45279</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33664-2025</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45841</v>
+        <v>45348</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6633,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>8.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45569</v>
+        <v>45359</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6705,13 +6710,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45713</v>
+        <v>44935</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46091</v>
+        <v>44934</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>10.9</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6910,14 +6910,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45146</v>
+        <v>45299</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45685</v>
+        <v>45146</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33910-2025</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45842</v>
+        <v>45677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45434</v>
+        <v>45777</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46097</v>
+        <v>44616</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45308</v>
+        <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45348</v>
+        <v>45637</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44700</v>
+        <v>45685</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44893</v>
+        <v>45098</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45667</v>
+        <v>44934</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45622</v>
+        <v>45196</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44934</v>
+        <v>45595</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7786,14 +7786,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45643</v>
+        <v>44631</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45601</v>
+        <v>45142</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45701</v>
+        <v>45243</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7995,7 +7995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45870</v>
+        <v>45899</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8068,7 +8068,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8078,14 +8078,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45870</v>
+        <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46113</v>
+        <v>45713</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8170,13 +8170,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8219,7 +8214,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44973</v>
+        <v>44461</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8249,7 +8244,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8292,7 +8287,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8306,10 +8301,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45142</v>
+        <v>45478</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8322,7 +8317,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8365,7 +8360,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8379,10 +8374,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45116</v>
+        <v>45908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8395,7 +8390,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8438,7 +8433,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8452,10 +8447,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45116</v>
+        <v>45265</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8468,7 +8463,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8511,7 +8506,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8525,10 +8520,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45645</v>
+        <v>46129</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8541,7 +8536,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8584,7 +8579,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8598,10 +8593,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45569</v>
+        <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8613,13 +8608,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8662,7 +8652,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8676,10 +8666,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45575</v>
+        <v>45359</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8691,13 +8681,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8740,7 +8725,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8754,10 +8739,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44771</v>
+        <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8770,7 +8755,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8813,7 +8798,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8827,10 +8812,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44642</v>
+        <v>45561</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8843,7 +8828,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8886,7 +8871,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8896,14 +8881,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45271</v>
+        <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8916,7 +8901,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8959,7 +8944,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 50709-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8973,10 +8958,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45898</v>
+        <v>44460</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8989,7 +8974,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9032,7 +9017,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 50712-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9046,10 +9031,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45899</v>
+        <v>44460</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9062,7 +9047,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9105,7 +9090,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9115,14 +9100,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45299</v>
+        <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9134,8 +9119,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9178,7 +9168,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9192,10 +9182,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44601</v>
+        <v>45217</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9251,7 +9241,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9265,10 +9255,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45908</v>
+        <v>44551</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9281,7 +9271,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9324,7 +9314,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9338,10 +9328,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46136</v>
+        <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9354,7 +9344,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9397,7 +9387,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9411,10 +9401,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44816</v>
+        <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9427,7 +9417,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9470,7 +9460,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9484,10 +9474,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44461</v>
+        <v>45947</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9500,7 +9490,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9543,7 +9533,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9557,10 +9547,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44461</v>
+        <v>45947</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9573,7 +9563,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9616,7 +9606,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9630,10 +9620,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45715</v>
+        <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9645,13 +9635,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9694,7 +9679,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31967-2024</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9708,10 +9693,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45510</v>
+        <v>45221</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9724,7 +9709,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>9.1</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9767,7 +9752,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9781,10 +9766,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45637</v>
+        <v>45622</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9840,7 +9825,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9854,10 +9839,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45940</v>
+        <v>45397</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9870,7 +9855,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9913,7 +9898,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9927,10 +9912,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45687</v>
+        <v>45960</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9943,7 +9928,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9986,7 +9971,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10000,10 +9985,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45202</v>
+        <v>44895</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10016,7 +10001,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10059,7 +10044,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10073,10 +10058,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44823</v>
+        <v>44895</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10089,7 +10074,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10132,7 +10117,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10146,10 +10131,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44579</v>
+        <v>45960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10162,7 +10147,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>19.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10205,7 +10190,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10219,10 +10204,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46129</v>
+        <v>45960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10235,7 +10220,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10278,7 +10263,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10292,10 +10277,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45176</v>
+        <v>45967</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10308,7 +10293,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10351,7 +10336,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10365,10 +10350,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45777</v>
+        <v>45971</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10381,7 +10366,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10424,7 +10409,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10438,10 +10423,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45253</v>
+        <v>44565</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10454,7 +10439,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10497,7 +10482,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10511,10 +10496,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45098</v>
+        <v>45979</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10527,7 +10512,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10570,7 +10555,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10584,10 +10569,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44685</v>
+        <v>45629</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10600,7 +10585,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10643,7 +10628,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10657,10 +10642,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44685</v>
+        <v>45338</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10672,8 +10657,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10716,7 +10706,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10730,10 +10720,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44900</v>
+        <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10746,7 +10736,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10789,7 +10779,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10803,10 +10793,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45541</v>
+        <v>45377</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10819,7 +10809,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10862,7 +10852,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10872,14 +10862,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45740</v>
+        <v>44862</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10892,7 +10882,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10935,7 +10925,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10949,10 +10939,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44875</v>
+        <v>45116</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10965,7 +10955,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11008,7 +10998,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11022,10 +11012,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45967</v>
+        <v>45116</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11038,7 +11028,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11098,7 +11088,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11154,7 +11144,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11168,10 +11158,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45377</v>
+        <v>45993</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11184,7 +11174,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>19.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11227,7 +11217,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11241,10 +11231,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46157</v>
+        <v>45142</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11257,7 +11247,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11300,7 +11290,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11314,10 +11304,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45142</v>
+        <v>44988</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11330,7 +11320,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11373,7 +11363,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11387,10 +11377,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44909</v>
+        <v>45994</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11403,7 +11393,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11446,7 +11436,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11460,10 +11450,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44550</v>
+        <v>45274</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11476,7 +11466,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11519,7 +11509,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11533,10 +11523,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45576</v>
+        <v>45629</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11549,7 +11539,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11592,7 +11582,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11606,10 +11596,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45265</v>
+        <v>44837</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11622,7 +11612,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11665,7 +11655,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11679,10 +11669,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45943</v>
+        <v>45267</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11694,13 +11684,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11743,7 +11728,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11757,10 +11742,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45338</v>
+        <v>45840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11772,13 +11757,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11821,7 +11801,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 50713-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11835,10 +11815,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46171</v>
+        <v>44460</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11851,7 +11831,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11894,7 +11874,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11908,10 +11888,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45944</v>
+        <v>46020</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11924,7 +11904,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11967,7 +11947,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11981,10 +11961,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45243</v>
+        <v>45677</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11997,7 +11977,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12040,7 +12020,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12054,10 +12034,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45947</v>
+        <v>45688</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12069,8 +12049,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12113,7 +12098,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12127,10 +12112,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45344</v>
+        <v>45541</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12143,7 +12128,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12186,7 +12171,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12200,10 +12185,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45947</v>
+        <v>44579</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12216,7 +12201,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12259,7 +12244,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12273,10 +12258,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45947</v>
+        <v>46038</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12289,7 +12274,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12332,7 +12317,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12346,10 +12331,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45478</v>
+        <v>45601</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12362,7 +12347,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12405,7 +12390,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12419,10 +12404,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12435,7 +12420,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12478,7 +12463,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12492,10 +12477,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45180</v>
+        <v>45944</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12508,7 +12493,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12551,7 +12536,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12561,14 +12546,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44644</v>
+        <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12580,8 +12565,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12624,7 +12614,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12634,14 +12624,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45435</v>
+        <v>45202</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12654,7 +12644,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12697,7 +12687,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12711,10 +12701,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45621</v>
+        <v>45266</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12727,7 +12717,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12770,7 +12760,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12784,10 +12774,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45960</v>
+        <v>46178</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12800,7 +12790,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>19.8</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12843,7 +12833,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12857,10 +12847,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45960</v>
+        <v>45005</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12873,7 +12863,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12916,7 +12906,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12930,10 +12920,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45160</v>
+        <v>46069</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12946,7 +12936,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12989,7 +12979,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13003,10 +12993,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45196</v>
+        <v>45338</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13018,8 +13008,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13062,7 +13057,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13076,10 +13071,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45358</v>
+        <v>46073</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13092,7 +13087,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13135,7 +13130,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13149,10 +13144,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44565</v>
+        <v>46073</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13165,7 +13160,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13208,7 +13203,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13222,10 +13217,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45218</v>
+        <v>46073</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13238,7 +13233,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13281,7 +13276,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13295,10 +13290,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45960</v>
+        <v>46073</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13311,7 +13306,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13354,7 +13349,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13368,10 +13363,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46195</v>
+        <v>46073</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13384,7 +13379,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13427,7 +13422,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13441,10 +13436,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46195</v>
+        <v>45434</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13457,7 +13452,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13500,7 +13495,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13514,10 +13509,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46197</v>
+        <v>44900</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13530,7 +13525,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13573,7 +13568,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13587,10 +13582,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46196</v>
+        <v>45142</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13603,7 +13598,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13646,7 +13641,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13660,10 +13655,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45971</v>
+        <v>44858</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13676,7 +13671,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13719,7 +13714,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13733,10 +13728,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46198</v>
+        <v>45160</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13749,7 +13744,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13792,7 +13787,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13806,10 +13801,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45629</v>
+        <v>45435</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13822,7 +13817,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13865,7 +13860,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13875,14 +13870,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45226</v>
+        <v>45435</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13895,7 +13890,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13938,7 +13933,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13952,10 +13947,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45979</v>
+        <v>45320</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13968,7 +13963,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14011,7 +14006,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14025,10 +14020,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45629</v>
+        <v>45218</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14041,7 +14036,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14084,7 +14079,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14098,10 +14093,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44637</v>
+        <v>46091</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14114,7 +14109,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.4</v>
+        <v>10.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14157,7 +14152,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14171,10 +14166,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45232</v>
+        <v>45344</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14187,7 +14182,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14230,7 +14225,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14244,10 +14239,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45728</v>
+        <v>46097</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14260,7 +14255,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14303,7 +14298,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14317,10 +14312,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45757</v>
+        <v>44601</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14333,7 +14328,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14376,7 +14371,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14390,10 +14385,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45142</v>
+        <v>46196</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14406,7 +14401,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14449,7 +14444,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14463,10 +14458,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45274</v>
+        <v>45253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14479,7 +14474,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14522,7 +14517,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14536,10 +14531,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46209</v>
+        <v>46195</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14552,7 +14547,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14595,7 +14590,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14609,10 +14604,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44615</v>
+        <v>45569</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14624,8 +14619,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14678,14 +14678,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45265</v>
+        <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45910</v>
+        <v>46195</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45994</v>
+        <v>46198</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45320</v>
+        <v>46197</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14960,7 +14960,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46212</v>
+        <v>45728</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15033,7 +15033,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15047,10 +15047,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45993</v>
+        <v>44642</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>19.6</v>
+        <v>2.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15106,7 +15106,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45264</v>
+        <v>44615</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15179,7 +15179,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15193,10 +15193,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46045</v>
+        <v>45450</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15252,7 +15252,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15266,10 +15266,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44895</v>
+        <v>45253</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15339,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44895</v>
+        <v>46113</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15354,8 +15354,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15398,7 +15403,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15412,10 +15417,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45253</v>
+        <v>45308</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15428,7 +15433,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15471,7 +15476,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15485,10 +15490,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46220</v>
+        <v>44893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15501,7 +15506,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15544,7 +15549,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15558,10 +15563,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46265</v>
+        <v>44637</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15574,7 +15579,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15617,7 +15622,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15631,10 +15636,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46220</v>
+        <v>44539</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15647,7 +15652,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15690,7 +15695,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15704,10 +15709,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45043</v>
+        <v>45116</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15720,7 +15725,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15763,7 +15768,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15777,10 +15782,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46220</v>
+        <v>44812</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15793,7 +15798,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15836,7 +15841,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15850,10 +15855,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46227</v>
+        <v>44816</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15866,7 +15871,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15909,7 +15914,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15923,10 +15928,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45701</v>
+        <v>45940</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15939,7 +15944,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15982,7 +15987,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15996,10 +16001,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44895</v>
+        <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16012,7 +16017,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16055,7 +16060,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16069,10 +16074,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45561</v>
+        <v>46136</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16085,7 +16090,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16128,7 +16133,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 51421-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16142,10 +16147,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45840</v>
+        <v>44461</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16158,7 +16163,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16201,7 +16206,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16215,10 +16220,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45142</v>
+        <v>44875</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16231,7 +16236,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16274,7 +16279,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16288,10 +16293,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46020</v>
+        <v>44909</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16304,7 +16309,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16347,7 +16352,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 50712-2021</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16361,10 +16366,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44460</v>
+        <v>45701</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16377,7 +16382,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16420,7 +16425,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 50713-2021</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16434,10 +16439,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44460</v>
+        <v>44900</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16450,7 +16455,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16493,7 +16498,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16507,10 +16512,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44900</v>
+        <v>45226</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16523,7 +16528,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16566,7 +16571,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16576,14 +16581,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44935</v>
+        <v>44644</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16596,7 +16601,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16639,7 +16644,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16653,10 +16658,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44935</v>
+        <v>45910</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16669,7 +16674,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16712,7 +16717,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16726,10 +16731,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44539</v>
+        <v>45265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16742,7 +16747,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16785,7 +16790,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16799,10 +16804,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44551</v>
+        <v>46209</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16815,7 +16820,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16858,7 +16863,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16872,10 +16877,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44979</v>
+        <v>45180</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16888,7 +16893,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16931,7 +16936,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16941,14 +16946,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45146</v>
+        <v>46212</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16961,7 +16966,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17004,7 +17009,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17018,10 +17023,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45359</v>
+        <v>45645</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17034,7 +17039,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17077,7 +17082,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 52237-2021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17091,10 +17096,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45358</v>
+        <v>44463</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17107,7 +17112,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17150,7 +17155,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17164,10 +17169,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45230</v>
+        <v>46045</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17180,7 +17185,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17223,7 +17228,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17237,10 +17242,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46038</v>
+        <v>45358</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17253,7 +17258,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17296,7 +17301,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17310,10 +17315,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45005</v>
+        <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17326,7 +17331,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17369,7 +17374,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17383,10 +17388,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45246</v>
+        <v>45715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17398,8 +17403,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17442,7 +17452,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17456,10 +17466,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45221</v>
+        <v>45043</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17472,7 +17482,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17515,7 +17525,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17529,10 +17539,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45090</v>
+        <v>44600</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17545,7 +17555,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17588,7 +17598,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17602,10 +17612,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45435</v>
+        <v>45719</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17617,8 +17627,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17661,7 +17676,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17675,10 +17690,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45237</v>
+        <v>45621</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17691,7 +17706,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17734,7 +17749,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17748,10 +17763,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46048</v>
+        <v>46265</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17763,13 +17778,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17812,7 +17822,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17826,10 +17836,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45448</v>
+        <v>45569</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17841,8 +17851,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17885,7 +17900,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17899,10 +17914,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45435</v>
+        <v>46220</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17915,7 +17930,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17958,7 +17973,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17972,10 +17987,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45358</v>
+        <v>46220</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -17988,7 +18003,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18031,7 +18046,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18041,14 +18056,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44631</v>
+        <v>45387</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18061,7 +18076,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18104,7 +18119,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18118,10 +18133,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45677</v>
+        <v>46220</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18177,7 +18192,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18191,10 +18206,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45628</v>
+        <v>45055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18207,7 +18222,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18250,7 +18265,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18264,10 +18279,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45677</v>
+        <v>45728</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18280,7 +18295,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18323,7 +18338,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18337,10 +18352,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45266</v>
+        <v>44700</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18353,7 +18368,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18396,7 +18411,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18410,10 +18425,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45635</v>
+        <v>45630</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18426,7 +18441,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18469,7 +18484,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18483,10 +18498,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45387</v>
+        <v>46227</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18499,7 +18514,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18542,7 +18557,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18556,10 +18571,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45554</v>
+        <v>45665</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18571,13 +18586,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18620,7 +18630,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18634,10 +18644,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45569</v>
+        <v>45387</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18649,13 +18659,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -18698,7 +18703,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18708,14 +18713,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45719</v>
+        <v>45365</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18727,13 +18732,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18776,7 +18776,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18790,10 +18790,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44463</v>
+        <v>45713</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18849,7 +18849,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18863,10 +18863,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44812</v>
+        <v>45792</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18922,7 +18922,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18936,10 +18936,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44655</v>
+        <v>45792</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18995,7 +18995,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19009,10 +19009,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44600</v>
+        <v>45685</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44837</v>
+        <v>45594</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19141,7 +19141,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19155,10 +19155,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45253</v>
+        <v>45475</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19228,10 +19228,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45630</v>
+        <v>45604</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19287,7 +19287,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19301,10 +19301,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45265</v>
+        <v>45475</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19360,7 +19360,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19374,10 +19374,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45386</v>
+        <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19433,7 +19433,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19447,10 +19447,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45665</v>
+        <v>45629</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19506,7 +19506,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19520,10 +19520,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45387</v>
+        <v>45638</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19579,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19593,10 +19593,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45365</v>
+        <v>45728</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19666,10 +19666,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45792</v>
+        <v>45832</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19812,10 +19812,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45594</v>
+        <v>45834</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19881,14 +19881,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45792</v>
+        <v>45786</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45685</v>
+        <v>45841</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20017,7 +20017,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 33664-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20031,10 +20031,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45629</v>
+        <v>45841</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20090,7 +20090,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 33910-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20104,10 +20104,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45629</v>
+        <v>45842</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20163,7 +20163,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45475</v>
+        <v>45667</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20236,7 +20236,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20250,10 +20250,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45604</v>
+        <v>45701</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20309,7 +20309,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45475</v>
+        <v>45870</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20382,7 +20382,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45638</v>
+        <v>45870</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20455,7 +20455,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20469,10 +20469,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45728</v>
+        <v>45271</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20528,7 +20528,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 1352-2022</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -20542,10 +20542,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44628</v>
+        <v>45323</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20557,13 +20557,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I271" t="n">
-        <v>47.1</v>
+        <v>3.8</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -20606,7 +20601,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 1352-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20616,14 +20611,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44601</v>
+        <v>44628</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20637,11 +20632,11 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.4</v>
+        <v>47.1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -20684,7 +20679,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20701,7 +20696,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20714,7 +20709,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>3.8</v>
+        <v>38.9</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -20757,7 +20752,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 510-2025</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20767,14 +20762,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45706</v>
+        <v>44601</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -20786,8 +20781,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I274" t="n">
-        <v>32.6</v>
+        <v>1.4</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -20830,7 +20830,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -20840,14 +20840,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45323</v>
+        <v>45368</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>38.9</v>
+        <v>2.9</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -20903,7 +20903,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -20913,14 +20913,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45368</v>
+        <v>45323</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -20976,7 +20976,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -20993,7 +20993,7 @@
         <v>45323</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>7.9</v>
+        <v>16.3</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21049,7 +21049,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 280-2024</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21063,10 +21063,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45323</v>
+        <v>45706</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>16.3</v>
+        <v>32.6</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -601,7 +601,7 @@
         <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>45870</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>45624</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>46252</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44627</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44851</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44460</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44460</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44858</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45554</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45358</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>45635</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45386</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45435</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45628</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45569</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45359</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>45358</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45232</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44550</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45448</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44655</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45435</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45142</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>44771</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45575</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45327</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45230</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45740</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>45687</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45576</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45757</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45090</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45279</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45348</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45359</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44935</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44934</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45299</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45146</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45677</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45777</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44616</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45637</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45685</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45098</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44934</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45196</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45595</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44631</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45142</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45243</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45899</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45713</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44461</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45478</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45265</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>46129</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45359</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45561</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44460</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44460</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>45217</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44551</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45947</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45947</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45221</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45622</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45397</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45960</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44895</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44895</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>45960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>45967</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45971</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44565</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45979</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45629</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45338</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45377</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>44862</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45116</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45116</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45993</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45142</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44988</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45994</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45274</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45629</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44837</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45267</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44460</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>46020</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>45677</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45688</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45541</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44579</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>46038</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>45601</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>46171</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45944</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45202</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45266</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>46178</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45005</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46069</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45338</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>46073</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>46073</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>46073</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46073</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>46073</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45434</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>44900</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45142</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44858</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45160</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45435</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45435</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45320</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45218</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>46091</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45344</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>46097</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>44601</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>46196</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>46195</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45569</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>46195</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46198</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>46197</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45728</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>44642</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>44615</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45450</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45253</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>46113</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45308</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44637</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>44539</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45116</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44812</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>44816</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45940</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>46136</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44461</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44875</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>44909</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45701</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44900</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45226</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44644</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45910</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>46209</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45180</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>46212</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45645</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44463</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46045</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45358</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45043</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44600</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45719</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45621</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>46265</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45569</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>46220</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>46220</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45387</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>46220</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45728</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>44700</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45630</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>46227</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45665</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45387</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45365</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45713</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45792</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45792</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45685</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45594</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45475</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45604</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45475</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45629</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45638</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45728</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45825</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45832</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45834</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45786</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>45841</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45841</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45842</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45667</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45701</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45870</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45870</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45271</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45323</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44628</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44601</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45368</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45323</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45323</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45706</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE278"/>
+  <dimension ref="A1:AE270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>45870</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 56164-2024</t>
+          <t>A 33920-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1018,14 +1018,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45624</v>
+        <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>15.7</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1071,154 +1071,154 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 56164-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45624</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Mattlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 33920-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 9847-2022</t>
+          <t>A 34906-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44620</v>
+        <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34906-2022</t>
+          <t>A 9847-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10831-2022</t>
+          <t>A 62540-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44627</v>
+        <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 62540-2021</t>
+          <t>A 10831-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44503</v>
+        <v>44627</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46713-2022</t>
+          <t>A 50987-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44851</v>
+        <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50987-2022</t>
+          <t>A 46713-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44867</v>
+        <v>44851</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 50699-2021</t>
+          <t>A 49047-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44460</v>
+        <v>44858</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 50702-2021</t>
+          <t>A 50985-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44460</v>
+        <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49047-2022</t>
+          <t>A 5174-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44858</v>
+        <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50985-2022</t>
+          <t>A 50984-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5174-2022</t>
+          <t>A 33171-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44594</v>
+        <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50984-2022</t>
+          <t>A 10503-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44867</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33171-2022</t>
+          <t>A 12173-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44785</v>
+        <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10503-2022</t>
+          <t>A 12175-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44623</v>
+        <v>44636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12173-2022</t>
+          <t>A 21085-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44636</v>
+        <v>44704</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12175-2022</t>
+          <t>A 9212-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44636</v>
+        <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21085-2022</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44704</v>
+        <v>45554</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3629,8 +3629,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3673,7 +3678,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9212-2022</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3687,10 +3692,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44616</v>
+        <v>45435</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3703,7 +3708,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3746,7 +3751,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3760,10 +3765,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45554</v>
+        <v>45358</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3775,13 +3780,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>12.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45358</v>
+        <v>45628</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>12.2</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>45510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45635</v>
+        <v>44973</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45386</v>
+        <v>45635</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44973</v>
+        <v>45386</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45435</v>
+        <v>45569</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4510,8 +4510,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4554,7 +4559,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4568,10 +4573,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45628</v>
+        <v>45359</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4584,7 +4589,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4627,7 +4632,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4641,10 +4646,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45569</v>
+        <v>45358</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4656,13 +4661,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4705,7 +4705,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45359</v>
+        <v>44935</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45358</v>
+        <v>45232</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44935</v>
+        <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45232</v>
+        <v>45448</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44550</v>
+        <v>45435</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5070,7 +5070,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45448</v>
+        <v>44655</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44655</v>
+        <v>44895</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45435</v>
+        <v>44771</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44895</v>
+        <v>45142</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5362,7 +5362,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45142</v>
+        <v>45740</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44771</v>
+        <v>44823</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44823</v>
+        <v>45575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5537,8 +5537,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5598,7 +5603,7 @@
         <v>45176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5654,7 +5659,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5673,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45575</v>
+        <v>45327</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5683,13 +5688,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45327</v>
+        <v>45230</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45230</v>
+        <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5878,7 +5878,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5888,14 +5888,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45740</v>
+        <v>45687</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5951,7 +5951,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44895</v>
+        <v>44867</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45687</v>
+        <v>45576</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44867</v>
+        <v>45757</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45576</v>
+        <v>45090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45757</v>
+        <v>45265</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6316,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45090</v>
+        <v>45359</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6389,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45265</v>
+        <v>45870</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6472,14 +6472,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45279</v>
+        <v>45870</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45279</v>
+        <v>45713</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45348</v>
+        <v>45146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6691,14 +6691,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45359</v>
+        <v>45279</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44935</v>
+        <v>45279</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6837,14 +6837,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44934</v>
+        <v>45271</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6910,14 +6910,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45299</v>
+        <v>44539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45146</v>
+        <v>45685</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45677</v>
+        <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45777</v>
+        <v>45348</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44616</v>
+        <v>46136</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7275,14 +7275,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44539</v>
+        <v>45299</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45637</v>
+        <v>45777</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45685</v>
+        <v>44935</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45098</v>
+        <v>44934</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44934</v>
+        <v>45899</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45196</v>
+        <v>45898</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45595</v>
+        <v>45908</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7786,14 +7786,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44631</v>
+        <v>45677</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45142</v>
+        <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45243</v>
+        <v>45637</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7995,7 +7995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45899</v>
+        <v>45098</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8068,7 +8068,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45898</v>
+        <v>44934</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45713</v>
+        <v>45196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44461</v>
+        <v>45595</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45478</v>
+        <v>44631</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8360,7 +8360,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45908</v>
+        <v>46129</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45265</v>
+        <v>45142</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46129</v>
+        <v>45243</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8593,10 +8593,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44979</v>
+        <v>45478</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45359</v>
+        <v>45265</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8725,7 +8725,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45358</v>
+        <v>45943</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8754,8 +8754,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8798,7 +8803,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8812,10 +8817,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45561</v>
+        <v>45967</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8828,7 +8833,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8871,7 +8876,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8885,10 +8890,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45246</v>
+        <v>44979</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8901,7 +8906,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8944,7 +8949,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 50709-2021</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8958,10 +8963,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44460</v>
+        <v>45359</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8974,7 +8979,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9017,7 +9022,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50712-2021</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9031,10 +9036,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44460</v>
+        <v>45358</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9047,7 +9052,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9090,7 +9095,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9104,10 +9109,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9117,11 +9122,6 @@
       <c r="G115" t="inlineStr">
         <is>
           <t>VARA</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -9168,7 +9168,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45217</v>
+        <v>45947</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9241,7 +9241,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44551</v>
+        <v>45947</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9314,7 +9314,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44685</v>
+        <v>46157</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9387,7 +9387,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44685</v>
+        <v>45377</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9460,7 +9460,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45947</v>
+        <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45947</v>
+        <v>45561</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.2</v>
+        <v>7.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9606,7 +9606,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9620,10 +9620,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45947</v>
+        <v>45246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9679,7 +9679,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9693,10 +9693,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45221</v>
+        <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9752,7 +9752,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45622</v>
+        <v>45960</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>19.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9825,7 +9825,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45397</v>
+        <v>45960</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9898,7 +9898,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9912,10 +9912,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45960</v>
+        <v>45971</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9971,7 +9971,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44895</v>
+        <v>45979</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.6</v>
+        <v>7.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10044,7 +10044,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10058,10 +10058,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44895</v>
+        <v>45217</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10117,7 +10117,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45960</v>
+        <v>44551</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>19.8</v>
+        <v>3.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10190,7 +10190,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10204,10 +10204,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45960</v>
+        <v>44685</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10263,7 +10263,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45967</v>
+        <v>44685</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10336,7 +10336,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45971</v>
+        <v>45221</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10409,7 +10409,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44565</v>
+        <v>45993</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.8</v>
+        <v>19.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10482,7 +10482,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10496,10 +10496,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45979</v>
+        <v>45622</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10555,7 +10555,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10569,10 +10569,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45629</v>
+        <v>45994</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10628,7 +10628,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10642,10 +10642,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45338</v>
+        <v>45397</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10657,13 +10657,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10706,7 +10701,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10720,10 +10715,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10736,7 +10731,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10779,7 +10774,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10793,10 +10788,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45377</v>
+        <v>45944</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10809,7 +10804,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10852,7 +10847,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10866,10 +10861,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44862</v>
+        <v>44895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10882,7 +10877,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10925,7 +10920,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10939,10 +10934,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45116</v>
+        <v>44895</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10955,7 +10950,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10998,7 +10993,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45116</v>
+        <v>44565</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11028,7 +11023,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11071,7 +11066,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11085,10 +11080,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45898</v>
+        <v>46178</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11101,7 +11096,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11144,7 +11139,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11158,10 +11153,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45993</v>
+        <v>45840</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11174,7 +11169,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>19.6</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11217,7 +11212,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11231,10 +11226,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45142</v>
+        <v>46020</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11247,7 +11242,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11290,7 +11285,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11304,10 +11299,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44988</v>
+        <v>45629</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11320,7 +11315,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11363,7 +11358,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11377,10 +11372,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45994</v>
+        <v>45338</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11392,8 +11387,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11436,7 +11436,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11450,10 +11450,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45274</v>
+        <v>44862</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11509,7 +11509,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11523,10 +11523,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45629</v>
+        <v>45116</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11582,7 +11582,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44837</v>
+        <v>45116</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11655,7 +11655,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45267</v>
+        <v>46038</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11728,7 +11728,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11742,10 +11742,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45840</v>
+        <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11757,8 +11757,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11801,7 +11806,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50713-2021</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11815,10 +11820,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44460</v>
+        <v>45142</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11831,7 +11836,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11874,7 +11879,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11888,10 +11893,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46020</v>
+        <v>44988</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11904,7 +11909,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11947,7 +11952,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11961,10 +11966,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45677</v>
+        <v>46196</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11977,7 +11982,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12020,7 +12025,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12034,10 +12039,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45688</v>
+        <v>45274</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12049,13 +12054,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12098,7 +12098,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45541</v>
+        <v>45629</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12171,7 +12171,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44579</v>
+        <v>46195</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12244,7 +12244,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46038</v>
+        <v>46195</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12331,10 +12331,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45601</v>
+        <v>44837</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12390,7 +12390,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12404,10 +12404,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46171</v>
+        <v>46198</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12463,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12477,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45944</v>
+        <v>46197</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12536,7 +12536,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12550,10 +12550,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46048</v>
+        <v>46069</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12565,13 +12565,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12614,7 +12609,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12628,10 +12623,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45202</v>
+        <v>45267</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12644,7 +12639,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12687,7 +12682,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12701,10 +12696,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45266</v>
+        <v>46073</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12717,7 +12712,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12760,7 +12755,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12774,10 +12769,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46178</v>
+        <v>46073</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12790,7 +12785,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12833,7 +12828,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12847,10 +12842,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45005</v>
+        <v>46073</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12863,7 +12858,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12906,7 +12901,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12920,10 +12915,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46069</v>
+        <v>46073</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12936,7 +12931,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12979,7 +12974,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12993,10 +12988,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45338</v>
+        <v>46073</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13008,13 +13003,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13057,7 +13047,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13071,10 +13061,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46073</v>
+        <v>46091</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13087,7 +13077,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5.5</v>
+        <v>10.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13130,7 +13120,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13144,10 +13134,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46073</v>
+        <v>45677</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13160,7 +13150,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13203,7 +13193,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13217,10 +13207,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46073</v>
+        <v>46097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13233,7 +13223,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13276,7 +13266,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13290,10 +13280,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46073</v>
+        <v>45688</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13305,8 +13295,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13349,7 +13344,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13363,10 +13358,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46073</v>
+        <v>45541</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13379,7 +13374,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13422,7 +13417,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13436,10 +13431,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45434</v>
+        <v>44579</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13452,7 +13447,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13495,7 +13490,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13509,10 +13504,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44900</v>
+        <v>45601</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13525,7 +13520,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13568,7 +13563,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13582,10 +13577,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45142</v>
+        <v>45202</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13598,7 +13593,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13641,7 +13636,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13655,10 +13650,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44858</v>
+        <v>46113</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13670,8 +13665,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13714,7 +13714,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13728,10 +13728,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45160</v>
+        <v>45266</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13787,7 +13787,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45435</v>
+        <v>45005</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13860,7 +13860,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13870,14 +13870,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45435</v>
+        <v>45338</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13889,8 +13889,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13933,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13947,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45320</v>
+        <v>45434</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13963,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14006,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14020,10 +14025,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45218</v>
+        <v>44900</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14036,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14079,7 +14084,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14093,10 +14098,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46091</v>
+        <v>45142</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14109,7 +14114,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>10.9</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14152,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14166,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45344</v>
+        <v>44858</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14182,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14225,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14239,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46097</v>
+        <v>45160</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14255,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14298,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14312,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44601</v>
+        <v>45910</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14328,7 +14333,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14371,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14385,10 +14390,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46196</v>
+        <v>45435</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14401,7 +14406,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14444,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14454,14 +14459,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45253</v>
+        <v>45435</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14474,7 +14479,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14517,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14531,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14547,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14590,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14604,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45569</v>
+        <v>45320</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14619,13 +14624,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14678,14 +14678,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45146</v>
+        <v>45218</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46195</v>
+        <v>46212</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46198</v>
+        <v>45344</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46197</v>
+        <v>46045</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14960,7 +14960,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45728</v>
+        <v>44601</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15033,7 +15033,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15047,10 +15047,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44642</v>
+        <v>45253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15106,7 +15106,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44615</v>
+        <v>45569</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15135,8 +15135,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15179,7 +15184,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15189,14 +15194,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45450</v>
+        <v>45146</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15209,7 +15214,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15252,7 +15257,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15266,10 +15271,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45253</v>
+        <v>45728</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15282,7 +15287,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15325,7 +15330,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15339,10 +15344,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46113</v>
+        <v>44642</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15354,13 +15359,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15403,7 +15403,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15417,10 +15417,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45308</v>
+        <v>44615</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15476,7 +15476,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15490,10 +15490,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44893</v>
+        <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15549,7 +15549,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15563,10 +15563,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44637</v>
+        <v>45253</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15622,7 +15622,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15636,10 +15636,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44539</v>
+        <v>46265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15695,7 +15695,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15709,10 +15709,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45116</v>
+        <v>46220</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15782,10 +15782,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44812</v>
+        <v>45308</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15855,10 +15855,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44816</v>
+        <v>46220</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.3</v>
+        <v>15.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15914,7 +15914,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15928,10 +15928,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45940</v>
+        <v>44893</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,7 +15987,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45237</v>
+        <v>44637</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16060,7 +16060,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16074,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46136</v>
+        <v>44539</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16133,7 +16133,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 51421-2021</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16147,10 +16147,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44461</v>
+        <v>46220</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16206,7 +16206,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16220,10 +16220,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44875</v>
+        <v>45116</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16279,7 +16279,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44909</v>
+        <v>44812</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16352,7 +16352,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45701</v>
+        <v>44816</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16425,7 +16425,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44900</v>
+        <v>45237</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16498,7 +16498,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45226</v>
+        <v>44875</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16581,14 +16581,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44644</v>
+        <v>46227</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16644,7 +16644,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16658,10 +16658,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45910</v>
+        <v>44909</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16717,7 +16717,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45265</v>
+        <v>45701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16790,7 +16790,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16804,10 +16804,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46209</v>
+        <v>44900</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45180</v>
+        <v>45226</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16946,14 +16946,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46212</v>
+        <v>44644</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17009,7 +17009,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17023,10 +17023,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45645</v>
+        <v>45265</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17096,10 +17096,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44463</v>
+        <v>45180</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17155,7 +17155,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17169,10 +17169,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46045</v>
+        <v>45645</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17228,7 +17228,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 52237-2021</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17242,10 +17242,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45358</v>
+        <v>44463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45260</v>
+        <v>45358</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17374,7 +17374,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17388,10 +17388,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45715</v>
+        <v>45260</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17403,13 +17403,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17452,7 +17447,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17466,10 +17461,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45043</v>
+        <v>45715</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17481,8 +17476,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17525,7 +17525,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17539,10 +17539,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44600</v>
+        <v>45043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17598,7 +17598,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17612,10 +17612,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45719</v>
+        <v>44600</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17627,13 +17627,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17676,7 +17671,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17690,10 +17685,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45621</v>
+        <v>45719</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17705,8 +17700,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17749,7 +17749,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17763,10 +17763,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46265</v>
+        <v>45621</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17839,7 +17839,7 @@
         <v>45569</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 39054-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17914,10 +17914,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46220</v>
+        <v>46287</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17973,7 +17973,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17987,10 +17987,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46220</v>
+        <v>45387</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>15.5</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18046,7 +18046,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18060,10 +18060,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45387</v>
+        <v>45055</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18119,7 +18119,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18133,10 +18133,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46220</v>
+        <v>45728</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18192,7 +18192,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18206,10 +18206,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45055</v>
+        <v>44700</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18265,7 +18265,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18279,10 +18279,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45728</v>
+        <v>45630</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18338,7 +18338,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18352,10 +18352,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44700</v>
+        <v>45665</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18411,7 +18411,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18425,10 +18425,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45630</v>
+        <v>45387</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18484,7 +18484,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18494,14 +18494,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46227</v>
+        <v>45365</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18557,7 +18557,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18571,10 +18571,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45665</v>
+        <v>45713</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18630,7 +18630,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18644,10 +18644,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45387</v>
+        <v>45792</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18713,14 +18713,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45365</v>
+        <v>45792</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18776,7 +18776,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18790,10 +18790,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45713</v>
+        <v>45685</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18849,7 +18849,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18863,10 +18863,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45792</v>
+        <v>45594</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18922,7 +18922,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18936,10 +18936,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45792</v>
+        <v>45475</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18995,7 +18995,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19009,10 +19009,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45685</v>
+        <v>45604</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45594</v>
+        <v>45475</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19141,7 +19141,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19155,10 +19155,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45475</v>
+        <v>45629</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19228,10 +19228,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45604</v>
+        <v>45629</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19287,7 +19287,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19301,10 +19301,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45475</v>
+        <v>45638</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19360,7 +19360,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19370,14 +19370,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45629</v>
+        <v>45728</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19433,7 +19433,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19447,10 +19447,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45629</v>
+        <v>45825</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19506,7 +19506,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19520,10 +19520,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45638</v>
+        <v>45832</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19579,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19589,14 +19589,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45728</v>
+        <v>45834</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19662,14 +19662,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45825</v>
+        <v>45786</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19812,10 +19812,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45834</v>
+        <v>45667</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19881,14 +19881,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45786</v>
+        <v>45701</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,24 +19944,24 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45841</v>
+        <v>45323</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20017,24 +20017,24 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 33664-2025</t>
+          <t>S 1352-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45841</v>
+        <v>44628</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20046,8 +20046,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I264" t="n">
-        <v>4.7</v>
+        <v>47.1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20090,24 +20095,24 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 33910-2025</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45842</v>
+        <v>45323</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20120,7 +20125,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>3.6</v>
+        <v>38.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20163,24 +20168,24 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45667</v>
+        <v>44601</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20192,8 +20197,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I266" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20236,24 +20246,24 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45701</v>
+        <v>45368</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20266,7 +20276,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20309,24 +20319,24 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45870</v>
+        <v>45323</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20339,7 +20349,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.7</v>
+        <v>7.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20382,24 +20392,24 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45870</v>
+        <v>45323</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20412,7 +20422,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1.1</v>
+        <v>16.3</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20452,27 +20462,27 @@
       </c>
       <c r="V269" s="2" t="inlineStr"/>
     </row>
-    <row r="270" ht="15" customHeight="1">
+    <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45271</v>
+        <v>45706</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20485,7 +20495,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.4</v>
+        <v>32.6</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20524,600 +20534,6 @@
         <v>0</v>
       </c>
       <c r="V270" s="2" t="inlineStr"/>
-    </row>
-    <row r="271" ht="15" customHeight="1">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>S 279-2024</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D271" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E271" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I271" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J271" t="n">
-        <v>0</v>
-      </c>
-      <c r="K271" t="n">
-        <v>0</v>
-      </c>
-      <c r="L271" t="n">
-        <v>0</v>
-      </c>
-      <c r="M271" t="n">
-        <v>0</v>
-      </c>
-      <c r="N271" t="n">
-        <v>0</v>
-      </c>
-      <c r="O271" t="n">
-        <v>0</v>
-      </c>
-      <c r="P271" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0</v>
-      </c>
-      <c r="S271" t="n">
-        <v>0</v>
-      </c>
-      <c r="T271" t="n">
-        <v>0</v>
-      </c>
-      <c r="U271" t="n">
-        <v>0</v>
-      </c>
-      <c r="V271" s="2" t="inlineStr"/>
-    </row>
-    <row r="272" ht="15" customHeight="1">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>S 1352-2022</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D272" s="1" t="n">
-        <v>44628</v>
-      </c>
-      <c r="E272" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I272" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J272" t="n">
-        <v>0</v>
-      </c>
-      <c r="K272" t="n">
-        <v>0</v>
-      </c>
-      <c r="L272" t="n">
-        <v>0</v>
-      </c>
-      <c r="M272" t="n">
-        <v>0</v>
-      </c>
-      <c r="N272" t="n">
-        <v>0</v>
-      </c>
-      <c r="O272" t="n">
-        <v>0</v>
-      </c>
-      <c r="P272" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0</v>
-      </c>
-      <c r="S272" t="n">
-        <v>0</v>
-      </c>
-      <c r="T272" t="n">
-        <v>0</v>
-      </c>
-      <c r="U272" t="n">
-        <v>0</v>
-      </c>
-      <c r="V272" s="2" t="inlineStr"/>
-    </row>
-    <row r="273" ht="15" customHeight="1">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>S 273-2024</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D273" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E273" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I273" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="J273" t="n">
-        <v>0</v>
-      </c>
-      <c r="K273" t="n">
-        <v>0</v>
-      </c>
-      <c r="L273" t="n">
-        <v>0</v>
-      </c>
-      <c r="M273" t="n">
-        <v>0</v>
-      </c>
-      <c r="N273" t="n">
-        <v>0</v>
-      </c>
-      <c r="O273" t="n">
-        <v>0</v>
-      </c>
-      <c r="P273" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0</v>
-      </c>
-      <c r="S273" t="n">
-        <v>0</v>
-      </c>
-      <c r="T273" t="n">
-        <v>0</v>
-      </c>
-      <c r="U273" t="n">
-        <v>0</v>
-      </c>
-      <c r="V273" s="2" t="inlineStr"/>
-    </row>
-    <row r="274" ht="15" customHeight="1">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>S 761-2022</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D274" s="1" t="n">
-        <v>44601</v>
-      </c>
-      <c r="E274" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I274" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J274" t="n">
-        <v>0</v>
-      </c>
-      <c r="K274" t="n">
-        <v>0</v>
-      </c>
-      <c r="L274" t="n">
-        <v>0</v>
-      </c>
-      <c r="M274" t="n">
-        <v>0</v>
-      </c>
-      <c r="N274" t="n">
-        <v>0</v>
-      </c>
-      <c r="O274" t="n">
-        <v>0</v>
-      </c>
-      <c r="P274" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
-      <c r="R274" t="n">
-        <v>0</v>
-      </c>
-      <c r="S274" t="n">
-        <v>0</v>
-      </c>
-      <c r="T274" t="n">
-        <v>0</v>
-      </c>
-      <c r="U274" t="n">
-        <v>0</v>
-      </c>
-      <c r="V274" s="2" t="inlineStr"/>
-    </row>
-    <row r="275" ht="15" customHeight="1">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>S 777-2024</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D275" s="1" t="n">
-        <v>45368</v>
-      </c>
-      <c r="E275" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I275" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J275" t="n">
-        <v>0</v>
-      </c>
-      <c r="K275" t="n">
-        <v>0</v>
-      </c>
-      <c r="L275" t="n">
-        <v>0</v>
-      </c>
-      <c r="M275" t="n">
-        <v>0</v>
-      </c>
-      <c r="N275" t="n">
-        <v>0</v>
-      </c>
-      <c r="O275" t="n">
-        <v>0</v>
-      </c>
-      <c r="P275" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0</v>
-      </c>
-      <c r="S275" t="n">
-        <v>0</v>
-      </c>
-      <c r="T275" t="n">
-        <v>0</v>
-      </c>
-      <c r="U275" t="n">
-        <v>0</v>
-      </c>
-      <c r="V275" s="2" t="inlineStr"/>
-    </row>
-    <row r="276" ht="15" customHeight="1">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>S 274-2024</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D276" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E276" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I276" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J276" t="n">
-        <v>0</v>
-      </c>
-      <c r="K276" t="n">
-        <v>0</v>
-      </c>
-      <c r="L276" t="n">
-        <v>0</v>
-      </c>
-      <c r="M276" t="n">
-        <v>0</v>
-      </c>
-      <c r="N276" t="n">
-        <v>0</v>
-      </c>
-      <c r="O276" t="n">
-        <v>0</v>
-      </c>
-      <c r="P276" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0</v>
-      </c>
-      <c r="S276" t="n">
-        <v>0</v>
-      </c>
-      <c r="T276" t="n">
-        <v>0</v>
-      </c>
-      <c r="U276" t="n">
-        <v>0</v>
-      </c>
-      <c r="V276" s="2" t="inlineStr"/>
-    </row>
-    <row r="277" ht="15" customHeight="1">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>S 280-2024</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D277" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E277" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I277" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J277" t="n">
-        <v>0</v>
-      </c>
-      <c r="K277" t="n">
-        <v>0</v>
-      </c>
-      <c r="L277" t="n">
-        <v>0</v>
-      </c>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0</v>
-      </c>
-      <c r="S277" t="n">
-        <v>0</v>
-      </c>
-      <c r="T277" t="n">
-        <v>0</v>
-      </c>
-      <c r="U277" t="n">
-        <v>0</v>
-      </c>
-      <c r="V277" s="2" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>S 510-2025</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D278" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E278" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I278" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="J278" t="n">
-        <v>0</v>
-      </c>
-      <c r="K278" t="n">
-        <v>0</v>
-      </c>
-      <c r="L278" t="n">
-        <v>0</v>
-      </c>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0</v>
-      </c>
-      <c r="S278" t="n">
-        <v>0</v>
-      </c>
-      <c r="T278" t="n">
-        <v>0</v>
-      </c>
-      <c r="U278" t="n">
-        <v>0</v>
-      </c>
-      <c r="V278" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE270"/>
+  <dimension ref="A1:AE271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 11270-2025</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45726</v>
+        <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>15.7</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -740,10 +740,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -752,46 +752,42 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Härfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
@@ -815,7 +811,7 @@
         <v>45870</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +916,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1008,7 +1004,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 33920-2026</t>
+          <t>A 11270-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1018,14 +1014,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46252</v>
+        <v>45726</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1038,7 +1034,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1047,19 +1043,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -1078,147 +1074,151 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Härfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 33920-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Gulsparv</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56164-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45624</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34906-2022</t>
+          <t>A 9847-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44796</v>
+        <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9847-2022</t>
+          <t>A 34906-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44620</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44627</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 42438-2022</t>
+          <t>A 46713-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44831</v>
+        <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>15.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 50987-2022</t>
+          <t>A 46930-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44867</v>
+        <v>44851</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46713-2022</t>
+          <t>A 42438-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44851</v>
+        <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.7</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46930-2022</t>
+          <t>A 50987-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44851</v>
+        <v>44867</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44858</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 50985-2022</t>
+          <t>A 10503-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44867</v>
+        <v>44623</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5174-2022</t>
+          <t>A 50985-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44594</v>
+        <v>44867</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50984-2022</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44867</v>
+        <v>44601</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33171-2022</t>
+          <t>A 12173-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44785</v>
+        <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10503-2022</t>
+          <t>A 12175-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>44636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12173-2022</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3318,14 +3318,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44636</v>
+        <v>45365</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12175-2022</t>
+          <t>A 5174-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44636</v>
+        <v>44594</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21085-2022</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44704</v>
+        <v>44816</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9212-2022</t>
+          <t>A 21085-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44616</v>
+        <v>44704</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 9212-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45554</v>
+        <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3629,13 +3629,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3678,7 +3673,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3692,10 +3687,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45435</v>
+        <v>45715</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3707,8 +3702,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 50984-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45358</v>
+        <v>44867</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>12.2</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 33171-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45628</v>
+        <v>44785</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>45510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45643</v>
+        <v>45637</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44973</v>
+        <v>45687</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>7.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45635</v>
+        <v>45202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45386</v>
+        <v>45267</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45264</v>
+        <v>44823</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45253</v>
+        <v>44579</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45253</v>
+        <v>45359</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45569</v>
+        <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45359</v>
+        <v>44867</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45358</v>
+        <v>45176</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4705,7 +4705,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44935</v>
+        <v>45713</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45232</v>
+        <v>45253</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44550</v>
+        <v>45359</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45448</v>
+        <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45435</v>
+        <v>45253</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5070,7 +5070,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44655</v>
+        <v>44858</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44895</v>
+        <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44771</v>
+        <v>45792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45142</v>
+        <v>45685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5362,7 +5362,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45740</v>
+        <v>45098</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44823</v>
+        <v>44685</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45575</v>
+        <v>44685</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5537,13 +5537,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5586,7 +5581,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5600,10 +5595,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45176</v>
+        <v>44539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5616,7 +5611,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5659,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5673,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45327</v>
+        <v>44900</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5689,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5732,7 +5727,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5746,10 +5741,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45230</v>
+        <v>45541</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5762,7 +5757,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5805,7 +5800,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5822,7 +5817,7 @@
         <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5835,7 +5830,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5878,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5892,10 +5887,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45687</v>
+        <v>45327</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5908,7 +5903,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5951,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5965,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44867</v>
+        <v>45713</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5981,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6024,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6038,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45576</v>
+        <v>45146</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6054,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6097,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6111,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45757</v>
+        <v>45685</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6127,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6170,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6180,14 +6175,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45090</v>
+        <v>45740</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6200,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6243,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6257,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45265</v>
+        <v>45397</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6273,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6316,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6330,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45359</v>
+        <v>44875</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6389,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45870</v>
+        <v>45116</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6472,14 +6467,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45870</v>
+        <v>45435</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6492,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6545,14 +6540,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45713</v>
+        <v>45279</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45146</v>
+        <v>45279</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6633,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6691,14 +6686,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45279</v>
+        <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6711,7 +6706,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45279</v>
+        <v>45899</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6779,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6837,14 +6832,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45271</v>
+        <v>45450</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6852,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6895,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6909,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44539</v>
+        <v>45142</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6925,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6968,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6982,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45685</v>
+        <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +6998,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7041,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7055,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45940</v>
+        <v>44550</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7071,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7114,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45348</v>
+        <v>45576</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7149,7 +7144,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7187,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7206,10 +7201,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46136</v>
+        <v>45265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7217,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7260,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7275,14 +7270,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45299</v>
+        <v>44934</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7290,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7333,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7347,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45777</v>
+        <v>45908</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7363,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7406,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7420,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44935</v>
+        <v>44988</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7441,7 +7436,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7479,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7498,10 +7493,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44934</v>
+        <v>44862</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7514,7 +7509,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7557,7 +7552,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7571,10 +7566,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45899</v>
+        <v>45338</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7586,8 +7581,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45898</v>
+        <v>45243</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45908</v>
+        <v>45344</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45677</v>
+        <v>45629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44616</v>
+        <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45637</v>
+        <v>45478</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7995,7 +7995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45098</v>
+        <v>45475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8068,7 +8068,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44934</v>
+        <v>45604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45196</v>
+        <v>45475</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45595</v>
+        <v>44616</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44631</v>
+        <v>45180</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8360,7 +8360,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46129</v>
+        <v>45260</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45142</v>
+        <v>45055</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8516,14 +8516,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45243</v>
+        <v>44644</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8589,14 +8589,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45478</v>
+        <v>45435</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45265</v>
+        <v>45943</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8681,8 +8681,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8725,7 +8730,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45943</v>
+        <v>45621</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8754,13 +8759,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8803,7 +8803,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45967</v>
+        <v>45688</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8832,8 +8832,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8876,7 +8881,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8890,10 +8895,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44979</v>
+        <v>45160</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8906,7 +8911,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8949,7 +8954,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8963,10 +8968,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45359</v>
+        <v>45196</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8979,7 +8984,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9022,7 +9027,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9039,7 +9044,7 @@
         <v>45358</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9052,7 +9057,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.5</v>
+        <v>12.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9112,7 +9117,7 @@
         <v>45947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9185,7 +9190,7 @@
         <v>45947</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9241,7 +9246,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9255,10 +9260,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45947</v>
+        <v>45728</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9271,7 +9276,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9314,7 +9319,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9328,10 +9333,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46157</v>
+        <v>45595</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9344,7 +9349,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9387,7 +9392,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9401,10 +9406,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45377</v>
+        <v>45358</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9417,7 +9422,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9460,7 +9465,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9474,10 +9479,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45898</v>
+        <v>45947</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9490,7 +9495,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9533,7 +9538,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9547,10 +9552,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45561</v>
+        <v>44565</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9563,7 +9568,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9606,7 +9611,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9620,10 +9625,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45246</v>
+        <v>45218</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9636,7 +9641,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9679,7 +9684,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9693,10 +9698,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45960</v>
+        <v>45638</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9709,7 +9714,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9752,7 +9757,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9762,14 +9767,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45960</v>
+        <v>45728</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9782,7 +9787,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>19.8</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9825,7 +9830,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9839,10 +9844,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45960</v>
+        <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9855,7 +9860,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9898,7 +9903,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9912,10 +9917,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45971</v>
+        <v>45960</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9928,7 +9933,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>19.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9971,7 +9976,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9985,10 +9990,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45979</v>
+        <v>45960</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10001,7 +10006,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10044,7 +10049,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10058,10 +10063,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45217</v>
+        <v>45569</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10073,8 +10078,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10117,7 +10127,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10131,10 +10141,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44551</v>
+        <v>45629</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10147,7 +10157,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10190,7 +10200,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10204,10 +10214,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44685</v>
+        <v>45226</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10220,7 +10230,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10263,7 +10273,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10277,10 +10287,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44685</v>
+        <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10293,7 +10303,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10336,7 +10346,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10350,10 +10360,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45221</v>
+        <v>45434</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10366,7 +10376,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10409,7 +10419,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10423,10 +10433,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45993</v>
+        <v>45629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10439,7 +10449,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>19.6</v>
+        <v>6.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10482,7 +10492,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10496,10 +10506,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45622</v>
+        <v>45308</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10512,7 +10522,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10555,7 +10565,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10569,10 +10579,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45994</v>
+        <v>45971</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10585,7 +10595,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10628,7 +10638,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10642,10 +10652,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45397</v>
+        <v>45348</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10658,7 +10668,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10701,7 +10711,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10715,10 +10725,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46171</v>
+        <v>44700</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10731,7 +10741,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10774,7 +10784,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10788,10 +10798,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45944</v>
+        <v>44893</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10804,7 +10814,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10847,7 +10857,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10861,10 +10871,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44895</v>
+        <v>44637</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10877,7 +10887,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10920,7 +10930,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10934,10 +10944,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44895</v>
+        <v>45232</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10950,7 +10960,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10993,7 +11003,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11007,10 +11017,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44565</v>
+        <v>45622</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11023,7 +11033,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>7.8</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11066,7 +11076,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11080,10 +11090,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46178</v>
+        <v>45728</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11096,7 +11106,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11139,7 +11149,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11153,10 +11163,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45840</v>
+        <v>45757</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11169,7 +11179,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11212,7 +11222,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11226,10 +11236,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46020</v>
+        <v>44934</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11242,7 +11252,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11285,7 +11295,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11299,10 +11309,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45629</v>
+        <v>45643</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11315,7 +11325,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11358,7 +11368,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11372,10 +11382,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45338</v>
+        <v>45601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11387,13 +11397,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11436,7 +11441,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11450,10 +11455,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44862</v>
+        <v>45979</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11466,7 +11471,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11509,7 +11514,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11523,10 +11528,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45116</v>
+        <v>45142</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11539,7 +11544,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11582,7 +11587,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11596,10 +11601,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45116</v>
+        <v>44973</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11612,7 +11617,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11655,7 +11660,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11669,10 +11674,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46038</v>
+        <v>45274</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11685,7 +11690,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11728,7 +11733,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11742,10 +11747,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46048</v>
+        <v>45142</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11757,13 +11762,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11806,7 +11806,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11820,10 +11820,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45142</v>
+        <v>45116</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11879,7 +11879,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44988</v>
+        <v>45116</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46196</v>
+        <v>44615</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12025,7 +12025,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12039,10 +12039,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45274</v>
+        <v>45265</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12098,7 +12098,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45629</v>
+        <v>45645</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12171,7 +12171,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46195</v>
+        <v>45569</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12200,8 +12200,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12244,7 +12249,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12258,10 +12263,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46195</v>
+        <v>45575</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12273,8 +12278,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12317,7 +12327,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12331,10 +12341,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44837</v>
+        <v>44771</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12390,7 +12400,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12404,10 +12414,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46198</v>
+        <v>45825</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12420,7 +12430,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12473,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12487,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46197</v>
+        <v>44642</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12503,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12536,7 +12546,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12550,10 +12560,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46069</v>
+        <v>45994</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12566,7 +12576,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12609,7 +12619,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12623,10 +12633,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45267</v>
+        <v>45832</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12682,7 +12692,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12696,10 +12706,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46073</v>
+        <v>45993</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12712,7 +12722,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5.5</v>
+        <v>19.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12755,7 +12765,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12769,10 +12779,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46073</v>
+        <v>45834</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12785,7 +12795,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12828,7 +12838,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12842,10 +12852,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46073</v>
+        <v>45320</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12858,7 +12868,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12901,7 +12911,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12915,10 +12925,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46073</v>
+        <v>45264</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12931,7 +12941,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12974,7 +12984,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12988,10 +12998,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46073</v>
+        <v>46038</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13004,7 +13014,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13047,7 +13057,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13061,10 +13071,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46091</v>
+        <v>44895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13077,7 +13087,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>10.9</v>
+        <v>2.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13120,7 +13130,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13134,10 +13144,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45677</v>
+        <v>44895</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13150,7 +13160,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13193,7 +13203,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13207,10 +13217,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46097</v>
+        <v>45253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13223,7 +13233,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13266,7 +13276,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13276,14 +13286,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45688</v>
+        <v>45786</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13295,13 +13305,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13344,7 +13349,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13358,10 +13363,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45541</v>
+        <v>46048</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13373,8 +13378,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13417,7 +13427,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13431,10 +13441,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44579</v>
+        <v>45840</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13447,7 +13457,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13490,7 +13500,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13504,10 +13514,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45601</v>
+        <v>45043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13520,7 +13530,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13563,7 +13573,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13577,10 +13587,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45202</v>
+        <v>45841</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13593,7 +13603,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13636,7 +13646,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13650,10 +13660,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46113</v>
+        <v>46020</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13665,13 +13675,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13714,7 +13719,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13728,10 +13733,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45266</v>
+        <v>45701</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13744,7 +13749,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13787,7 +13792,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13801,10 +13806,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45005</v>
+        <v>44895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13817,7 +13822,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13860,7 +13865,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13874,10 +13879,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45338</v>
+        <v>45561</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13889,13 +13894,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 39054-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13952,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45434</v>
+        <v>46287</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14011,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44900</v>
+        <v>45142</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14084,7 +14084,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 39380-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45142</v>
+        <v>46288</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14157,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14171,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44858</v>
+        <v>46069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14230,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45160</v>
+        <v>44900</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14303,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14317,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45910</v>
+        <v>46073</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14390,10 +14390,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45435</v>
+        <v>46073</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14459,14 +14459,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45435</v>
+        <v>46073</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14522,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46209</v>
+        <v>46073</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14595,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14609,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45320</v>
+        <v>46073</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14682,10 +14682,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45218</v>
+        <v>44935</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46212</v>
+        <v>44935</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45344</v>
+        <v>44539</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46045</v>
+        <v>44551</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14960,7 +14960,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44601</v>
+        <v>44979</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15033,7 +15033,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15043,14 +15043,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45253</v>
+        <v>45146</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15106,7 +15106,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45569</v>
+        <v>46091</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15135,13 +15135,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>10.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15184,7 +15179,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15194,14 +15189,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45146</v>
+        <v>46097</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15214,7 +15209,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15257,7 +15252,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15271,10 +15266,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45728</v>
+        <v>45359</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15287,7 +15282,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15330,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15344,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44642</v>
+        <v>45358</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15360,7 +15355,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15403,7 +15398,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15417,10 +15412,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44615</v>
+        <v>45230</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15433,7 +15428,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15476,7 +15471,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15490,10 +15485,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45450</v>
+        <v>45005</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15506,7 +15501,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15549,7 +15544,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15563,10 +15558,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45253</v>
+        <v>45667</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15579,7 +15574,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15622,7 +15617,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15636,10 +15631,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46265</v>
+        <v>45246</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15652,7 +15647,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15695,7 +15690,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15709,10 +15704,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46220</v>
+        <v>45221</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15725,7 +15720,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15768,7 +15763,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15782,10 +15777,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45308</v>
+        <v>45090</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15798,7 +15793,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15841,7 +15836,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15855,10 +15850,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46220</v>
+        <v>45435</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15871,7 +15866,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>15.5</v>
+        <v>0.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15914,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15928,10 +15923,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44893</v>
+        <v>46113</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15943,8 +15938,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,7 +15987,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44637</v>
+        <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16060,7 +16060,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16074,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44539</v>
+        <v>45701</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16133,7 +16133,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16147,10 +16147,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46220</v>
+        <v>45870</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16206,7 +16206,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16216,14 +16216,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45116</v>
+        <v>45870</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16279,7 +16279,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44812</v>
+        <v>45448</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16352,7 +16352,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16362,14 +16362,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44816</v>
+        <v>45299</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16425,7 +16425,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45237</v>
+        <v>45435</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16498,7 +16498,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44875</v>
+        <v>45358</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16581,14 +16581,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46227</v>
+        <v>44631</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16644,7 +16644,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16658,10 +16658,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44909</v>
+        <v>45677</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45701</v>
+        <v>46136</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16790,7 +16790,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16804,10 +16804,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44900</v>
+        <v>45628</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45226</v>
+        <v>45677</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16950,10 +16950,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44644</v>
+        <v>45271</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17009,7 +17009,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17023,10 +17023,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17096,10 +17096,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45180</v>
+        <v>45635</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17155,7 +17155,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17169,10 +17169,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45645</v>
+        <v>45940</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17228,7 +17228,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17242,10 +17242,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44463</v>
+        <v>45387</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45358</v>
+        <v>46129</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17374,7 +17374,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17388,10 +17388,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45260</v>
+        <v>45554</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17403,8 +17403,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17447,7 +17452,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17461,10 +17466,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45715</v>
+        <v>45569</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17482,7 +17487,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17525,7 +17530,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17539,10 +17544,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45043</v>
+        <v>45719</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17554,8 +17559,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17598,7 +17608,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 52237-2021</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17612,10 +17622,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44600</v>
+        <v>44463</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17628,7 +17638,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17671,7 +17681,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17685,10 +17695,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45719</v>
+        <v>44812</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17700,13 +17710,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17749,7 +17754,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17763,10 +17768,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45621</v>
+        <v>44655</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17779,7 +17784,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17822,7 +17827,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17836,10 +17841,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45569</v>
+        <v>45777</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17851,13 +17856,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17900,7 +17900,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 39054-2026</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17914,10 +17914,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46287</v>
+        <v>44600</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17973,7 +17973,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17987,10 +17987,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45387</v>
+        <v>44837</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18046,7 +18046,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18060,10 +18060,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45055</v>
+        <v>45253</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18119,7 +18119,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18133,10 +18133,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45728</v>
+        <v>45630</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18192,7 +18192,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18206,10 +18206,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44700</v>
+        <v>45265</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18265,7 +18265,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18279,10 +18279,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45630</v>
+        <v>45386</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18355,7 +18355,7 @@
         <v>45665</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45387</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18494,14 +18494,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45365</v>
+        <v>45967</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18557,7 +18557,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18571,10 +18571,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45713</v>
+        <v>45898</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18630,7 +18630,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18644,10 +18644,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45792</v>
+        <v>45377</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -18703,7 +18703,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18717,10 +18717,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45792</v>
+        <v>46157</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18790,10 +18790,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45685</v>
+        <v>46171</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18849,7 +18849,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18863,10 +18863,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45594</v>
+        <v>45944</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18922,7 +18922,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18936,10 +18936,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45475</v>
+        <v>46178</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18995,7 +18995,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19009,10 +19009,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45604</v>
+        <v>46195</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45475</v>
+        <v>46195</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19141,7 +19141,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19155,10 +19155,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45629</v>
+        <v>46197</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19228,10 +19228,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45629</v>
+        <v>46196</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19287,7 +19287,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19301,10 +19301,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45638</v>
+        <v>46198</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19360,7 +19360,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19370,14 +19370,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45728</v>
+        <v>46209</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19433,7 +19433,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19447,10 +19447,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45825</v>
+        <v>45910</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19506,7 +19506,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19520,10 +19520,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45832</v>
+        <v>46212</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19579,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19593,10 +19593,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45834</v>
+        <v>46045</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19662,14 +19662,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45786</v>
+        <v>46220</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.4</v>
+        <v>15.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45841</v>
+        <v>46265</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19812,10 +19812,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45667</v>
+        <v>46220</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45701</v>
+        <v>46220</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,24 +19944,24 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45323</v>
+        <v>46227</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20034,7 +20034,7 @@
         <v>44628</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20105,14 +20105,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45323</v>
+        <v>44601</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20124,8 +20124,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I265" t="n">
-        <v>38.9</v>
+        <v>1.4</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20168,7 +20173,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20178,14 +20183,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44601</v>
+        <v>45323</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20197,13 +20202,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20246,7 +20246,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20256,14 +20256,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45368</v>
+        <v>45706</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.9</v>
+        <v>32.6</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20319,7 +20319,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20336,7 +20336,7 @@
         <v>45323</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>7.9</v>
+        <v>38.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20392,148 +20392,221 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
+          <t>S 777-2024</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="n">
+        <v>45368</v>
+      </c>
+      <c r="E269" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="n">
+        <v>0</v>
+      </c>
+      <c r="T269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0</v>
+      </c>
+      <c r="V269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270" ht="15" customHeight="1">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>S 274-2024</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="E270" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="n">
+        <v>0</v>
+      </c>
+      <c r="V270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>S 280-2024</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C271" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D269" s="1" t="n">
+      <c r="D271" s="1" t="n">
         <v>45323</v>
       </c>
-      <c r="E269" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I269" t="n">
+      <c r="E271" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
         <v>16.3</v>
       </c>
-      <c r="J269" t="n">
-        <v>0</v>
-      </c>
-      <c r="K269" t="n">
-        <v>0</v>
-      </c>
-      <c r="L269" t="n">
-        <v>0</v>
-      </c>
-      <c r="M269" t="n">
-        <v>0</v>
-      </c>
-      <c r="N269" t="n">
-        <v>0</v>
-      </c>
-      <c r="O269" t="n">
-        <v>0</v>
-      </c>
-      <c r="P269" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0</v>
-      </c>
-      <c r="S269" t="n">
-        <v>0</v>
-      </c>
-      <c r="T269" t="n">
-        <v>0</v>
-      </c>
-      <c r="U269" t="n">
-        <v>0</v>
-      </c>
-      <c r="V269" s="2" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>S 510-2025</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D270" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E270" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I270" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="J270" t="n">
-        <v>0</v>
-      </c>
-      <c r="K270" t="n">
-        <v>0</v>
-      </c>
-      <c r="L270" t="n">
-        <v>0</v>
-      </c>
-      <c r="M270" t="n">
-        <v>0</v>
-      </c>
-      <c r="N270" t="n">
-        <v>0</v>
-      </c>
-      <c r="O270" t="n">
-        <v>0</v>
-      </c>
-      <c r="P270" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0</v>
-      </c>
-      <c r="S270" t="n">
-        <v>0</v>
-      </c>
-      <c r="T270" t="n">
-        <v>0</v>
-      </c>
-      <c r="U270" t="n">
-        <v>0</v>
-      </c>
-      <c r="V270" s="2" t="inlineStr"/>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="n">
+        <v>0</v>
+      </c>
+      <c r="T271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="n">
+        <v>0</v>
+      </c>
+      <c r="V271" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE271"/>
+  <dimension ref="A1:AE270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 56164-2024</t>
+          <t>A 11270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45624</v>
+        <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>15.7</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -740,10 +740,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -752,42 +752,46 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Härfågel</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
         <v/>
       </c>
     </row>
@@ -811,7 +815,7 @@
         <v>45870</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +920,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1004,7 +1008,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 11270-2025</t>
+          <t>A 33920-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,14 +1018,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45726</v>
+        <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1034,7 +1038,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1043,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1055,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -1074,46 +1078,46 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Härfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
         <v/>
       </c>
       <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 33920-2026</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1123,14 +1127,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46252</v>
+        <v>45624</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1143,7 +1147,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>15.7</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1152,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1167,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1176,46 +1180,42 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 33920-2026 artfynd.xlsx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 33920-2026 karta.png", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 33920-2026 georefererad karta.tif", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 33920-2026 FSC-klagomål.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 33920-2026 FSC-klagomål mail.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 33920-2026 tillsynsbegäran.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 33920-2026 tillsynsbegäran mail.docx", "A 33920-2026")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 33920-2026 prioriterade fågelarter.docx", "A 33920-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 9847-2022</t>
+          <t>A 34906-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44620</v>
+        <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34906-2022</t>
+          <t>A 9847-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44627</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46713-2022</t>
+          <t>A 42438-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44851</v>
+        <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>15.7</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46930-2022</t>
+          <t>A 46713-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2006,7 +2006,7 @@
         <v>44851</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>15.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 42438-2022</t>
+          <t>A 50987-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44831</v>
+        <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 50987-2022</t>
+          <t>A 46930-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44867</v>
+        <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3865-2022</t>
+          <t>A 54964-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44587</v>
+        <v>44474</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2281,7 +2281,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54964-2021</t>
+          <t>A 62992-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44474</v>
+        <v>44504</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 62992-2021</t>
+          <t>A 28253-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44504</v>
+        <v>44746</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28253-2022</t>
+          <t>A 3865-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44746</v>
+        <v>44587</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44858</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10503-2022</t>
+          <t>A 50985-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44623</v>
+        <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 50985-2022</t>
+          <t>A 5174-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44867</v>
+        <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 50984-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44601</v>
+        <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12173-2022</t>
+          <t>A 33171-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44636</v>
+        <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12175-2022</t>
+          <t>A 10503-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44636</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 12173-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3318,14 +3318,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45365</v>
+        <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5174-2022</t>
+          <t>A 12175-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44594</v>
+        <v>44636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 21085-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44816</v>
+        <v>44704</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21085-2022</t>
+          <t>A 9212-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44704</v>
+        <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9212-2022</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44616</v>
+        <v>45554</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3629,8 +3629,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3673,7 +3678,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3687,10 +3692,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45715</v>
+        <v>45435</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3702,13 +3707,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50984-2022</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44867</v>
+        <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33171-2022</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44785</v>
+        <v>45510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31967-2024</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45510</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45637</v>
+        <v>45358</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>12.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45687</v>
+        <v>45635</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45202</v>
+        <v>45386</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45267</v>
+        <v>45264</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44823</v>
+        <v>44973</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44579</v>
+        <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45359</v>
+        <v>45253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45338</v>
+        <v>45569</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44867</v>
+        <v>44935</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45176</v>
+        <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4705,7 +4705,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45713</v>
+        <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45253</v>
+        <v>45448</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45359</v>
+        <v>45435</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45792</v>
+        <v>44655</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45253</v>
+        <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5070,7 +5070,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44858</v>
+        <v>44771</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45594</v>
+        <v>45142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5226,14 +5226,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45792</v>
+        <v>45740</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45685</v>
+        <v>44823</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5362,7 +5362,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45098</v>
+        <v>45359</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44685</v>
+        <v>45358</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44685</v>
+        <v>45575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5537,8 +5537,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5581,7 +5586,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5595,10 +5600,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44539</v>
+        <v>45176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5611,7 +5616,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5659,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5673,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44900</v>
+        <v>45327</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5684,7 +5689,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5732,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45541</v>
+        <v>45230</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5757,7 +5762,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5800,7 +5805,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5817,7 +5822,7 @@
         <v>44895</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5830,7 +5835,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5878,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5887,10 +5892,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45327</v>
+        <v>45687</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5903,7 +5908,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5951,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5965,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45713</v>
+        <v>44867</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5981,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6024,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6038,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45146</v>
+        <v>45757</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6054,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6097,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6111,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45685</v>
+        <v>45576</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6127,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6170,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6175,14 +6180,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45740</v>
+        <v>45090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6200,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6243,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6257,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45397</v>
+        <v>45265</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6273,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44875</v>
+        <v>45713</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6346,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45116</v>
+        <v>45359</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6419,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6476,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45435</v>
+        <v>45870</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6487,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6540,14 +6545,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45279</v>
+        <v>45870</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45279</v>
+        <v>45146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6633,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45898</v>
+        <v>45940</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6706,7 +6711,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45899</v>
+        <v>44539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6779,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6832,14 +6837,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45450</v>
+        <v>45279</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6852,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6895,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45142</v>
+        <v>45279</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44909</v>
+        <v>45685</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6998,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7041,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7055,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44550</v>
+        <v>45348</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7071,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7114,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7124,14 +7129,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45576</v>
+        <v>45271</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7144,7 +7149,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7187,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7201,10 +7206,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45265</v>
+        <v>46136</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7217,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7260,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44934</v>
+        <v>45899</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7290,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7333,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7347,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45908</v>
+        <v>45898</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7363,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7406,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7420,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44988</v>
+        <v>44935</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7436,7 +7441,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7479,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7493,10 +7498,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44862</v>
+        <v>44934</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7509,7 +7514,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7552,7 +7557,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7562,14 +7567,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45338</v>
+        <v>45299</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7581,13 +7586,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45243</v>
+        <v>45908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45344</v>
+        <v>45677</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45629</v>
+        <v>44616</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45629</v>
+        <v>45637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45478</v>
+        <v>45098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7995,7 +7995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45475</v>
+        <v>44934</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8068,7 +8068,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45604</v>
+        <v>45777</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45475</v>
+        <v>45196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44616</v>
+        <v>45595</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45180</v>
+        <v>44631</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8360,7 +8360,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45260</v>
+        <v>45142</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45055</v>
+        <v>45243</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8516,14 +8516,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44644</v>
+        <v>45478</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8589,14 +8589,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45435</v>
+        <v>45265</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45943</v>
+        <v>44979</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8681,13 +8681,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8730,7 +8725,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45621</v>
+        <v>45943</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8759,8 +8754,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8803,7 +8803,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45688</v>
+        <v>45359</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8832,13 +8832,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8881,7 +8876,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8895,10 +8890,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45160</v>
+        <v>45358</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8911,7 +8906,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8954,7 +8949,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8968,10 +8963,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45196</v>
+        <v>45947</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9027,7 +9022,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9041,10 +9036,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45358</v>
+        <v>45947</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9057,7 +9052,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>12.2</v>
+        <v>0.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9100,7 +9095,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9117,7 +9112,7 @@
         <v>45947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9130,7 +9125,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9173,7 +9168,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9187,10 +9182,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45947</v>
+        <v>45561</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9203,7 +9198,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.2</v>
+        <v>7.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9246,7 +9241,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9260,10 +9255,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45728</v>
+        <v>45246</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9276,7 +9271,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9319,7 +9314,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9333,10 +9328,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45595</v>
+        <v>46129</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9349,7 +9344,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9392,7 +9387,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9406,10 +9401,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45358</v>
+        <v>45960</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9422,7 +9417,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9465,7 +9460,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9479,10 +9474,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45947</v>
+        <v>45960</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9495,7 +9490,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>19.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9538,7 +9533,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9552,10 +9547,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44565</v>
+        <v>45960</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9568,7 +9563,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9611,7 +9606,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9625,10 +9620,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45218</v>
+        <v>45971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9641,7 +9636,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9684,7 +9679,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9698,10 +9693,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45638</v>
+        <v>45217</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9714,7 +9709,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9757,7 +9752,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9767,14 +9762,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45728</v>
+        <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9787,7 +9782,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9830,7 +9825,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9844,10 +9839,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45217</v>
+        <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9860,7 +9855,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9903,7 +9898,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9917,10 +9912,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45960</v>
+        <v>45979</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9933,7 +9928,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>19.8</v>
+        <v>7.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9976,7 +9971,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9990,10 +9985,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45960</v>
+        <v>44685</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10006,7 +10001,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10049,7 +10044,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10063,10 +10058,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45569</v>
+        <v>45221</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10078,13 +10073,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10127,7 +10117,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10141,10 +10131,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45629</v>
+        <v>45622</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10157,7 +10147,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10200,7 +10190,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10214,10 +10204,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45226</v>
+        <v>45397</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10230,7 +10220,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10273,7 +10263,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10287,10 +10277,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45960</v>
+        <v>44895</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10303,7 +10293,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10346,7 +10336,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10360,10 +10350,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45434</v>
+        <v>44895</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10376,7 +10366,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10419,7 +10409,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10433,10 +10423,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45629</v>
+        <v>45993</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10449,7 +10439,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.6</v>
+        <v>19.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10492,7 +10482,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10506,10 +10496,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45308</v>
+        <v>45994</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10522,7 +10512,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10565,7 +10555,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10579,10 +10569,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45971</v>
+        <v>45967</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10595,7 +10585,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10638,7 +10628,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10652,10 +10642,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45348</v>
+        <v>44565</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10668,7 +10658,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10711,7 +10701,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10725,10 +10715,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44700</v>
+        <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10741,7 +10731,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10784,7 +10774,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10798,10 +10788,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44893</v>
+        <v>45377</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10814,7 +10804,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10857,7 +10847,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10871,10 +10861,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44637</v>
+        <v>45629</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10887,7 +10877,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10930,7 +10920,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10944,10 +10934,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45232</v>
+        <v>45840</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10960,7 +10950,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11003,7 +10993,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11017,10 +11007,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45622</v>
+        <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11033,7 +11023,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11076,7 +11066,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11090,10 +11080,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45728</v>
+        <v>46020</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11106,7 +11096,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11149,7 +11139,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11163,10 +11153,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45757</v>
+        <v>45338</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11178,8 +11168,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11222,7 +11217,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11236,10 +11231,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44934</v>
+        <v>44862</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11252,7 +11247,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11295,7 +11290,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11309,10 +11304,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45643</v>
+        <v>45116</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11325,7 +11320,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11368,7 +11363,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11382,10 +11377,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45601</v>
+        <v>45116</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11398,7 +11393,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11441,7 +11436,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11455,10 +11450,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45979</v>
+        <v>45142</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11471,7 +11466,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11514,7 +11509,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11528,10 +11523,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45142</v>
+        <v>46038</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11544,7 +11539,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11587,7 +11582,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11601,10 +11596,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44973</v>
+        <v>44988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11617,7 +11612,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11677,7 +11672,7 @@
         <v>45274</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11733,7 +11728,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11747,10 +11742,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45142</v>
+        <v>45629</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11763,7 +11758,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11806,7 +11801,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11820,10 +11815,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45116</v>
+        <v>46048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11835,8 +11830,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11879,7 +11879,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45116</v>
+        <v>44837</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11966,10 +11966,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44615</v>
+        <v>45267</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12025,7 +12025,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12039,10 +12039,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45265</v>
+        <v>46069</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12098,7 +12098,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45645</v>
+        <v>46073</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12171,7 +12171,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45569</v>
+        <v>46073</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12200,13 +12200,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12249,7 +12244,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12263,10 +12258,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45575</v>
+        <v>46073</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12278,13 +12273,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12327,7 +12317,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12341,10 +12331,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44771</v>
+        <v>46073</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12357,7 +12347,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12400,7 +12390,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12414,10 +12404,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45825</v>
+        <v>46073</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12430,7 +12420,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12473,7 +12463,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12487,10 +12477,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44642</v>
+        <v>45677</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12503,7 +12493,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12546,7 +12536,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12560,10 +12550,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45994</v>
+        <v>45688</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12575,8 +12565,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12619,7 +12614,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12633,10 +12628,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45832</v>
+        <v>45541</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12692,7 +12687,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12706,10 +12701,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45993</v>
+        <v>44579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12722,7 +12717,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>19.6</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12765,7 +12760,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 24715-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12779,10 +12774,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45834</v>
+        <v>46171</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12795,7 +12790,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12838,7 +12833,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 50604-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12852,10 +12847,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45320</v>
+        <v>45944</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12868,7 +12863,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12911,7 +12906,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12925,10 +12920,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45264</v>
+        <v>46091</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12941,7 +12936,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.2</v>
+        <v>10.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12984,7 +12979,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12998,10 +12993,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46038</v>
+        <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13014,7 +13009,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13057,7 +13052,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13071,10 +13066,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44895</v>
+        <v>46097</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13087,7 +13082,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13130,7 +13125,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13144,10 +13139,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44895</v>
+        <v>45601</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13160,7 +13155,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13203,7 +13198,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13217,10 +13212,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45253</v>
+        <v>45202</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13233,7 +13228,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13276,7 +13271,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13286,14 +13281,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45786</v>
+        <v>45266</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13306,7 +13301,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13349,7 +13344,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13363,10 +13358,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46048</v>
+        <v>46113</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13380,11 +13375,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13427,7 +13422,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13441,10 +13436,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45840</v>
+        <v>45005</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13500,7 +13495,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13514,10 +13509,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45043</v>
+        <v>45338</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13529,8 +13524,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13573,7 +13573,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13587,10 +13587,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45841</v>
+        <v>45434</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13660,10 +13660,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46020</v>
+        <v>44900</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13719,7 +13719,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 6977-2025</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45701</v>
+        <v>45142</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13792,7 +13792,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13806,10 +13806,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44895</v>
+        <v>44858</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13865,7 +13865,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13879,10 +13879,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45561</v>
+        <v>45160</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 39054-2026</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13952,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46287</v>
+        <v>45435</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14011,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14021,14 +14021,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45142</v>
+        <v>45435</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14084,7 +14084,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39380-2026</t>
+          <t>A 28195-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46288</v>
+        <v>46196</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14157,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14171,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46069</v>
+        <v>46195</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14230,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44900</v>
+        <v>46195</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14303,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14317,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46073</v>
+        <v>46198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14390,10 +14390,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46073</v>
+        <v>46197</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14463,10 +14463,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46073</v>
+        <v>45320</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14522,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46073</v>
+        <v>45218</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14595,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14609,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46073</v>
+        <v>45344</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7.1</v>
+        <v>2.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14682,10 +14682,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44935</v>
+        <v>44601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44935</v>
+        <v>45253</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44539</v>
+        <v>45569</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14843,8 +14843,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14887,7 +14892,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14897,14 +14902,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44551</v>
+        <v>45146</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14917,7 +14922,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14960,7 +14965,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14974,10 +14979,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44979</v>
+        <v>45728</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14990,7 +14995,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15033,7 +15038,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15043,14 +15048,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45146</v>
+        <v>44642</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15063,7 +15068,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15106,7 +15111,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15120,10 +15125,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46091</v>
+        <v>44615</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15136,7 +15141,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>10.9</v>
+        <v>2.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15179,7 +15184,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15193,10 +15198,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46097</v>
+        <v>45450</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15209,7 +15214,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15252,7 +15257,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15266,10 +15271,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45359</v>
+        <v>45253</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15282,7 +15287,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15325,7 +15330,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15339,10 +15344,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45358</v>
+        <v>45910</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15355,7 +15360,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15398,7 +15403,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15412,10 +15417,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45230</v>
+        <v>46209</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15428,7 +15433,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15471,7 +15476,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15485,10 +15490,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45005</v>
+        <v>45308</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15501,7 +15506,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15544,7 +15549,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15558,10 +15563,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45667</v>
+        <v>44893</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15574,7 +15579,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15617,7 +15622,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15631,10 +15636,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45246</v>
+        <v>44637</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15647,7 +15652,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15690,7 +15695,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15704,10 +15709,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45221</v>
+        <v>44539</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15720,7 +15725,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15763,7 +15768,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15777,10 +15782,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45090</v>
+        <v>46212</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15793,7 +15798,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15836,7 +15841,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15850,10 +15855,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45435</v>
+        <v>45116</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15866,7 +15871,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15909,7 +15914,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15923,10 +15928,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46113</v>
+        <v>46045</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15938,13 +15943,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,7 +15987,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45237</v>
+        <v>44812</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16060,7 +16060,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16074,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45701</v>
+        <v>44816</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16133,7 +16133,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16147,10 +16147,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45870</v>
+        <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16206,7 +16206,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16216,14 +16216,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45870</v>
+        <v>44875</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16279,7 +16279,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45448</v>
+        <v>44909</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16352,7 +16352,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16362,14 +16362,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45299</v>
+        <v>46265</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16425,7 +16425,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 6977-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45435</v>
+        <v>45701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45358</v>
+        <v>46220</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16581,14 +16581,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44631</v>
+        <v>44900</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16644,7 +16644,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16658,10 +16658,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45677</v>
+        <v>45226</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16717,7 +16717,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46136</v>
+        <v>46220</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.3</v>
+        <v>15.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16790,7 +16790,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16804,10 +16804,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45628</v>
+        <v>46220</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16873,14 +16873,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45677</v>
+        <v>44644</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16946,14 +16946,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45271</v>
+        <v>45265</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17009,7 +17009,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17023,10 +17023,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45266</v>
+        <v>45180</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17096,10 +17096,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45635</v>
+        <v>45645</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17155,7 +17155,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17169,10 +17169,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45940</v>
+        <v>45358</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17242,10 +17242,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45387</v>
+        <v>46227</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46129</v>
+        <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17374,7 +17374,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17388,10 +17388,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45554</v>
+        <v>45715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17405,11 +17405,11 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17452,7 +17452,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17466,10 +17466,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45569</v>
+        <v>45043</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17481,13 +17481,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17530,7 +17525,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17544,10 +17539,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45719</v>
+        <v>44600</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17559,13 +17554,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17608,7 +17598,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 52237-2021</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17622,10 +17612,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44463</v>
+        <v>45719</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17637,8 +17627,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17681,7 +17676,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17695,10 +17690,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44812</v>
+        <v>45621</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17711,7 +17706,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17754,7 +17749,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17768,10 +17763,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44655</v>
+        <v>45569</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17783,8 +17778,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17841,10 +17841,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45777</v>
+        <v>45387</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17900,7 +17900,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17914,10 +17914,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44600</v>
+        <v>45055</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17973,7 +17973,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17987,10 +17987,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44837</v>
+        <v>45728</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18046,7 +18046,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18060,10 +18060,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45253</v>
+        <v>44700</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18136,7 +18136,7 @@
         <v>45630</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18206,10 +18206,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45265</v>
+        <v>45665</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18265,7 +18265,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18279,10 +18279,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18338,7 +18338,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18348,14 +18348,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45665</v>
+        <v>45365</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18411,7 +18411,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 39054-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18425,10 +18425,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45387</v>
+        <v>46287</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18484,7 +18484,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18498,10 +18498,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45967</v>
+        <v>45713</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18557,7 +18557,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18571,10 +18571,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45898</v>
+        <v>45792</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18630,7 +18630,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18644,10 +18644,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45377</v>
+        <v>45792</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -18703,7 +18703,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 39380-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18717,10 +18717,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46157</v>
+        <v>46288</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18776,7 +18776,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 24715-2026</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18790,10 +18790,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46171</v>
+        <v>45685</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18849,7 +18849,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 50604-2025</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18863,10 +18863,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45944</v>
+        <v>45594</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18922,7 +18922,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18936,10 +18936,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46178</v>
+        <v>45475</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18995,7 +18995,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19009,10 +19009,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46195</v>
+        <v>45604</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46195</v>
+        <v>45475</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19141,7 +19141,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19155,10 +19155,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46197</v>
+        <v>45629</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 28195-2026</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19228,10 +19228,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46196</v>
+        <v>45629</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19287,7 +19287,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19301,10 +19301,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46198</v>
+        <v>45638</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19360,7 +19360,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19370,14 +19370,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46209</v>
+        <v>45728</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19433,7 +19433,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19447,10 +19447,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45910</v>
+        <v>45825</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19506,7 +19506,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19520,10 +19520,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46212</v>
+        <v>45832</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -19579,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19593,10 +19593,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46045</v>
+        <v>45834</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19662,14 +19662,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46220</v>
+        <v>45786</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>15.5</v>
+        <v>0.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46265</v>
+        <v>45841</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19812,10 +19812,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46220</v>
+        <v>45667</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46220</v>
+        <v>45701</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,24 +19944,24 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46227</v>
+        <v>45323</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20034,7 +20034,7 @@
         <v>44628</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20105,14 +20105,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44601</v>
+        <v>45323</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20124,13 +20124,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I265" t="n">
-        <v>1.4</v>
+        <v>38.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20173,7 +20168,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20183,14 +20178,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45323</v>
+        <v>44601</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20202,8 +20197,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I266" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20246,7 +20246,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 510-2025</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20256,14 +20256,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45706</v>
+        <v>45368</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>32.6</v>
+        <v>2.9</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20319,7 +20319,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20336,7 +20336,7 @@
         <v>45323</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>38.9</v>
+        <v>7.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20392,7 +20392,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20402,14 +20402,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45368</v>
+        <v>45323</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.9</v>
+        <v>16.3</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20462,10 +20462,10 @@
       </c>
       <c r="V269" s="2" t="inlineStr"/>
     </row>
-    <row r="270" ht="15" customHeight="1">
+    <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20479,10 +20479,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45323</v>
+        <v>45706</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>7.9</v>
+        <v>32.6</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -20534,79 +20534,6 @@
         <v>0</v>
       </c>
       <c r="V270" s="2" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>S 280-2024</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D271" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E271" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I271" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J271" t="n">
-        <v>0</v>
-      </c>
-      <c r="K271" t="n">
-        <v>0</v>
-      </c>
-      <c r="L271" t="n">
-        <v>0</v>
-      </c>
-      <c r="M271" t="n">
-        <v>0</v>
-      </c>
-      <c r="N271" t="n">
-        <v>0</v>
-      </c>
-      <c r="O271" t="n">
-        <v>0</v>
-      </c>
-      <c r="P271" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0</v>
-      </c>
-      <c r="S271" t="n">
-        <v>0</v>
-      </c>
-      <c r="T271" t="n">
-        <v>0</v>
-      </c>
-      <c r="U271" t="n">
-        <v>0</v>
-      </c>
-      <c r="V271" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 54293-2023</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45232</v>
+        <v>45624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -647,364 +647,360 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 36627-2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 36627-2025 artfynd.xlsx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 36627-2025 karta.png", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 36627-2025 georefererad karta.tif", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 36627-2025 FSC-klagomål.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 36627-2025 FSC-klagomål mail.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 36627-2025 tillsynsbegäran.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 36627-2025 tillsynsbegäran mail.docx", "A 36627-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 60881-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 60881-2025 artfynd.xlsx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 60881-2025 karta.png", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 60881-2025 georefererad karta.tif", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 60881-2025 FSC-klagomål.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 60881-2025 FSC-klagomål mail.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 60881-2025 tillsynsbegäran.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 60881-2025 tillsynsbegäran mail.docx", "A 60881-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 54293-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45232</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 11270-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45726</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Härfågel</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 36627-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45870</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 36627-2025 artfynd.xlsx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 36627-2025 karta.png", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 36627-2025 georefererad karta.tif", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 36627-2025 FSC-klagomål.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 36627-2025 FSC-klagomål mail.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 36627-2025 tillsynsbegäran.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 36627-2025 tillsynsbegäran mail.docx", "A 36627-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60881-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>VARA</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Rostfläck</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 60881-2025 artfynd.xlsx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 60881-2025 karta.png", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 60881-2025 georefererad karta.tif", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 60881-2025 FSC-klagomål.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 60881-2025 FSC-klagomål mail.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 60881-2025 tillsynsbegäran.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 60881-2025 tillsynsbegäran mail.docx", "A 60881-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1025,7 +1021,7 @@
         <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1117,7 +1113,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 56164-2024</t>
+          <t>A 11270-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1131,10 +1127,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45624</v>
+        <v>45726</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,7 +1143,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>15.7</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1168,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1180,42 +1176,46 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Härfågel</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
         <v/>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62540-2021</t>
+          <t>A 10831-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44503</v>
+        <v>44627</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10831-2022</t>
+          <t>A 62540-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44627</v>
+        <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46713-2022</t>
+          <t>A 50987-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44851</v>
+        <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50987-2022</t>
+          <t>A 46713-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44867</v>
+        <v>44851</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54964-2021</t>
+          <t>A 3865-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44474</v>
+        <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2281,7 +2281,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 62992-2021</t>
+          <t>A 54964-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44504</v>
+        <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28253-2022</t>
+          <t>A 62992-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44746</v>
+        <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3865-2022</t>
+          <t>A 28253-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44587</v>
+        <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44858</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12173-2022</t>
+          <t>A 21085-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44636</v>
+        <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12175-2022</t>
+          <t>A 12173-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3398,7 +3398,7 @@
         <v>44636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21085-2022</t>
+          <t>A 12175-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44704</v>
+        <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 40224-2024</t>
+          <t>A 62313-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45554</v>
+        <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3629,13 +3629,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3678,7 +3673,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20443-2024</t>
+          <t>A 6454-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3692,10 +3687,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45435</v>
+        <v>45338</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3707,8 +3702,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56856-2024</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45628</v>
+        <v>44867</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31967-2024</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45510</v>
+        <v>45359</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>9.1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>45253</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 9410-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>12.2</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58514-2024</t>
+          <t>A 49041-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45635</v>
+        <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13235-2024</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45386</v>
+        <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 61687-2023</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45264</v>
+        <v>45327</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 14690-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44973</v>
+        <v>45397</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45253</v>
+        <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59335-2023</t>
+          <t>A 33299-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45253</v>
+        <v>45116</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45569</v>
+        <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4510,13 +4510,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4559,7 +4554,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1152-2023</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4573,10 +4568,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44935</v>
+        <v>45435</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4589,7 +4584,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4632,7 +4627,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54201-2023</t>
+          <t>A 64317-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4642,14 +4637,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45232</v>
+        <v>45279</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4662,7 +4657,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4705,7 +4700,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 73168-2021</t>
+          <t>A 64330-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4719,10 +4714,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44550</v>
+        <v>45279</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4735,7 +4730,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4778,7 +4773,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22901-2024</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45448</v>
+        <v>46020</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4808,7 +4803,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4851,7 +4846,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4865,10 +4860,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45435</v>
+        <v>45594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4881,7 +4876,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14593-2022</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44655</v>
+        <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 23065-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44895</v>
+        <v>45450</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5027,7 +5022,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44771</v>
+        <v>45685</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35056-2023</t>
+          <t>A 961-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45142</v>
+        <v>44934</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14116-2025</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5226,14 +5221,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45740</v>
+        <v>44539</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5246,7 +5241,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5289,7 +5284,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40331-2022</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5303,10 +5298,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44823</v>
+        <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5319,7 +5314,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5362,7 +5357,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9413-2024</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5376,10 +5371,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45359</v>
+        <v>45146</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5392,7 +5387,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5430,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9450-2024</t>
+          <t>A 4289-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5444,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45358</v>
+        <v>45685</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5460,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5503,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5517,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45575</v>
+        <v>46038</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5537,13 +5532,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5586,7 +5576,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41690-2023</t>
+          <t>A 10728-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5600,10 +5590,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45176</v>
+        <v>44988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5616,7 +5606,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5659,7 +5649,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 49820-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5673,10 +5663,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45327</v>
+        <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5689,7 +5679,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5732,7 +5722,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53719-2023</t>
+          <t>A 41286-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5746,10 +5736,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45230</v>
+        <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5762,7 +5752,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5805,7 +5795,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57253-2022</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5819,10 +5809,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44895</v>
+        <v>45899</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5835,7 +5825,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5878,7 +5868,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4622-2025</t>
+          <t>A 4701-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5892,10 +5882,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45687</v>
+        <v>46048</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5907,8 +5897,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5951,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5965,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44867</v>
+        <v>45908</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5981,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6024,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17543-2025</t>
+          <t>A 9404-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6038,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45757</v>
+        <v>44616</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6054,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6097,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45303-2024</t>
+          <t>A 60819-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6111,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45576</v>
+        <v>45260</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6127,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6170,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25764-2023</t>
+          <t>A 8949-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6184,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45090</v>
+        <v>46069</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6200,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6243,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61738-2023</t>
+          <t>A 20240-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6257,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45265</v>
+        <v>45055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6273,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6316,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 9881-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6330,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45713</v>
+        <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6389,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 9919-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45359</v>
+        <v>46073</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36630-2025</t>
+          <t>A 9923-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45870</v>
+        <v>46073</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6492,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36632-2025</t>
+          <t>A 9925-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6545,14 +6540,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45870</v>
+        <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 9928-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45146</v>
+        <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6633,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49863-2025</t>
+          <t>A 4812-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45940</v>
+        <v>45688</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6710,8 +6705,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44539</v>
+        <v>45358</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>12.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6837,14 +6837,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45279</v>
+        <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45279</v>
+        <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4289-2025</t>
+          <t>A 12007-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45685</v>
+        <v>45728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 49391-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45348</v>
+        <v>45595</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.5</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62775-2023</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45271</v>
+        <v>45475</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20022-2026</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46136</v>
+        <v>45604</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 12700-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45899</v>
+        <v>46091</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>10.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41286-2025</t>
+          <t>A 13710-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45898</v>
+        <v>46097</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1141-2023</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44935</v>
+        <v>45475</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44934</v>
+        <v>45943</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7513,8 +7513,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7557,7 +7562,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 579-2024</t>
+          <t>A 50812-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7567,14 +7572,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45299</v>
+        <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7587,7 +7592,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7630,7 +7635,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 43624-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7644,10 +7649,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45908</v>
+        <v>45569</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7659,8 +7664,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7703,7 +7713,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2680-2025</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7717,10 +7727,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45677</v>
+        <v>45947</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7733,7 +7743,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7776,7 +7786,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7790,10 +7800,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44616</v>
+        <v>45947</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7806,7 +7816,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7849,7 +7859,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 59314-2024</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7863,10 +7873,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45637</v>
+        <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7879,7 +7889,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7922,7 +7932,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 27845-2023</t>
+          <t>A 20196-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7936,10 +7946,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45098</v>
+        <v>45434</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7952,7 +7962,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7995,7 +8005,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 16754-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8009,10 +8019,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44934</v>
+        <v>46113</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8024,8 +8034,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8068,7 +8083,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20911-2025</t>
+          <t>A 1980-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8082,10 +8097,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45777</v>
+        <v>45308</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8098,7 +8113,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8141,7 +8156,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46137-2023</t>
+          <t>A 7655-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8155,10 +8170,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45196</v>
+        <v>45348</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8171,7 +8186,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8214,7 +8229,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 20536-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8228,10 +8243,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45595</v>
+        <v>44700</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8244,7 +8259,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8287,7 +8302,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11589-2022</t>
+          <t>A 56456-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8297,14 +8312,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44631</v>
+        <v>44893</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8317,7 +8332,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8360,7 +8375,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35059-2023</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8374,10 +8389,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45142</v>
+        <v>45960</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8390,7 +8405,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>19.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8433,7 +8448,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56654-2023</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8447,10 +8462,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45243</v>
+        <v>45960</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8463,7 +8478,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8506,7 +8521,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28851-2024</t>
+          <t>A 55667-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8520,10 +8535,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45478</v>
+        <v>45622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8536,7 +8551,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8579,7 +8594,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61740-2023</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8593,10 +8608,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45265</v>
+        <v>45960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8609,7 +8624,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8652,7 +8667,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9013-2023</t>
+          <t>A 962-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8666,10 +8681,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44979</v>
+        <v>44934</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8682,7 +8697,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8725,7 +8740,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8739,10 +8754,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45943</v>
+        <v>45643</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8754,13 +8769,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8803,7 +8813,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 50673-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8817,10 +8827,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45359</v>
+        <v>45601</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8833,7 +8843,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8876,7 +8886,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 9216-2024</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8890,10 +8900,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45358</v>
+        <v>45971</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8906,7 +8916,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8949,7 +8959,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8963,10 +8973,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45947</v>
+        <v>44973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9022,7 +9032,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 35042-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9036,10 +9046,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45947</v>
+        <v>45142</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9052,7 +9062,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9095,7 +9105,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 33300-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9109,10 +9119,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45947</v>
+        <v>45116</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9125,7 +9135,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9168,7 +9178,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 42038-2024</t>
+          <t>A 33301-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9182,10 +9192,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45561</v>
+        <v>45116</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9198,7 +9208,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9241,7 +9251,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57759-2023</t>
+          <t>A 61269-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9255,10 +9265,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45246</v>
+        <v>45645</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9271,7 +9281,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9314,7 +9324,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18836-2026</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9328,10 +9338,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46129</v>
+        <v>45569</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9343,8 +9353,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9387,7 +9402,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9401,10 +9416,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45960</v>
+        <v>45575</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9416,8 +9431,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9460,7 +9480,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 57260-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9474,10 +9494,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45960</v>
+        <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9490,7 +9510,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>19.8</v>
+        <v>7.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9533,7 +9553,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9547,10 +9567,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45960</v>
+        <v>44771</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9606,7 +9626,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 12938-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9620,10 +9640,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45971</v>
+        <v>44642</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9636,7 +9656,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9679,7 +9699,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 579-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9689,14 +9709,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45217</v>
+        <v>45299</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9709,7 +9729,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9752,7 +9772,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 73305-2021</t>
+          <t>A 20022-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9766,10 +9786,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44551</v>
+        <v>46136</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9782,7 +9802,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9825,7 +9845,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 18224-2022</t>
+          <t>A 60216-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9839,10 +9859,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44685</v>
+        <v>45994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9855,7 +9875,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9898,7 +9918,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 57260-2025</t>
+          <t>A 6517-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9912,10 +9932,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45979</v>
+        <v>44601</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9928,7 +9948,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9971,7 +9991,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18244-2022</t>
+          <t>A 60029-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9985,10 +10005,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44685</v>
+        <v>45993</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10001,7 +10021,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10044,7 +10064,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 51467-2023</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10058,10 +10078,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45221</v>
+        <v>45638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10074,7 +10094,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10117,7 +10137,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10127,14 +10147,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45622</v>
+        <v>45728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10147,7 +10167,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10190,7 +10210,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 49863-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10204,10 +10224,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45397</v>
+        <v>45940</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10220,7 +10240,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10263,7 +10283,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 57256-2022</t>
+          <t>A 38920-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10277,10 +10297,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44895</v>
+        <v>44816</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10293,7 +10313,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10336,7 +10356,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 57257-2022</t>
+          <t>A 9380-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10350,10 +10370,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44895</v>
+        <v>45715</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10365,8 +10385,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10409,7 +10434,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60029-2025</t>
+          <t>A 18836-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10423,10 +10448,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45993</v>
+        <v>46129</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10439,7 +10464,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>19.6</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10482,7 +10507,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 60216-2025</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10496,10 +10521,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45994</v>
+        <v>45510</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10512,7 +10537,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10555,7 +10580,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 54997-2025</t>
+          <t>A 59314-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10569,10 +10594,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45967</v>
+        <v>45637</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10585,7 +10610,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10628,7 +10653,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 365-2022</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10642,10 +10667,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44565</v>
+        <v>45687</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10701,7 +10726,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22721-2026</t>
+          <t>A 47332-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10715,10 +10740,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46157</v>
+        <v>45202</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10731,7 +10756,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10774,7 +10799,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12026-2024</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10788,10 +10813,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45377</v>
+        <v>44823</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10804,7 +10829,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10847,7 +10872,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 57303-2024</t>
+          <t>A 2452-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10861,10 +10886,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45629</v>
+        <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10877,7 +10902,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10920,7 +10945,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 20911-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10934,10 +10959,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45840</v>
+        <v>45777</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10950,7 +10975,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10993,7 +11018,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 41281-2025</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11007,10 +11032,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45898</v>
+        <v>45825</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11023,7 +11048,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11066,7 +11091,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11080,10 +11105,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46020</v>
+        <v>45176</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11096,7 +11121,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11139,7 +11164,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11153,10 +11178,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45338</v>
+        <v>45832</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11168,13 +11193,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11217,7 +11237,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11231,10 +11251,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44862</v>
+        <v>45253</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11247,7 +11267,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11290,7 +11310,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 27845-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11304,10 +11324,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45116</v>
+        <v>45098</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11320,7 +11340,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11363,7 +11383,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 18224-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11377,10 +11397,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45116</v>
+        <v>44685</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11393,7 +11413,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11436,7 +11456,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11450,10 +11470,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45142</v>
+        <v>45834</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11466,7 +11486,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11509,7 +11529,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 18244-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11523,10 +11543,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46038</v>
+        <v>44685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11539,7 +11559,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11582,7 +11602,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 59786-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11596,10 +11616,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44988</v>
+        <v>44900</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11612,7 +11632,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11655,7 +11675,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 63426-2023</t>
+          <t>A 37726-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11669,10 +11689,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45274</v>
+        <v>45541</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11728,7 +11748,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57420-2024</t>
+          <t>A 54997-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11742,10 +11762,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45629</v>
+        <v>45967</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11758,7 +11778,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11801,7 +11821,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 41281-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11815,10 +11835,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46048</v>
+        <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11830,13 +11850,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11879,7 +11894,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 43754-2022</t>
+          <t>A 12026-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11893,10 +11908,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44837</v>
+        <v>45377</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11952,7 +11967,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 22721-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11966,10 +11981,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45267</v>
+        <v>46157</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11982,7 +11997,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12025,7 +12040,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12035,14 +12050,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46069</v>
+        <v>45740</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12055,7 +12070,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12098,7 +12113,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12108,14 +12123,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46073</v>
+        <v>45786</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12128,7 +12143,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12171,7 +12186,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12185,10 +12200,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46073</v>
+        <v>45841</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12201,7 +12216,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12244,7 +12259,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 52778-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12258,10 +12273,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46073</v>
+        <v>44875</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12274,7 +12289,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12317,7 +12332,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12331,10 +12346,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46073</v>
+        <v>45142</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12347,7 +12362,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12390,7 +12405,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 59946-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12404,10 +12419,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46073</v>
+        <v>44909</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12420,7 +12435,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12478,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 2781-2025</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12492,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45677</v>
+        <v>44550</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12508,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12536,7 +12551,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12550,10 +12565,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45688</v>
+        <v>45667</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12565,13 +12580,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12614,7 +12624,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37726-2024</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12628,10 +12638,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45541</v>
+        <v>45576</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12644,7 +12654,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12687,7 +12697,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 2452-2022</t>
+          <t>A 61737-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12701,10 +12711,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44579</v>
+        <v>45265</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12717,7 +12727,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12777,7 +12787,7 @@
         <v>46171</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12850,7 +12860,7 @@
         <v>45944</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12906,7 +12916,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12920,10 +12930,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46091</v>
+        <v>45701</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12936,7 +12946,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12979,7 +12989,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25827-2026</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12993,10 +13003,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46178</v>
+        <v>45870</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13009,7 +13019,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13052,7 +13062,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13062,14 +13072,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46097</v>
+        <v>45870</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13082,7 +13092,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13125,7 +13135,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 25827-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13139,10 +13149,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45601</v>
+        <v>46178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13155,7 +13165,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13198,7 +13208,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 47332-2023</t>
+          <t>A 56654-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13212,10 +13222,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45202</v>
+        <v>45243</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13228,7 +13238,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13271,7 +13281,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 61879-2023</t>
+          <t>A 7238-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13285,10 +13295,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45266</v>
+        <v>45344</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13301,7 +13311,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13344,7 +13354,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 28851-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13358,10 +13368,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46113</v>
+        <v>45478</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13373,13 +13383,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13422,7 +13427,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 13481-2023</t>
+          <t>A 42427-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13436,10 +13441,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45005</v>
+        <v>45180</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13452,7 +13457,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13495,7 +13500,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 6453-2024</t>
+          <t>A 27980-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13509,10 +13514,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45338</v>
+        <v>46195</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13524,13 +13529,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13573,7 +13573,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 28168-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13587,10 +13587,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45434</v>
+        <v>46195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59786-2022</t>
+          <t>A 13194-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13656,14 +13656,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44900</v>
+        <v>44644</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13719,7 +13719,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 35035-2023</t>
+          <t>A 20439-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13729,14 +13729,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45142</v>
+        <v>45435</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13792,7 +13792,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 55356-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13806,10 +13806,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44858</v>
+        <v>45621</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13865,7 +13865,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37917-2023</t>
+          <t>A 28524-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13879,10 +13879,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45160</v>
+        <v>46197</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20433-2024</t>
+          <t>A 37917-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13952,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45435</v>
+        <v>45160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14011,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 20439-2024</t>
+          <t>A 46137-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14021,14 +14021,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45435</v>
+        <v>45196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14101,7 +14101,7 @@
         <v>46196</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28168-2026</t>
+          <t>A 28706-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14171,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14230,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 27980-2026</t>
+          <t>A 9218-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14244,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46195</v>
+        <v>45358</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14303,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 28706-2026</t>
+          <t>A 365-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14317,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46198</v>
+        <v>44565</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28524-2026</t>
+          <t>A 50909-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14390,10 +14390,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46197</v>
+        <v>45218</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3522-2024</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14459,14 +14459,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45320</v>
+        <v>45271</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14522,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 50909-2023</t>
+          <t>A 57303-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45218</v>
+        <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14595,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 7238-2024</t>
+          <t>A 30468-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14609,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45344</v>
+        <v>46209</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 6517-2022</t>
+          <t>A 52918-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14682,10 +14682,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44601</v>
+        <v>45226</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 59272-2023</t>
+          <t>A 43216-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45253</v>
+        <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 43620-2024</t>
+          <t>A 57420-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45569</v>
+        <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14843,13 +14843,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14892,7 +14887,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 35608-2023</t>
+          <t>A 12333-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14902,14 +14897,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45146</v>
+        <v>44637</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14922,7 +14917,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14965,7 +14960,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14979,10 +14974,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45728</v>
+        <v>45232</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14995,7 +14990,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15038,7 +15033,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 12938-2022</t>
+          <t>A 30884-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15052,10 +15047,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44642</v>
+        <v>46212</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15068,7 +15063,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15111,7 +15106,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 9108-2022</t>
+          <t>A 12016-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15125,10 +15120,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44615</v>
+        <v>45728</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15141,7 +15136,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15184,7 +15179,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15198,10 +15193,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45450</v>
+        <v>45757</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15214,7 +15209,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15257,7 +15252,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 59266-2023</t>
+          <t>A 4278-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15271,10 +15266,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45253</v>
+        <v>46045</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15287,7 +15282,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15330,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 43216-2025</t>
+          <t>A 35035-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15344,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45910</v>
+        <v>45142</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15360,7 +15355,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15403,7 +15398,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30468-2026</t>
+          <t>A 63426-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15417,10 +15412,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46209</v>
+        <v>45274</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15433,7 +15428,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15476,7 +15471,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 9108-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15490,10 +15485,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45308</v>
+        <v>44615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15506,7 +15501,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15549,7 +15544,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15563,10 +15558,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44893</v>
+        <v>45265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15579,7 +15574,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15622,7 +15617,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 12333-2022</t>
+          <t>A 31419-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15636,10 +15631,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44637</v>
+        <v>46220</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15652,7 +15647,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.4</v>
+        <v>15.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15695,7 +15690,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 35817-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15709,10 +15704,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44539</v>
+        <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15725,7 +15720,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15768,7 +15763,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30884-2026</t>
+          <t>A 31440-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15782,10 +15777,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46212</v>
+        <v>46220</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15798,7 +15793,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15841,7 +15836,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 3522-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15855,10 +15850,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45116</v>
+        <v>45320</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15871,7 +15866,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15914,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 4278-2026</t>
+          <t>A 31438-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15928,10 +15923,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46045</v>
+        <v>46220</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15944,7 +15939,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,7 +15982,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 38160-2022</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16001,10 +15996,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44812</v>
+        <v>45264</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16017,7 +16012,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16060,7 +16055,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 38920-2022</t>
+          <t>A 31733-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16069,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44816</v>
+        <v>46227</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16085,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16133,7 +16128,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 55296-2023</t>
+          <t>A 57256-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16147,10 +16142,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45237</v>
+        <v>44895</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16163,7 +16158,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16206,7 +16201,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 52778-2022</t>
+          <t>A 57257-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16220,10 +16215,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44875</v>
+        <v>44895</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16236,7 +16231,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16279,7 +16274,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 59946-2022</t>
+          <t>A 59266-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16293,10 +16288,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44909</v>
+        <v>45253</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16309,7 +16304,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16352,7 +16347,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 35817-2026</t>
+          <t>A 18691-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16366,10 +16361,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46265</v>
+        <v>45043</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16382,7 +16377,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16442,7 +16437,7 @@
         <v>45701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16498,7 +16493,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31440-2026</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16512,10 +16507,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46220</v>
+        <v>44895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16528,7 +16523,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16571,7 +16566,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 59782-2022</t>
+          <t>A 42038-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16585,10 +16580,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44900</v>
+        <v>45561</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16601,7 +16596,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16644,7 +16639,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 52918-2023</t>
+          <t>A 35059-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16658,10 +16653,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45226</v>
+        <v>45142</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16674,7 +16669,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16717,7 +16712,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31419-2026</t>
+          <t>A 59782-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16731,10 +16726,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46220</v>
+        <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16747,7 +16742,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>15.5</v>
+        <v>2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16790,7 +16785,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31438-2026</t>
+          <t>A 1141-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16804,10 +16799,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46220</v>
+        <v>44935</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16863,7 +16858,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 13194-2022</t>
+          <t>A 39054-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16873,14 +16868,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44644</v>
+        <v>46287</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16893,7 +16888,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16936,7 +16931,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61737-2023</t>
+          <t>A 39380-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16950,10 +16945,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45265</v>
+        <v>46288</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16966,7 +16961,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17009,7 +17004,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 42427-2023</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17023,10 +17018,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45180</v>
+        <v>44935</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17039,7 +17034,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17082,7 +17077,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17096,10 +17091,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45645</v>
+        <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17112,7 +17107,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17155,7 +17150,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 9218-2024</t>
+          <t>A 73305-2021</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17169,10 +17164,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45358</v>
+        <v>44551</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17185,7 +17180,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17228,7 +17223,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 31733-2026</t>
+          <t>A 9013-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17242,10 +17237,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46227</v>
+        <v>44979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17258,7 +17253,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17301,7 +17296,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 35608-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17311,14 +17306,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45260</v>
+        <v>45146</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17331,7 +17326,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17374,7 +17369,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 9380-2025</t>
+          <t>A 6453-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17388,10 +17383,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45715</v>
+        <v>45338</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17409,7 +17404,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17452,7 +17447,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 18691-2023</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17466,10 +17461,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45043</v>
+        <v>45359</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17482,7 +17477,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17525,7 +17520,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 6336-2022</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17539,10 +17534,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44600</v>
+        <v>45358</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17555,7 +17550,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17598,7 +17593,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10165-2025</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17612,10 +17607,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45719</v>
+        <v>45230</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17627,13 +17622,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17676,7 +17666,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 55356-2024</t>
+          <t>A 13481-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17690,10 +17680,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45621</v>
+        <v>45005</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17706,7 +17696,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17749,7 +17739,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 57759-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -17763,10 +17753,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45569</v>
+        <v>45246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17778,13 +17768,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -17827,7 +17812,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 13511-2024</t>
+          <t>A 51467-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -17841,10 +17826,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45387</v>
+        <v>45221</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17857,7 +17842,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -17900,7 +17885,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -17914,10 +17899,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45055</v>
+        <v>45090</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17930,7 +17915,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -17973,7 +17958,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 12016-2025</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17987,10 +17972,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45728</v>
+        <v>45435</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18003,7 +17988,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18046,7 +18031,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 55296-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18060,10 +18045,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44700</v>
+        <v>45237</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18076,7 +18061,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18119,7 +18104,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 57465-2024</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18133,10 +18118,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45630</v>
+        <v>45448</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18149,7 +18134,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18192,7 +18177,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 725-2025</t>
+          <t>A 20433-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18206,10 +18191,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45665</v>
+        <v>45435</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18222,7 +18207,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18265,7 +18250,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 13513-2024</t>
+          <t>A 9216-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18279,10 +18264,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45387</v>
+        <v>45358</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18295,7 +18280,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18338,7 +18323,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 10303-2024</t>
+          <t>A 11589-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18352,10 +18337,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45365</v>
+        <v>44631</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18411,7 +18396,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 39054-2026</t>
+          <t>A 2680-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18425,10 +18410,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46287</v>
+        <v>45677</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18441,7 +18426,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18484,7 +18469,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 9098-2025</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18498,10 +18483,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45713</v>
+        <v>45628</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18514,7 +18499,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18557,7 +18542,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 2781-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18571,10 +18556,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45792</v>
+        <v>45677</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18587,7 +18572,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18630,7 +18615,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 61879-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18644,10 +18629,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45792</v>
+        <v>45266</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18660,7 +18645,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -18703,7 +18688,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 39380-2026</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -18717,10 +18702,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46288</v>
+        <v>45635</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18733,7 +18718,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -18776,7 +18761,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 13511-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -18790,10 +18775,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45685</v>
+        <v>45387</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18806,7 +18791,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -18849,7 +18834,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18863,10 +18848,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45594</v>
+        <v>45554</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18878,8 +18863,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -18922,7 +18912,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 43620-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18936,10 +18926,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45475</v>
+        <v>45569</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -18951,8 +18941,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -18995,7 +18990,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 10165-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19009,10 +19004,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45604</v>
+        <v>45719</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19024,8 +19019,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 38160-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45475</v>
+        <v>44812</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19141,7 +19141,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19155,10 +19155,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45629</v>
+        <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 6336-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19228,10 +19228,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45629</v>
+        <v>44600</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19287,7 +19287,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 59527-2024</t>
+          <t>A 43754-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19301,10 +19301,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45638</v>
+        <v>44837</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19360,7 +19360,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 12009-2025</t>
+          <t>A 59272-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19370,14 +19370,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45728</v>
+        <v>45253</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19433,7 +19433,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 29814-2025</t>
+          <t>A 57465-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19447,10 +19447,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45825</v>
+        <v>45630</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19506,7 +19506,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 31163-2025</t>
+          <t>A 61740-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19520,10 +19520,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45832</v>
+        <v>45265</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 31629-2025</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19593,10 +19593,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45834</v>
+        <v>45386</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 22532-2025</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19662,14 +19662,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45786</v>
+        <v>45665</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 33672-2025</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45841</v>
+        <v>45387</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 1197-2025</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19808,14 +19808,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45667</v>
+        <v>45365</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -19871,7 +19871,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 6974-2025</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45701</v>
+        <v>45713</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 279-2024</t>
+          <t>S 1352-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45323</v>
+        <v>44628</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19973,8 +19973,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I263" t="n">
-        <v>3.8</v>
+        <v>47.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20017,7 +20022,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 1352-2022</t>
+          <t>S 761-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20027,14 +20032,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44628</v>
+        <v>44601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20048,11 +20053,11 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I264" t="n">
-        <v>47.1</v>
+        <v>1.4</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20095,7 +20100,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 273-2024</t>
+          <t>S 279-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20112,7 +20117,7 @@
         <v>45323</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20125,7 +20130,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>38.9</v>
+        <v>3.8</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20168,7 +20173,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 761-2022</t>
+          <t>S 510-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20178,14 +20183,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44601</v>
+        <v>45706</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20197,13 +20202,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>1.4</v>
+        <v>32.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20246,7 +20246,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 777-2024</t>
+          <t>S 273-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20256,14 +20256,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45368</v>
+        <v>45323</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.9</v>
+        <v>38.9</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20319,7 +20319,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 274-2024</t>
+          <t>S 777-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20329,14 +20329,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45323</v>
+        <v>45368</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20392,7 +20392,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 280-2024</t>
+          <t>S 274-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20409,7 +20409,7 @@
         <v>45323</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>16.3</v>
+        <v>7.9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20465,7 +20465,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 510-2025</t>
+          <t>S 280-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20479,10 +20479,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45706</v>
+        <v>45323</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>32.6</v>
+        <v>16.3</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -601,7 +601,7 @@
         <v>45624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>45999</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>45726</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44627</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44851</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44858</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45338</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>44867</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45359</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45253</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45327</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45397</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45116</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45435</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45279</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45279</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>46020</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45450</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45685</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44934</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44539</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45146</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45685</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>46038</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45899</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>46048</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45908</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44616</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45260</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>46069</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>46073</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>46073</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45688</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45358</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45595</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45475</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45604</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46091</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>46097</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45475</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45943</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45569</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45947</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45947</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45434</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>46113</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45308</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45348</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44700</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44893</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45960</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45960</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44934</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45643</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45601</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45971</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>44973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45142</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45116</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45116</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>45645</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45569</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>45575</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44771</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44642</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45299</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46136</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44601</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45993</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45940</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44816</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45715</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>46129</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>45510</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>45637</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>45687</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45202</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>44823</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45777</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45825</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45176</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45832</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45253</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45098</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44685</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45834</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>44685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>44900</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45541</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45967</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45377</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>46157</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45740</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45786</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45841</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>44875</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45142</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44909</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44550</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45667</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45576</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>45265</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>46171</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45944</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45701</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45870</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45870</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45243</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45344</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45478</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45180</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46195</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>46195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44644</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45435</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45621</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>46197</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>46196</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45358</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>44565</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45218</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45271</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46209</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45226</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>44637</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45232</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46212</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45728</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45757</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>46045</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45142</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45274</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>44615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>46220</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46220</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45320</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46220</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45264</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>46227</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44895</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44895</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45253</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45043</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45561</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45142</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44935</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46287</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>46288</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44935</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44551</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45146</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45338</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45359</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45358</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45230</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45005</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45221</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45090</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45435</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45237</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45448</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45435</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45358</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44631</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45677</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45628</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45677</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45266</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45635</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45387</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45554</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45569</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45719</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>44812</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44600</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44837</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45253</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45630</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45265</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45386</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45665</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45387</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45365</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45713</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>44628</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45323</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45706</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45323</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>45368</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45323</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45323</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -601,7 +601,7 @@
         <v>45624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>45999</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>45726</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44627</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44851</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44858</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45338</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>44867</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45359</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45253</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45327</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45397</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45116</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45435</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45279</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45279</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>46020</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45450</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45685</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44934</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44539</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45146</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45685</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>46038</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45899</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>46048</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45908</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44616</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45260</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>46069</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>46073</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>46073</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45688</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45358</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45595</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45475</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45604</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46091</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>46097</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45475</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45943</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45569</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45947</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45947</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45947</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45434</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>46113</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45308</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45348</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44700</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44893</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45960</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45960</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44934</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45643</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45601</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45971</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>44973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45142</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45116</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45116</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>45645</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45569</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>45575</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44771</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44642</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45299</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46136</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44601</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45993</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45940</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44816</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45715</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>46129</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>45510</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>45637</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>45687</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45202</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>44823</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45777</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45825</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45176</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45832</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45253</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45098</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44685</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45834</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>44685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>44900</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45541</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45967</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45377</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>46157</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45740</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45786</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45841</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>44875</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45142</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44909</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44550</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45667</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45576</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>45265</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>46171</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45944</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45701</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45870</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45870</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45243</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45344</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45478</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45180</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46195</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>46195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44644</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45435</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45621</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>46197</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>46196</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45358</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>44565</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45218</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45271</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46209</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45226</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>44637</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45232</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46212</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45728</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45757</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>46045</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45142</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45274</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>44615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>46220</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46220</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45320</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46220</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45264</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>46227</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44895</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44895</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45253</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45043</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45561</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45142</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44935</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46287</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>46288</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44935</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44551</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45146</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45338</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45359</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45358</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45230</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45005</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45221</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45090</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45435</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45237</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45448</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45435</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45358</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44631</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45677</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45628</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45677</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45266</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45635</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45387</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45554</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45569</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45719</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>44812</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44600</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44837</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45253</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45630</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45265</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45386</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45665</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45387</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45365</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45713</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>44628</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45323</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45706</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45323</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>45368</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45323</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45323</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>

--- a/Översikt VARA.xlsx
+++ b/Översikt VARA.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56164-2024</t>
+          <t>A 54293-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45624</v>
+        <v>45232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -647,42 +647,42 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
         <v/>
       </c>
     </row>
@@ -706,7 +706,7 @@
         <v>45870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>45999</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 54293-2023</t>
+          <t>A 11270-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45232</v>
+        <v>45726</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -950,10 +950,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -965,39 +965,43 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Härfågel</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 54293-2023 artfynd.xlsx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 54293-2023 karta.png", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 54293-2023 georefererad karta.tif", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 54293-2023 FSC-klagomål.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 54293-2023 FSC-klagomål mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 54293-2023 tillsynsbegäran.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 54293-2023 tillsynsbegäran mail.docx", "A 54293-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
         <v/>
       </c>
     </row>
@@ -1021,7 +1025,7 @@
         <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1117,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11270-2025</t>
+          <t>A 56164-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1127,10 +1131,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45726</v>
+        <v>45624</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1143,7 +1147,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>15.7</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1164,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1176,46 +1180,42 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Härfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 11270-2025 artfynd.xlsx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/artfynd/A 56164-2024 artfynd.xlsx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 11270-2025 karta.png", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor/A 56164-2024 karta.png", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 11270-2025 georefererad karta.tif", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/kartor_geotiff/A 56164-2024 georefererad karta.tif", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 11270-2025 FSC-klagomål.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomål/A 56164-2024 FSC-klagomål.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 11270-2025 FSC-klagomål mail.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/klagomålsmail/A 56164-2024 FSC-klagomål mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 11270-2025 tillsynsbegäran.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsyn/A 56164-2024 tillsynsbegäran.docx", "A 56164-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 11270-2025 tillsynsbegäran mail.docx", "A 11270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1470/fåglar/A 11270-2025 prioriterade fågelarter.docx", "A 11270-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1470/tillsynsmail/A 56164-2024 tillsynsbegäran mail.docx", "A 56164-2024")</f>
         <v/>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44875</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44782</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>44475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10831-2022</t>
+          <t>A 62540-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44627</v>
+        <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 62540-2021</t>
+          <t>A 10831-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44503</v>
+        <v>44627</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>44831</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44851</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44851</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44858</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21085-2022</t>
+          <t>A 12173-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44704</v>
+        <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12173-2022</t>
+          <t>A 21085-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44636</v>
+        <v>44704</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62313-2023</t>
+          <t>A 20443-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45267</v>
+        <v>45435</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6454-2024</t>
+          <t>A 9215-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45338</v>
+        <v>45358</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3702,13 +3702,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3751,7 +3746,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50702-2022</t>
+          <t>A 56856-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3765,10 +3760,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44867</v>
+        <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3776,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3824,7 +3819,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9411-2024</t>
+          <t>A 40224-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3838,10 +3833,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45359</v>
+        <v>45554</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3853,8 +3848,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59259-2023</t>
+          <t>A 31967-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45253</v>
+        <v>45510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>9.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9410-2024</t>
+          <t>A 60543-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49041-2022</t>
+          <t>A 7851-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44858</v>
+        <v>44973</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57255-2022</t>
+          <t>A 58514-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44895</v>
+        <v>45635</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4434-2024</t>
+          <t>A 13235-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45327</v>
+        <v>45386</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14690-2024</t>
+          <t>A 61687-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45397</v>
+        <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23668-2025</t>
+          <t>A 59259-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45792</v>
+        <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33299-2023</t>
+          <t>A 59335-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45116</v>
+        <v>45253</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33099-2025</t>
+          <t>A 725-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45840</v>
+        <v>45665</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20465-2024</t>
+          <t>A 13513-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45435</v>
+        <v>45387</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64317-2023</t>
+          <t>A 10303-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45279</v>
+        <v>45365</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64330-2023</t>
+          <t>A 9058-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45279</v>
+        <v>45713</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63842-2025</t>
+          <t>A 9098-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46020</v>
+        <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48908-2024</t>
+          <t>A 9413-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45594</v>
+        <v>45359</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23669-2025</t>
+          <t>A 9450-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45792</v>
+        <v>45358</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23065-2024</t>
+          <t>A 43615-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45450</v>
+        <v>45569</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5021,8 +5021,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4303-2025</t>
+          <t>A 23669-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45685</v>
+        <v>45792</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 961-2023</t>
+          <t>A 23668-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44934</v>
+        <v>45792</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 71326-2021</t>
+          <t>A 35588-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44539</v>
+        <v>45146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5241,7 +5246,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5284,7 +5289,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9058-2025</t>
+          <t>A 4303-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5298,10 +5303,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45713</v>
+        <v>45685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5314,7 +5319,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5357,7 +5362,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35588-2023</t>
+          <t>A 71326-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45146</v>
+        <v>44539</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5387,7 +5392,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5447,7 +5452,7 @@
         <v>45685</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2867-2026</t>
+          <t>A 48908-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5517,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46038</v>
+        <v>45594</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5533,7 +5538,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5576,7 +5581,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10728-2023</t>
+          <t>A 1152-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5590,10 +5595,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44988</v>
+        <v>44935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5606,7 +5611,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5649,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49820-2022</t>
+          <t>A 41331-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5663,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44862</v>
+        <v>45899</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5679,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5739,7 +5744,7 @@
         <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41331-2025</t>
+          <t>A 73168-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5809,10 +5814,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45899</v>
+        <v>44550</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5825,7 +5830,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4701-2026</t>
+          <t>A 54201-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5882,10 +5887,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46048</v>
+        <v>45232</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5897,13 +5902,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42920-2025</t>
+          <t>A 27856-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45908</v>
+        <v>45475</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9404-2022</t>
+          <t>A 51398-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44616</v>
+        <v>45604</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60819-2023</t>
+          <t>A 27819-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45260</v>
+        <v>45475</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8949-2026</t>
+          <t>A 57313-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46069</v>
+        <v>45629</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20240-2023</t>
+          <t>A 57295-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45055</v>
+        <v>45629</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9881-2026</t>
+          <t>A 42920-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46073</v>
+        <v>45908</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.5</v>
+        <v>0.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9919-2026</t>
+          <t>A 14593-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46073</v>
+        <v>44655</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9923-2026</t>
+          <t>A 22901-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46073</v>
+        <v>45448</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9925-2026</t>
+          <t>A 20465-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46073</v>
+        <v>45435</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9928-2026</t>
+          <t>A 59527-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46073</v>
+        <v>45638</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.1</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4812-2025</t>
+          <t>A 12009-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6686,14 +6686,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45688</v>
+        <v>45728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6705,13 +6705,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9215-2024</t>
+          <t>A 57255-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45358</v>
+        <v>44895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6779,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>12.2</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57313-2024</t>
+          <t>A 31260-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45629</v>
+        <v>44771</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6852,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6895,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57295-2024</t>
+          <t>A 29814-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6909,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45629</v>
+        <v>45825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6925,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6968,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12007-2025</t>
+          <t>A 33099-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6982,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45728</v>
+        <v>45840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +6998,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7041,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49391-2024</t>
+          <t>A 14116-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7056,14 +7051,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45595</v>
+        <v>45740</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7071,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7114,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 27819-2024</t>
+          <t>A 35056-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45475</v>
+        <v>45142</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7149,7 +7144,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7192,7 +7187,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51398-2024</t>
+          <t>A 31163-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7206,10 +7201,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45604</v>
+        <v>45832</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7222,7 +7217,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7265,7 +7260,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12700-2026</t>
+          <t>A 44947-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46091</v>
+        <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7294,8 +7289,13 @@
           <t>VARA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>10.9</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13710-2026</t>
+          <t>A 31629-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46097</v>
+        <v>45834</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 27856-2024</t>
+          <t>A 40331-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45475</v>
+        <v>44823</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50123-2025</t>
+          <t>A 41690-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45943</v>
+        <v>45176</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7513,13 +7513,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7562,7 +7557,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50812-2023</t>
+          <t>A 22532-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7572,14 +7567,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45217</v>
+        <v>45786</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7592,7 +7587,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7635,7 +7630,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43624-2024</t>
+          <t>A 33672-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7649,10 +7644,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45569</v>
+        <v>45841</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7662,11 +7657,6 @@
       <c r="G95" t="inlineStr">
         <is>
           <t>VARA</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -7713,7 +7703,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 51212-2025</t>
+          <t>A 50123-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7727,10 +7717,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45947</v>
+        <v>45943</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7740,6 +7730,11 @@
       <c r="G96" t="inlineStr">
         <is>
           <t>VARA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -7786,7 +7781,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51218-2025</t>
+          <t>A 4434-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7800,10 +7795,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45947</v>
+        <v>45327</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7816,7 +7811,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7859,7 +7854,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51206-2025</t>
+          <t>A 53719-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7873,10 +7868,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45947</v>
+        <v>45230</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7889,7 +7884,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7932,7 +7927,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20196-2024</t>
+          <t>A 63842-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7946,10 +7941,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45434</v>
+        <v>46020</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7962,7 +7957,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8005,7 +8000,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16754-2026</t>
+          <t>A 51212-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8019,10 +8014,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46113</v>
+        <v>45947</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8032,11 +8027,6 @@
       <c r="G100" t="inlineStr">
         <is>
           <t>VARA</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -8083,7 +8073,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1980-2024</t>
+          <t>A 51218-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8097,10 +8087,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45308</v>
+        <v>45947</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8113,7 +8103,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8156,7 +8146,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7655-2024</t>
+          <t>A 51206-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8170,10 +8160,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45348</v>
+        <v>45947</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8186,7 +8176,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8.5</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8229,7 +8219,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20536-2022</t>
+          <t>A 1197-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8243,10 +8233,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44700</v>
+        <v>45667</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8259,7 +8249,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8302,7 +8292,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56456-2022</t>
+          <t>A 57253-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8316,10 +8306,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44893</v>
+        <v>44895</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8332,7 +8322,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8375,7 +8365,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 53604-2025</t>
+          <t>A 4622-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8389,10 +8379,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45960</v>
+        <v>45687</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8405,7 +8395,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>19.8</v>
+        <v>7.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8448,7 +8438,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 53606-2025</t>
+          <t>A 6974-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8462,10 +8452,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45960</v>
+        <v>45701</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8478,7 +8468,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8521,7 +8511,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 55667-2024</t>
+          <t>A 53606-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8535,10 +8525,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45622</v>
+        <v>45960</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8551,7 +8541,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8594,7 +8584,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53802-2025</t>
+          <t>A 36630-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8608,10 +8598,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45960</v>
+        <v>45870</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8624,7 +8614,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8667,7 +8657,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 962-2023</t>
+          <t>A 36632-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8677,14 +8667,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44934</v>
+        <v>45870</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8697,7 +8687,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8740,7 +8730,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 60543-2024</t>
+          <t>A 53604-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8754,10 +8744,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45643</v>
+        <v>45960</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8770,7 +8760,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>19.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8813,7 +8803,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 50673-2024</t>
+          <t>A 50702-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8827,10 +8817,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45601</v>
+        <v>44867</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8843,7 +8833,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8886,7 +8876,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 55561-2025</t>
+          <t>A 53802-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8900,10 +8890,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45971</v>
+        <v>45960</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8916,7 +8906,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8959,7 +8949,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7851-2023</t>
+          <t>A 17543-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8973,10 +8963,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44973</v>
+        <v>45757</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8989,7 +8979,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9032,7 +9022,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35042-2023</t>
+          <t>A 45303-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9046,10 +9036,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45142</v>
+        <v>45576</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9062,7 +9052,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9105,7 +9095,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 33300-2023</t>
+          <t>A 55561-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9119,10 +9109,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45116</v>
+        <v>45971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9178,7 +9168,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33301-2023</t>
+          <t>A 25764-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9192,10 +9182,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45116</v>
+        <v>45090</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9208,7 +9198,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9251,7 +9241,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61269-2024</t>
+          <t>A 62775-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9261,14 +9251,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45645</v>
+        <v>45271</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9281,7 +9271,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9324,7 +9314,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 43615-2024</t>
+          <t>A 61738-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9338,10 +9328,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45569</v>
+        <v>45265</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9353,13 +9343,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9402,7 +9387,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 44947-2024</t>
+          <t>A 2867-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9416,10 +9401,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45575</v>
+        <v>46038</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9431,13 +9416,8 @@
           <t>VARA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9497,7 +9477,7 @@
         <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9553,7 +9533,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31260-2022</t>
+          <t>A 9411-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9567,10 +9547,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44771</v>
+        <v>45359</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>